--- a/MyEUDR_Lead_Mapping_v2.xlsx
+++ b/MyEUDR_Lead_Mapping_v2.xlsx
@@ -962,7 +962,7 @@
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>https://www.conceriaitalia.com/contatti</t>
+          <t>https://www.conceriaitalia.com/nuova-pagina</t>
         </is>
       </c>
     </row>
@@ -1526,8 +1526,16 @@
           <t>≈28,2M€ (2024) / ~95 dip. (ReportAziende/FatturatoItalia)</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr"/>
-      <c r="E26" s="5" t="inlineStr"/>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Alessandro Dal Soglio</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Presidente</t>
+        </is>
+      </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
           <t>https://it.linkedin.com/company/compensati-impiallacciature-materiali-affini-c.i.m.a.-s.r.l.-in-sigla-c.i.m.a.-s.r.l.</t>
@@ -1898,8 +1906,16 @@
           <t>≈19,1M€ (2024) / ~35 dip. (FatturatoItalia)</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr"/>
-      <c r="E35" s="3" t="inlineStr"/>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Giovanni Ballardini</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Direttore Generale</t>
+        </is>
+      </c>
       <c r="F35" s="3" t="inlineStr"/>
       <c r="G35" s="4" t="inlineStr">
         <is>
@@ -1986,8 +2002,16 @@
           <t>n.d.</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr"/>
-      <c r="E37" s="3" t="inlineStr"/>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Nella De Sabbata</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Presidente</t>
+        </is>
+      </c>
       <c r="F37" s="3" t="inlineStr"/>
       <c r="G37" s="4" t="inlineStr">
         <is>
@@ -2031,7 +2055,7 @@
       <c r="F38" s="5" t="inlineStr"/>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>n.d.</t>
+          <t>zalfcen@zalf.com</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr"/>
@@ -2062,8 +2086,16 @@
           <t>~12,5 mln € (2022); ~60 dip.</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr"/>
-      <c r="E39" s="3" t="inlineStr"/>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Giorgio Giovanni Bartoli</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Presidente / Amministratore unico</t>
+        </is>
+      </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/bartoli-spa/</t>
@@ -2330,8 +2362,16 @@
           <t>~14,1 mln € (2024); prodotti FSC</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr"/>
-      <c r="E45" s="3" t="inlineStr"/>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Ernesto Sandreschi</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Presidente / Legale rappresentante</t>
+        </is>
+      </c>
       <c r="F45" s="3" t="inlineStr"/>
       <c r="G45" s="4" t="inlineStr">
         <is>
@@ -2910,8 +2950,16 @@
           <t>Fatturato ~10,5 mln € (2025); 6,2 mln € (2023); ~21 dipendenti</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr"/>
-      <c r="E59" s="3" t="inlineStr"/>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Matteo Trucillo</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>Presidente e Amministratore Delegato</t>
+        </is>
+      </c>
       <c r="F59" s="3" t="inlineStr"/>
       <c r="G59" s="4" t="inlineStr">
         <is>
@@ -3650,8 +3698,16 @@
           <t>~30 mln € (2024); importatore diretto di cacao — NB: gruppo Polo del Gusto (Illy)</t>
         </is>
       </c>
-      <c r="D75" s="3" t="inlineStr"/>
-      <c r="E75" s="3" t="inlineStr"/>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>Riccardo Illy</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>Amministratore Delegato</t>
+        </is>
+      </c>
       <c r="F75" s="3" t="inlineStr"/>
       <c r="G75" s="4" t="inlineStr">
         <is>
@@ -3778,8 +3834,16 @@
           <t>~13 mln €; PMI familiare (produzione cacao/cioccolato)</t>
         </is>
       </c>
-      <c r="D78" s="5" t="inlineStr"/>
-      <c r="E78" s="5" t="inlineStr"/>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>Francesco Mezzadri Majani</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>Presidente e Amministratore Delegato</t>
+        </is>
+      </c>
       <c r="F78" s="5" t="inlineStr"/>
       <c r="G78" s="6" t="inlineStr">
         <is>
@@ -4030,8 +4094,16 @@
           <t>~29,1 mln €; guarnizioni/tenute in gomma (PEC da registro)</t>
         </is>
       </c>
-      <c r="D84" s="5" t="inlineStr"/>
-      <c r="E84" s="5" t="inlineStr"/>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>Guglielmo Debenedetti</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>Presidente</t>
+        </is>
+      </c>
       <c r="F84" s="5" t="inlineStr"/>
       <c r="G84" s="5" t="inlineStr">
         <is>
@@ -4146,7 +4218,7 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Gomma</t>
+          <t>Gomma — articoli tecnici in gomma naturale (NR), sintetica, siliconica e fluoroelastomeri</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -4194,8 +4266,16 @@
           <t>~59,3 mln € (2024); 50-99 dip. — sopra soglia ma PMI indip. specializzata in soia</t>
         </is>
       </c>
-      <c r="D88" s="5" t="inlineStr"/>
-      <c r="E88" s="5" t="inlineStr"/>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>Gianpietro Didoné</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>Presidente</t>
+        </is>
+      </c>
       <c r="F88" s="6" t="inlineStr">
         <is>
           <t>https://it.linkedin.com/company/cortal-extrasoy-spa</t>
@@ -6518,7 +6598,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Jutta Summann, Emanuel Dick</t>
+          <t>Jutta Summann, Johannes Kunze</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -6958,7 +7038,7 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Max J.W. Ültzen</t>
+          <t>Max J.W. Ueltzen, Christian Bruns, Pauline von Mettenheim</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -7345,7 +7425,7 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>n.d. (torrefazione media, gegr. 1908)</t>
+          <t>n.d. (torrefazione media, gegr. 1908). Legame di gruppo: controllata al 100% da Zentralkonsum eG (Berlino) — HRB 107856.</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -8026,7 +8106,7 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Edmund Agyapong-Poku</t>
+          <t>Nathaniel Durant</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -8259,7 +8339,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>Weibler Confiserie Chocolaterie GmbH</t>
+          <t>Weibler Confiserie Chocolaterie GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -8370,7 +8450,7 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>Franz Josef Wolf</t>
+          <t>Joachim Geimer</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
@@ -9228,7 +9308,7 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Mangimi/Soia</t>
+          <t>Mangimi/Soia + Legno — pellet di legno Sonnen-Pellets (dal 1998, certificati ENplus)</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -9878,7 +9958,7 @@
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>akonkoskensaha@akonkoskensaha.fi</t>
+          <t>akonkoskensaha@netikka.fi</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -10597,7 +10677,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Legno/Arredo — compensato betulla/lamellare</t>
+          <t>Legno/Arredo — botole d'ispezione e prodotti in compensato (produzione e rivendita specializzata)</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -11416,7 +11496,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Piiroinen Oy</t>
+          <t>Arvo Piiroinen Oy</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -13334,7 +13414,7 @@
       <c r="F74" s="5" t="inlineStr"/>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>n.d.</t>
+          <t>tilaukset@brunberg.fi</t>
         </is>
       </c>
       <c r="H74" s="6" t="inlineStr">
@@ -13841,7 +13921,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Bovini/Carne</t>
+          <t>Bovini/Carne — prevalentemente ovino (~15.000 capi/anno); bovini ~2.500 capi/anno</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -14286,7 +14366,7 @@
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>https://www.proff.dk/firma/onecollection-as/ringk%C3%B8bing/m%C3%B8bler/GXS757I015G</t>
+          <t>https://www.proff.dk/firma/onecollection-as/ringk%C3%B8bing/producenter/GQYY8HI016D</t>
         </is>
       </c>
     </row>
@@ -16269,7 +16349,7 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>JOHNSEN GRAPHIC SOLUTIONS A/S (oggi anche Johnsen Print &amp; Digital Media A/S)</t>
+          <t>JOHNSEN PRINT &amp; DIGITAL MEDIA A/S (già Johnsen Graphic Solutions A/S)</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -19911,8 +19991,16 @@
           <t>≈6,2 M€ / 14 dip. (allabolag 2024: 70 552 KSEK) · org.nr 556093-1734 · sotto la fascia target 10-20 M€, tenuta per copertura · azienda familiare dal 1901</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr"/>
-      <c r="E25" s="3" t="inlineStr"/>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Lars Anders Hilding Carlsson</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Styrelseordförande / ansvarig (nessun VD registrato)</t>
+        </is>
+      </c>
       <c r="F25" s="3" t="inlineStr"/>
       <c r="G25" s="4" t="inlineStr">
         <is>
@@ -22327,8 +22415,16 @@
           <t>Fatturato 57,8 MSEK (~5,1 M€) 2024 (+28,7%); 13 dipendenti (gruppo di 4 società: 23 dipendenti, 55,0 MSEK) (fonte: allabolag.se / bolagsfakta.se, bilancio 2024). Org.nr 556764-1575.</t>
         </is>
       </c>
-      <c r="D73" s="3" t="inlineStr"/>
-      <c r="E73" s="3" t="inlineStr"/>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>Johan Wellander</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>Ordförande / grundare (nessun VD registrato)</t>
+        </is>
+      </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
           <t>https://sv.linkedin.com/company/lykke-coffee-farms</t>
@@ -22817,7 +22913,11 @@
           <t>VD (verkställande direktör)</t>
         </is>
       </c>
-      <c r="F83" s="3" t="inlineStr"/>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>https://se.linkedin.com/company/ab-johan-hansson</t>
+        </is>
+      </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
           <t>kontakt@johanhansson.se</t>
@@ -23027,12 +23127,12 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>Bovini/Carne — macello indipendente (bovini, suini, ovini) e commercio carni</t>
+          <t>Bovini/Carne — macello (bovini, suini, ovini) e commercio carni, in gruppo familiare</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Fatturato 227.210 KSEK (~20,1 M€) — bilancio 2024, +18,2% (fonte allabolag/bolagsfakta); org.nr 556257-9861. Nella società capofila risultano 0 dipendenti registrati (personale in società del gruppo). In pieno target di fatturato.</t>
+          <t>Fatturato 227.210 KSEK (~20,1 M€) — bilancio 2024, +18,2% (fonte allabolag/bolagsfakta); org.nr 556257-9861. Nella società capofila risultano 0 dipendenti registrati (personale in società del gruppo). In pieno target di fatturato. Capogruppo: Aktiebolaget Joh. M. Johansson, Kött- &amp; Charkuteriaffär (gruppo familiare di 4 societa').</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr"/>
@@ -23371,21 +23471,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId208"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId209"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F87" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F83" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F87" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId226"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24591,8 +24692,16 @@
           <t>Fatturato non pubblicato; numero dipendenti e numero KVK non reperiti da fonti pubbliche accessibili via ricerca. Membro FCC (Federation of Cocoa Commerce). Sede Weteringschans 26, Amsterdam. Ufficio vendite dedicato della Cocoa Abrabopa Association (cooperativa di coltivatori ghanesi): importatore diretto di cacao = operatore EUDR.</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr"/>
-      <c r="E26" s="5" t="inlineStr"/>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Merijn Bruinse</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/ascot-amsterdam</t>
@@ -25250,9 +25359,9 @@
       <c r="D40" s="5" t="inlineStr"/>
       <c r="E40" s="5" t="inlineStr"/>
       <c r="F40" s="5" t="inlineStr"/>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>n.d.</t>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>info@bannink.nl</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr">
@@ -25289,12 +25398,12 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Anton de Groot</t>
+          <t>Wim Everts</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Directeur</t>
+          <t>Algemeen directeur</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -25659,7 +25768,11 @@
           <t>n.d.</t>
         </is>
       </c>
-      <c r="H48" s="5" t="inlineStr"/>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>https://www.snelbv.nl</t>
+        </is>
+      </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
           <t>Bemmel (Lingewaard), Gelderland</t>
@@ -25934,159 +26047,147 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>Blanche Dael B.V. (Maison Blanche Dael)</t>
+          <t>BENZU (eenmanszaak) — handelsnaam «Origin Bridge»</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Caffè — torrefazione + engros/wholesale</t>
+          <t>Caffè — import caffè verde</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Fatturato non pubblicato (bilancio abbreviato); n. dipendenti non pubblicato nelle fonti consultate. KVK 76979229, Aan de Brikkebouw 10 Maastricht (entità costituita nel 2019), P.IVA NL860860814B01. Koffiebranderij + theepakkerij familiare dal 1878, SBI groothandel in koffie, thee, cacao en specerijen. Verosimilmente sotto la fascia 5-40 M€.</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>Albert Berghof</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>Directeur / eigenaar</t>
-        </is>
-      </c>
+          <t>Fatturato e n. dipendenti non pubblicati. KVK 70878315, P.IVA NL001587917B24 — la struttura del numero IVA indica una ditta individuale/eenmanszaak, NON una B.V.: la forma giuridica va verificata prima del contatto. Heidehoflaan 2B, Barchem. Importatore di caffè verde specialty dalla Colombia (micro-lotti e volumi da produzione) per torrefattori professionali in Europa. Micro-impresa, sotto i 5 M€, ma operatore EUDR in senso stretto.</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr"/>
+      <c r="E54" s="5" t="inlineStr"/>
       <c r="F54" s="5" t="inlineStr"/>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>office@blanchedael.nl</t>
+          <t>info@bridgetoorigin.com</t>
         </is>
       </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>https://www.blanchedael.nl/</t>
+          <t>https://originbridge.coffee/</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>Maastricht (Limburg)</t>
+          <t>Barchem, gem. Lochem (Gelderland)</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>https://www.creditsafe.com/business-index/en-us/company/blanche-dael-bv-nl05333583</t>
+          <t>https://originbridge.coffee/legal-information/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>Bocca Coffee B.V.</t>
+          <t>Blanche Dael B.V. (Maison Blanche Dael)</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Caffè — torrefazione + import caffè verde</t>
+          <t>Caffè — torrefazione + engros/wholesale</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Fatturato ~4,8 M€ con 40 dipendenti (fonte: New10, articolo aziendale). Sede Kerkstraat 96 Amsterdam, torrefazione a Dronten; primo specialty roaster olandese, B Corp. SOTTO la fascia 5-40 M€ (borderline). Nota legame: il fondatore Menno Simons è anche fondatore dell'importatore di caffè verde Trabocca B.V.</t>
+          <t>Fatturato non pubblicato (bilancio abbreviato); n. dipendenti non pubblicato nelle fonti consultate. KVK 76979229, Aan de Brikkebouw 10 Maastricht (entità costituita nel 2019), P.IVA NL860860814B01. Koffiebranderij + theepakkerij familiare dal 1878, SBI groothandel in koffie, thee, cacao en specerijen. Verosimilmente sotto la fascia 5-40 M€.</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Menno Simons</t>
+          <t>Albert Berghof</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Oprichter / directeur</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/bocca-coffee/</t>
-        </is>
-      </c>
+          <t>Directeur / eigenaar</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr"/>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>info@bocca.nl</t>
+          <t>office@blanchedael.nl</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>https://bocca.nl/</t>
+          <t>https://www.blanchedael.nl/</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>Amsterdam (Noord-Holland) — torrefazione a Dronten (Flevoland)</t>
+          <t>Maastricht (Limburg)</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>https://new10.com/blog/bocca-coffee-bliksemstart-verandering-groei</t>
+          <t>https://www.creditsafe.com/business-index/en-us/company/blanche-dael-bv-nl05333583</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>Brandsma Koffie B.V.</t>
+          <t>Bocca Coffee B.V.</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>Caffè — torrefazione + engros/wholesale</t>
+          <t>Caffè — torrefazione + import caffè verde</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Fatturato non pubblicato e n. dipendenti non pubblicato nelle fonti consultate (bilancio abbreviato). Numero KVK non reperito con le sole fonti aperte. Azienda familiare dal 1893 a Bolsward, torrefazione propria, fornitore nazionale per horeca, aziende e privati. Verosimilmente sotto la fascia 5-40 M€.</t>
+          <t>Fatturato ~4,8 M€ con 40 dipendenti (fonte: New10, articolo aziendale). Sede Kerkstraat 96 Amsterdam, torrefazione a Dronten; primo specialty roaster olandese, B Corp. SOTTO la fascia 5-40 M€ (borderline). Nota legame: il fondatore Menno Simons è anche fondatore dell'importatore di caffè verde Trabocca B.V.</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Menno Brandsma</t>
+          <t>Menno Simons</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>Directeur (4a generazione)</t>
+          <t>Oprichter / directeur</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/company/brandsma-koffie</t>
+          <t>https://www.linkedin.com/company/bocca-coffee/</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>info@brandsmakoffie.nl</t>
+          <t>info@bocca.nl</t>
         </is>
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>https://www.brandsmakoffie.nl/</t>
+          <t>https://bocca.nl/</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>Bolsward (Friesland)</t>
+          <t>Amsterdam (Noord-Holland) — torrefazione a Dronten (Flevoland)</t>
         </is>
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>https://grachtenbeans.nl/koffiebrander/brandsma-koffie/</t>
+          <t>https://new10.com/blog/bocca-coffee-bliksemstart-verandering-groei</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>Fleur de Café B.V.</t>
+          <t>Brandsma Koffie B.V.</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -26096,237 +26197,241 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Fatturato non pubblicato e n. dipendenti non pubblicato nelle fonti consultate (bilancio abbreviato). Numero KVK non reperito; P.IVA NL854149879B01. Hamburgweg 10, Deventer. Groothandel koffie/thee + koffiebranderij per horeca, retail e privati; fornisce anche impianti a chi vuole avviare una propria torrefazione. Verosimilmente piccola impresa sotto i 5 M€.</t>
-        </is>
-      </c>
-      <c r="D57" s="3" t="inlineStr"/>
-      <c r="E57" s="3" t="inlineStr"/>
-      <c r="F57" s="3" t="inlineStr"/>
+          <t>Fatturato non pubblicato e n. dipendenti non pubblicato nelle fonti consultate (bilancio abbreviato). Numero KVK non reperito con le sole fonti aperte. Azienda familiare dal 1893 a Bolsward, torrefazione propria, fornitore nazionale per horeca, aziende e privati. Verosimilmente sotto la fascia 5-40 M€.</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Menno Brandsma</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Directeur (4a generazione)</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>https://nl.linkedin.com/company/brandsma-koffie</t>
+        </is>
+      </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>info@fleurdecafe.nl</t>
+          <t>info@brandsmakoffie.nl</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>https://www.fleurdecafe.nl/</t>
+          <t>https://www.brandsmakoffie.nl/</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>Deventer (Overijssel)</t>
+          <t>Bolsward (Friesland)</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>https://www.fleurdecafe.nl/klantenservice</t>
+          <t>https://grachtenbeans.nl/koffiebrander/brandsma-koffie/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>G. Bijdendijk B.V. (Koffiehandelshuis G. Bijdendijk)</t>
+          <t>Fleur de Café B.V.</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>Caffè — import caffè verde</t>
+          <t>Caffè — torrefazione + engros/wholesale</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Fatturato non pubblicato (bilancio abbreviato). 2-5 dipendenti registrati alla sede (fonte: Oozo.nl / registro KVK, 2025); il team pubblicato sul sito conta ~9 persone. KVK 08022494, Laan 57 Nunspeet. Casa commerciale di caffè verde attiva dal 1843 (175 anni nel 2018): volumi d'import elevati rispetto all'organico — operatore EUDR in senso stretto.</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="inlineStr">
-        <is>
-          <t>Mark Bouw</t>
-        </is>
-      </c>
-      <c r="E58" s="5" t="inlineStr">
-        <is>
-          <t>Managing Director (con Robbert Bouw)</t>
-        </is>
-      </c>
-      <c r="F58" s="6" t="inlineStr">
-        <is>
-          <t>https://nl.linkedin.com/company/bijdendijk</t>
-        </is>
-      </c>
+          <t>Fatturato non pubblicato e n. dipendenti non pubblicato nelle fonti consultate (bilancio abbreviato). Numero KVK non reperito; P.IVA NL854149879B01. Hamburgweg 10, Deventer. Groothandel koffie/thee + koffiebranderij per horeca, retail e privati; fornisce anche impianti a chi vuole avviare una propria torrefazione. Verosimilmente piccola impresa sotto i 5 M€.</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr"/>
+      <c r="E58" s="5" t="inlineStr"/>
+      <c r="F58" s="5" t="inlineStr"/>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>info@bijdendijk.nl</t>
+          <t>info@fleurdecafe.nl</t>
         </is>
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>https://www.bijdendijk.nl/</t>
+          <t>https://www.fleurdecafe.nl/</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>Nunspeet (Gelderland)</t>
+          <t>Deventer (Overijssel)</t>
         </is>
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>https://www.oozo.nl/bedrijven/nunspeet/nunspeet/hulshorst/145458/g-bijdendijk-b-v</t>
+          <t>https://www.fleurdecafe.nl/klantenservice</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>Giraffe Coffee B.V.</t>
+          <t>G. Bijdendijk B.V. (Koffiehandelshuis G. Bijdendijk)</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Caffè — torrefazione + import caffè verde</t>
+          <t>Caffè — import caffè verde</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Fatturato e n. dipendenti non pubblicati nelle fonti consultate; numero KVK non reperito con le sole fonti aperte. Torrefazione specialty aperta nel 2013 a Rotterdam, con Coffee Bar &amp; Academy in Hoogstraat 46a; acquisto diretto con premio extra ai produttori, consegna a ristoranti e negozi in tutta NL. Micro-impresa, ben sotto i 5 M€ — segnalata per la componente di acquisto diretto di caffè verde.</t>
+          <t>Fatturato non pubblicato (bilancio abbreviato). 2-5 dipendenti registrati alla sede (fonte: Oozo.nl / registro KVK, 2025); il team pubblicato sul sito conta ~9 persone. KVK 08022494, Laan 57 Nunspeet. Casa commerciale di caffè verde attiva dal 1843 (175 anni nel 2018): volumi d'import elevati rispetto all'organico — operatore EUDR in senso stretto.</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Maarten van der Jagt</t>
+          <t>Mark Bouw</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Oprichter (con Mark Jordaan)</t>
+          <t>Managing Director (con Robbert Bouw)</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/company/giraffe-coffee-bv</t>
+          <t>https://nl.linkedin.com/company/bijdendijk</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>info@giraffecoffee.com</t>
+          <t>info@bijdendijk.nl</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>https://giraffecoffee.com/</t>
+          <t>https://www.bijdendijk.nl/</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>Rotterdam (Zuid-Holland)</t>
+          <t>Nunspeet (Gelderland)</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>https://giraffecoffee.com/en/pages/over</t>
+          <t>https://www.oozo.nl/bedrijven/nunspeet/nunspeet/hulshorst/145458/g-bijdendijk-b-v</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>Greencof B.V.</t>
+          <t>Giraffe Coffee B.V.</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>Caffè — import caffè verde</t>
+          <t>Caffè — torrefazione + import caffè verde</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Fatturato non pubblicato (BV con bilancio abbreviato). KVK 37123582 (su company.info registrata a Zaandam; sede operativa Grote Oost 53, Hoorn), P.IVA NL820866702B01, fondata 2006. Importatore/esportatore di caffè verde specialty (fairtrade, bio, Rainforest Alliance) con stoccaggio ad Anversa e Amburgo. Operatore EUDR in senso stretto; taglia probabilmente sotto i 10 M€ — da verificare.</t>
+          <t>Fatturato e n. dipendenti non pubblicati nelle fonti consultate; numero KVK non reperito con le sole fonti aperte. Torrefazione specialty aperta nel 2013 a Rotterdam, con Coffee Bar &amp; Academy in Hoogstraat 46a; acquisto diretto con premio extra ai produttori, consegna a ristoranti e negozi in tutta NL. Micro-impresa, ben sotto i 5 M€ — segnalata per la componente di acquisto diretto di caffè verde.</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Leon Zaal</t>
+          <t>Maarten van der Jagt</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>Directeur</t>
-        </is>
-      </c>
-      <c r="F60" s="5" t="inlineStr"/>
+          <t>Oprichter (con Mark Jordaan)</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>https://nl.linkedin.com/company/giraffe-coffee-bv</t>
+        </is>
+      </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>info@greencof.com</t>
+          <t>info@giraffecoffee.com</t>
         </is>
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
-          <t>https://greencof.com/</t>
+          <t>https://giraffecoffee.com/</t>
         </is>
       </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>Hoorn (Noord-Holland)</t>
+          <t>Rotterdam (Zuid-Holland)</t>
         </is>
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>https://companyinfo.nl/organisatieprofiel/groothandel-in-koffie-thee-cacao-en-specerijen/greencof-b-v-zaandam-37123582</t>
+          <t>https://giraffecoffee.com/en/pages/over</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>Hesselink Koffiesystemen B.V.</t>
+          <t>Greencof B.V.</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Caffè — torrefazione + engros/wholesale</t>
+          <t>Caffè — import caffè verde</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Fatturato non pubblicato (bilancio abbreviato). 11-20 dipendenti (fonte: Oozo.nl / registro KVK, 2025). KVK 08049402, Rondweg Zuid 95 Winterswijk. Groothandel in koffie, thee, cacao en specerijen. Fa capo a Hesselink Koffie Groep B.V. (KVK 59575492, holding). Torrefazione familiare dal 1885. Probabilmente sotto la fascia 5-40 M€ — segnalata per rilevanza settoriale.</t>
+          <t>Fatturato non pubblicato (BV con bilancio abbreviato). KVK 37123582 (su company.info registrata a Zaandam; sede operativa Grote Oost 53, Hoorn), P.IVA NL820866702B01, fondata 2006. Importatore/esportatore di caffè verde specialty (fairtrade, bio, Rainforest Alliance) con stoccaggio ad Anversa e Amburgo. Operatore EUDR in senso stretto; taglia probabilmente sotto i 10 M€ — da verificare.</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Gerrit Hesselink</t>
+          <t>Leon Zaal</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Directeur / eigenaar</t>
+          <t>Directeur</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr"/>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>info@hesselinkkoffie.eu</t>
+          <t>info@greencof.com</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>https://hesselinkkoffie.nl/</t>
+          <t>https://greencof.com/</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>Winterswijk (Gelderland)</t>
+          <t>Hoorn (Noord-Holland)</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>https://www.oozo.nl/bedrijven/winterswijk/stad/winterswijk-zuidwest/171483/hesselink-koffiesystemen-b-v</t>
+          <t>https://companyinfo.nl/organisatieprofiel/groothandel-in-koffie-thee-cacao-en-specerijen/greencof-b-v-zaandam-37123582</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Kaldi Koffie en Thee B.V.</t>
+          <t>Hesselink Koffiesystemen B.V.</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
@@ -26336,97 +26441,97 @@
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Fatturato non pubblicato (bilancio abbreviato). KVK 24310514, Popovstraat 70 Zwolle, costituita nel 2000. Formula in franchising con oltre 30 negozi specializzati koffie &amp; thee in NL + canale B2B; marchi propri con caffè da diversi continenti. Numero di dipendenti della BV non pubblicato nelle fonti consultate.</t>
+          <t>Fatturato non pubblicato (bilancio abbreviato). 11-20 dipendenti (fonte: Oozo.nl / registro KVK, 2025). KVK 08049402, Rondweg Zuid 95 Winterswijk. Groothandel in koffie, thee, cacao en specerijen. Fa capo a Hesselink Koffie Groep B.V. (KVK 59575492, holding). Torrefazione familiare dal 1885. Probabilmente sotto la fascia 5-40 M€ — segnalata per rilevanza settoriale.</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Martijn Bas</t>
+          <t>Gerrit Hesselink</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>Directeur (dagelijkse leiding)</t>
-        </is>
-      </c>
-      <c r="F62" s="6" t="inlineStr">
-        <is>
-          <t>https://nl.linkedin.com/company/kaldikoffieenthee</t>
-        </is>
-      </c>
-      <c r="G62" s="5" t="inlineStr">
-        <is>
-          <t>n.d.</t>
+          <t>Directeur / eigenaar</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr"/>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>info@hesselinkkoffie.eu</t>
         </is>
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>https://kaldi.nl/</t>
+          <t>https://hesselinkkoffie.nl/</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>Zwolle (Overijssel)</t>
+          <t>Winterswijk (Gelderland)</t>
         </is>
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>https://www.creditsafe.com/business-index/en-us/company/kaldi-koffie-en-thee-bv-nl01235350</t>
+          <t>https://www.oozo.nl/bedrijven/winterswijk/stad/winterswijk-zuidwest/171483/hesselink-koffiesystemen-b-v</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>Koffiebranderij G. Peeze B.V.</t>
+          <t>Kaldi Koffie en Thee B.V.</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Caffè — torrefazione + import caffè verde</t>
+          <t>Caffè — torrefazione + engros/wholesale</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Fatturato non pubblicato (bilancio abbreviato). ~55 dipendenti (fonte: GraydonGo / TransFirm, 2025). KVK 09026526, Ringoven 36 Arnhem, attiva dal 1971. ATTENZIONE LEGAME DI GRUPPO: da maggio 2025 le azioni sono state acquisite dal fondo Berk Partners e Peeze è confluita in Coffee Growth Group (direzione Myriam Lufting / Wouter Jansen van Velsen). Torrefazione B Corp, acquisto diretto di caffè verde all'origine.</t>
+          <t>Fatturato non pubblicato (bilancio abbreviato). KVK 24310514, Popovstraat 70 Zwolle, costituita nel 2000. Formula in franchising con oltre 30 negozi specializzati koffie &amp; thee in NL + canale B2B; marchi propri con caffè da diversi continenti. Numero di dipendenti della BV non pubblicato nelle fonti consultate.</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>Myriam Lufting</t>
+          <t>Martijn Bas</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Directeur</t>
-        </is>
-      </c>
-      <c r="F63" s="3" t="inlineStr"/>
-      <c r="G63" s="4" t="inlineStr">
-        <is>
-          <t>info@peeze.nl</t>
+          <t>Directeur (dagelijkse leiding)</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>https://nl.linkedin.com/company/kaldikoffieenthee</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>n.d.</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>https://peeze.nl/</t>
+          <t>https://kaldi.nl/</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>Arnhem (Gelderland)</t>
+          <t>Zwolle (Overijssel)</t>
         </is>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>https://www.transfirm.nl/nl/organisatie/090265260000-koffiebranderij-g.-peeze-b.v.</t>
+          <t>https://www.creditsafe.com/business-index/en-us/company/kaldi-koffie-en-thee-bv-nl01235350</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>Moyee Nederland B.V.</t>
+          <t>Koffiebranderij G. Peeze B.V.</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
@@ -26436,45 +26541,45 @@
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Fatturato non pubblicato (bilancio abbreviato); una fonte terza (rocketreach) riporta ~45 addetti — dato non ufficiale. KVK 61730556, Elementenstraat 10 Amsterdam, fondata 2014. Groothandel in koffie, thee, cacao en specerijen; modello 'FairChain' con torrefazione in Etiopia e importazione in NL. Micro/piccola impresa, verosimilmente sotto i 5 M€.</t>
+          <t>Fatturato non pubblicato (bilancio abbreviato). ~55 dipendenti (fonte: GraydonGo / TransFirm, 2025). KVK 09026526, Ringoven 36 Arnhem, attiva dal 1971. ATTENZIONE LEGAME DI GRUPPO: da maggio 2025 le azioni sono state acquisite dal fondo Berk Partners e Peeze è confluita in Coffee Growth Group (direzione Myriam Lufting / Wouter Jansen van Velsen). Torrefazione B Corp, acquisto diretto di caffè verde all'origine.</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Guido van Staveren van Dijk</t>
+          <t>Myriam Lufting</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>Managing director / oprichter</t>
+          <t>Directeur</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr"/>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>b2b@moyeecoffee.com</t>
+          <t>info@peeze.nl</t>
         </is>
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>https://www.moyeecoffee.com/</t>
+          <t>https://peeze.nl/</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>Amsterdam (Noord-Holland)</t>
+          <t>Arnhem (Gelderland)</t>
         </is>
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>https://companyinfo.nl/organisatieprofiel/groothandel-in-koffie-thee-cacao-en-specerijen/moyee-nederland-b-v-amsterdam-61730556-000030807255</t>
+          <t>https://www.transfirm.nl/nl/organisatie/090265260000-koffiebranderij-g.-peeze-b.v.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>Neuteboom Koffiebranders B.V.</t>
+          <t>Moyee Nederland B.V.</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -26484,82 +26589,90 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Fatturato non pubblicato (bilancio abbreviato); n. dipendenti non pubblicato nelle fonti consultate. Capacità produttiva 10.000 t/anno su due impianti di torrefazione (fonte: Wikipedia NL / Mister Barish). Indicata tra le cinque maggiori torrefazioni olandesi (dato 2013). Aadijk 41, Almelo, attiva dal 1891. Specialista private label per l'Europa occidentale: probabile fascia alta del target o superiore — da verificare.</t>
+          <t>Fatturato non pubblicato (bilancio abbreviato); una fonte terza (rocketreach) riporta ~45 addetti — dato non ufficiale. KVK 61730556, Elementenstraat 10 Amsterdam, fondata 2014. Groothandel in koffie, thee, cacao en specerijen; modello 'FairChain' con torrefazione in Etiopia e importazione in NL. Micro/piccola impresa, verosimilmente sotto i 5 M€.</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Gilbert Willemsen</t>
+          <t>Guido van Staveren van Dijk</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Directeur / eigenaar</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>https://nl.linkedin.com/company/neuteboom-koffiebrander</t>
-        </is>
-      </c>
-      <c r="G65" s="3" t="inlineStr">
-        <is>
-          <t>n.d.</t>
+          <t>Managing director / oprichter</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr"/>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>b2b@moyeecoffee.com</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>https://neuteboom.nl/</t>
+          <t>https://www.moyeecoffee.com/</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
-          <t>Almelo (Overijssel)</t>
+          <t>Amsterdam (Noord-Holland)</t>
         </is>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>https://nl.wikipedia.org/wiki/Neuteboom_koffiebranders</t>
+          <t>https://companyinfo.nl/organisatieprofiel/groothandel-in-koffie-thee-cacao-en-specerijen/moyee-nederland-b-v-amsterdam-61730556-000030807255</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Origin Bridge (Barchem)</t>
+          <t>Neuteboom Koffiebranders B.V.</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>Caffè — import caffè verde</t>
+          <t>Caffè — torrefazione + import caffè verde</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Fatturato e n. dipendenti non pubblicati. KVK 70878315, P.IVA NL001587917B24 — la struttura del numero IVA indica una ditta individuale/eenmanszaak, NON una B.V.: la forma giuridica va verificata prima del contatto. Heidehoflaan 2B, Barchem. Importatore di caffè verde specialty dalla Colombia (micro-lotti e volumi da produzione) per torrefattori professionali in Europa. Micro-impresa, sotto i 5 M€, ma operatore EUDR in senso stretto.</t>
-        </is>
-      </c>
-      <c r="D66" s="5" t="inlineStr"/>
-      <c r="E66" s="5" t="inlineStr"/>
-      <c r="F66" s="5" t="inlineStr"/>
-      <c r="G66" s="6" t="inlineStr">
-        <is>
-          <t>info@bridgetoorigin.com</t>
+          <t>Fatturato non pubblicato (bilancio abbreviato); n. dipendenti non pubblicato nelle fonti consultate. Capacità produttiva 10.000 t/anno su due impianti di torrefazione (fonte: Wikipedia NL / Mister Barish). Indicata tra le cinque maggiori torrefazioni olandesi (dato 2013). Aadijk 41, Almelo, attiva dal 1891. Specialista private label per l'Europa occidentale: probabile fascia alta del target o superiore — da verificare.</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>Gilbert Willemsen</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>Directeur / eigenaar</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>https://nl.linkedin.com/company/neuteboom-koffiebrander</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>n.d.</t>
         </is>
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>https://originbridge.coffee/</t>
+          <t>https://neuteboom.nl/</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>Barchem, gem. Lochem (Gelderland)</t>
+          <t>Almelo (Overijssel)</t>
         </is>
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>https://originbridge.coffee/legal-information/</t>
+          <t>https://nl.wikipedia.org/wiki/Neuteboom_koffiebranders</t>
         </is>
       </c>
     </row>
@@ -26824,7 +26937,7 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>Fatturato ~4 M€ (fonte: MT/Sprout, articolo sulla fusione con Hands Off, 2025). KVK 57652066. SBI verwerking van cacao. Fabbrica bean-to-bar nel porto di Amsterdam, importa direttamente fave da Congo, Perù e Rep. Dominicana: operatore EUDR. Nota: sotto la fascia 5-40 M€, tenuta per copertura del segmento bean-to-bar.</t>
+          <t>Fatturato ~4 M€ (fonte: MT/Sprout, articolo sulla fusione con Hands Off, 2025). KVK 57652066. SBI verwerking van cacao. Fabbrica bean-to-bar nel porto di Amsterdam, importa direttamente fave da Congo, Perù e Rep. Dominicana: operatore EUDR. Nota: sotto la fascia 5-40 M€, tenuta per copertura del segmento bean-to-bar. Legame di gruppo: dal 2025 confluita in The Chocolate Impact Group (fusione con Hands Off; marchi Chocolatemakers, Hands Off, CLARO).</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
@@ -27155,8 +27268,16 @@
           <t>Fatturato non pubblicato. 54 dipendenti (fonte: oozo.nl, dati KVK, 2025). KVK 14002870. Costituita nel 1955. SBI vervaardiging van chocolade en suikerwerk. Sede Langs de Heij 11, Sittard. Per organico plausibilmente nella fascia 10-20 M€, ma il fatturato non è depositato pubblicamente.</t>
         </is>
       </c>
-      <c r="D79" s="3" t="inlineStr"/>
-      <c r="E79" s="3" t="inlineStr"/>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>Paul Diepstraten</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>Directeur</t>
+        </is>
+      </c>
       <c r="F79" s="3" t="inlineStr"/>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -28127,8 +28248,16 @@
           <t>Fatturato NON pubblicato (B.V. con bilancio abbreviato). Ca. 20 dipendenti (fonte Company.info / Drimble, profilo 2024-2025). KVK 30112737. Sede Oeverweg 3, 3417 XK Montfoort. Azienda familiare con oltre 30 anni di attività nella distribuzione di carne; lavora con macelli medi e grandi. GRUPPO: collegata a Slachterij van Kooten B.V. (Julianalaan 1, 3417 GJ Montfoort, oltre 110 anni di attività, e-mail info@vankooten.nl), che macella, diseossa, confeziona e distribuisce carne bovina, di vitello e ovina. Fascia dimensionale probabilmente sotto il target sui dipendenti, ma i volumi di commercio carne possono collocare il fatturato nella fascia bassa del range. Commodity EUDR: bovini.</t>
         </is>
       </c>
-      <c r="D99" s="3" t="inlineStr"/>
-      <c r="E99" s="3" t="inlineStr"/>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>Wilco van Kooten, Gerwin van Kooten</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>Directeuren / eigenaren</t>
+        </is>
+      </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
           <t>https://nl.linkedin.com/company/van-kooten-vleesgroothandel-b.v.</t>
@@ -28314,152 +28443,154 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId99"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F50" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F51" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F55" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F58" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F59" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F62" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F65" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F68" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F69" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F70" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F71" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F74" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F75" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F80" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F82" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F83" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F84" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F85" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F86" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F88" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F89" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F91" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G91" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F92" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F93" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G93" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F94" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G94" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F95" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G95" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G96" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F99" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G99" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F100" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F50" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F51" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F57" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F59" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F60" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F63" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F66" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F68" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F69" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F70" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F71" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F74" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F75" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F80" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F82" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F83" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F84" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F85" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F86" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F88" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F89" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F91" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G91" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F92" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F93" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G93" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F94" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G94" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F95" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G95" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G96" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F99" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G99" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F100" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId249"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -28743,12 +28874,12 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Dirk Busschop</t>
+          <t>Carlo Busschop</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>CEO / Managing Director</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -28941,8 +29072,16 @@
           <t>Fatturato 17.317.401 € - 40,6 FTE (fonte trendstop.knack.be / companyweb.be, bilancio depositato NBB 27-07-2024). 19a nel settore Meubelindustrie. N. impresa BE 0412.863.078. Costituita 29-12-1972, sede Menensesteenweg 40, 8940 Wervik. Produce divani, relax e boxspring (telai in legno, rivestimenti in pelle). Amministratori attuali secondo FinCheck: Jimmy Ollevier, Heidi Ollevier, Jacqueline Pauwels (ruolo di gedelegeerd bestuurder non pubblicato in modo univoco). Legame di gruppo: holding familiare Telinfra, stessa proprieta di Meubelfabriek Lievens NV. IN TARGET 10-20 M€.</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr"/>
-      <c r="E11" s="3" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Jimmy Ollevier</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Bestuurder</t>
+        </is>
+      </c>
       <c r="F11" s="3" t="inlineStr"/>
       <c r="G11" s="4" t="inlineStr">
         <is>
@@ -31345,9 +31484,21 @@
           <t>Fatturato 6.140.610 € (fonte: trendstop.levif.be, ultimo bilancio depositato NBB). N. impresa BE 0688.794.525. Cioccolatiere dal 1909, oltre 80 varietà di praline. Sotto la fascia ottimale ma nel range tollerabile 5-40 M€. Legame di gruppo: entità distinta da Bruyerre SA (BE 0431.703.151, distribuzione alimentare, ~179,6 M€ — quest'ultima fuori target).</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr"/>
-      <c r="E61" s="3" t="inlineStr"/>
-      <c r="F61" s="3" t="inlineStr"/>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Marc Delsemme</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Amministratore / co-proprietario (titolo statutario non confermato)</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>https://be.linkedin.com/company/bruyerre-chocolates</t>
+        </is>
+      </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
           <t>contact@bruyerre.eu</t>
@@ -31429,8 +31580,16 @@
           <t>Fatturato 11.404.101 € e 34,4 FTE (fonte: companyweb.be, ultimo bilancio depositato NBB, deposito 08-06-2026). N. impresa BE 0400.120.050. Sede Waaslandlaan 5, 9160 Lokeren. Produttore di cioccolato e caramelle (marchio Trefin). In pieno target 10-20 M€.</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr"/>
-      <c r="E63" s="3" t="inlineStr"/>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Bert Verriet</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
       <c r="F63" s="3" t="inlineStr"/>
       <c r="G63" s="4" t="inlineStr">
         <is>
@@ -31561,8 +31720,16 @@
           <t>33,2 FTE da ultimo bilancio depositato NBB (deposito 20-01-2026, cifra d'affari non pubblicata); fatturato ~6 M€ secondo la stampa economica (L'Avenir/RTBF, ~385 t di cioccolato/anno). N. impresa BE 0437.332.220. Sede Avenue Robert Schuman 172, 1401 Baulers (Nivelles). Prima cioccolateria belga certificata carbon neutral (2008); programma di sostenibilità cacao proprio 'Cocoa Act 4'. Taglia sotto la fascia ottimale, nel range tollerabile 5-40 M€.</t>
         </is>
       </c>
-      <c r="D66" s="5" t="inlineStr"/>
-      <c r="E66" s="5" t="inlineStr"/>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>Jean-Jacques de Gruben</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>Directeur général (CEO)</t>
+        </is>
+      </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
           <t>https://be.linkedin.com/company/dolfin-sa</t>
@@ -31657,8 +31824,16 @@
           <t>Fatturato 29.502.986 € (fonte: pappers.be/trendstop, bilancio NBB); dato più recente ~32 M€ con perdita netta 1,7 M€ nel 2024; 194 dipendenti. N. impresa BE 0416.169.689. Azienda di confine nella parte alta del range tollerabile (5-40 M€). Nota: nell'aprile 2026 rilevata da un consorzio vallone con piano di ristrutturazione (~70 licenziamenti su 170).</t>
         </is>
       </c>
-      <c r="D68" s="5" t="inlineStr"/>
-      <c r="E68" s="5" t="inlineStr"/>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>Sebastien Desclee</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
       <c r="F68" s="5" t="inlineStr"/>
       <c r="G68" s="5" t="inlineStr">
         <is>
@@ -32068,7 +32243,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>Hexpol Compounding BV</t>
+          <t>Hexpol Compounding SRL</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -32205,7 +32380,7 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>Mangimi/Soia — granaglie e semi per mangimi</t>
+          <t>Mangimi/Soia — mangimi per colombi (duivenvoer) a base di granaglie, semi e soia tostata</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
@@ -32305,8 +32480,16 @@
           <t>Fatturato 33.531.211 EUR (Trends Top/NBB, ultimo esercizio pubblicato); 11,5 FTE — taglia gonfiata dal costo materia prima; n. impresa BE 0455.669.079</t>
         </is>
       </c>
-      <c r="D82" s="5" t="inlineStr"/>
-      <c r="E82" s="5" t="inlineStr"/>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>Dirk Mellaerts</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>Bestuurder</t>
+        </is>
+      </c>
       <c r="F82" s="6" t="inlineStr">
         <is>
           <t>https://be.linkedin.com/company/voeders-mellaerts</t>
@@ -32393,7 +32576,7 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>Olio di palma — raffinazione oli e grassi vegetali/animali</t>
+          <t>Olio di palma + Bovini — raffinazione di grassi animali (sego bovino/suino) e oli vegetali (palma, cocco, mais): doppia esposizione EUDR</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
@@ -32802,7 +32985,7 @@
       <c r="F93" s="3" t="inlineStr"/>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>info@vdw-grossisteenviande.be</t>
+          <t>vdwgrossiste@skynet.be</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
@@ -32829,7 +33012,7 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>Bovini/Carne — ingrosso e sezionamento</t>
+          <t>Bovini/Carne — sezionamento e commercio di carne (ingrosso piu' negozio proprio e punti di ritiro)</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
@@ -33006,77 +33189,78 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId137"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId138"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F62" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F64" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F66" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F67" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F70" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F71" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F73" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F74" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F75" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F76" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F78" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F81" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F82" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F83" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F85" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G93" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G94" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F61" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F62" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F64" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F66" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F67" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F70" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F71" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F73" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F74" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F75" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F76" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F78" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F81" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F82" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F83" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F85" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G93" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G94" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId211"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -35852,7 +36036,7 @@
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>https://ulrich.at</t>
+          <t>https://www.ulrich-etiketten.at</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
@@ -36369,96 +36553,96 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>Confiserie Wenschitz GmbH</t>
+          <t>Cafe-Konditorei Fürst GmbH</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>Cacao/Cioccolato — praline e figure di cioccolato</t>
+          <t>Cacao/Cioccolato — praline e Mozartkugeln</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Ca. 30 dipendenti; totale attivo di bilancio 4,4 Mio. €, patrimonio netto 2,0 Mio. € (esercizio 2025, fonte firmenabc.at / firmenatlas.com). Fatturato non pubblicato: stimabile SOTTO la forbice target (probabile 5-8 Mio. €) - AZIENDA PICCOLA, segnalata come tale. Firmenbuch FN 273013s, LG Linz; UID ATU62268101. Maître Chocolatier con 'Pralinenwelt' ad Allhaming; produce praline, figure di cioccolato e marzapane in lavorazione artigianale assistita. Trasformatore di cacao/couverture = operatore o commerciante EUDR.</t>
+          <t>Ca. 65-70 dipendenti, di cui 35 nella nuova manifattura di Elsbethen; produzione ca. 3,7 milioni di Original Salzburger Mozartkugel all'anno; investimento di 'diversi milioni di euro' nel nuovo stabilimento aperto a febbraio 2024 (fonte SN.at / wko.at / salzburgwiki, 2024-2026). Fatturato non pubblicato - VERIFICARE. Firmenbuch FN 257955x, LG Salzburg; UID ATU61451413. Café-Konditorei fondata nel 1884, 5a generazione (Martin Fürst dal 2015), inventrice della Mozartkugel (1890); 4 punti vendita a Salisburgo. Grande utilizzatore di cioccolato/cacao = operatore o commerciante EUDR.</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Helmut Wenschitz</t>
+          <t>Martin Fürst</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>Geschäftsführender Gesellschafter</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr"/>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>office@wenschitz.at</t>
+          <t>versand@fuerst.cc</t>
         </is>
       </c>
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>https://www.wenschitz.at</t>
+          <t>https://www.original-mozartkugel.com</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>Allhaming, Alta Austria (Oberösterreich)</t>
+          <t>Salisburgo (Salzburg), produzione a Elsbethen</t>
         </is>
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>https://www.wenschitz.at/impressum/</t>
+          <t>https://www.original-mozartkugel.com/en/imprint</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>Fürst GmbH</t>
+          <t>Confiserie Wenschitz GmbH</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Cacao/Cioccolato — praline e Mozartkugeln</t>
+          <t>Cacao/Cioccolato — praline e figure di cioccolato</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Ca. 65-70 dipendenti, di cui 35 nella nuova manifattura di Elsbethen; produzione ca. 3,7 milioni di Original Salzburger Mozartkugel all'anno; investimento di 'diversi milioni di euro' nel nuovo stabilimento aperto a febbraio 2024 (fonte SN.at / wko.at / salzburgwiki, 2024-2026). Fatturato non pubblicato - VERIFICARE. Firmenbuch FN 257955x, LG Salzburg; UID ATU61451413. Café-Konditorei fondata nel 1884, 5a generazione (Martin Fürst dal 2015), inventrice della Mozartkugel (1890); 4 punti vendita a Salisburgo. Grande utilizzatore di cioccolato/cacao = operatore o commerciante EUDR.</t>
+          <t>Ca. 30 dipendenti; totale attivo di bilancio 4,4 Mio. €, patrimonio netto 2,0 Mio. € (esercizio 2025, fonte firmenabc.at / firmenatlas.com). Fatturato non pubblicato: stimabile SOTTO la forbice target (probabile 5-8 Mio. €) - AZIENDA PICCOLA, segnalata come tale. Firmenbuch FN 273013s, LG Linz; UID ATU62268101. Maître Chocolatier con 'Pralinenwelt' ad Allhaming; produce praline, figure di cioccolato e marzapane in lavorazione artigianale assistita. Trasformatore di cacao/couverture = operatore o commerciante EUDR.</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>Martin Fürst</t>
+          <t>Helmut Wenschitz</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Geschäftsführender Gesellschafter</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr"/>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>versand@fuerst.cc</t>
+          <t>office@wenschitz.at</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>https://www.original-mozartkugel.com</t>
+          <t>https://www.wenschitz.at</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>Salisburgo (Salzburg), produzione a Elsbethen</t>
+          <t>Allhaming, Alta Austria (Oberösterreich)</t>
         </is>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>https://www.original-mozartkugel.com/en/imprint</t>
+          <t>https://www.wenschitz.at/impressum/</t>
         </is>
       </c>
     </row>

--- a/MyEUDR_Lead_Mapping_v2.xlsx
+++ b/MyEUDR_Lead_Mapping_v2.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Italia'!$A$2:$J$97</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Germania'!$A$2:$J$99</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Finlandia'!$A$2:$J$86</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Danimarca'!$A$2:$J$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Danimarca'!$A$2:$J$86</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Svezia'!$A$2:$J$90</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Olanda'!$A$2:$J$100</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Belgio'!$A$2:$J$94</definedName>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>≈27,5M€ (2024) (CompanyReports/RegistroAziende)</t>
+          <t>≈27,5M€ (2024) (CompanyReports/RegistroAziende) /note: 'societa' del Gruppo Euromobil (marchi Euromobil, Zalf, Desiree) - decisione EUDR a livello di capogruppo.</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr"/>
@@ -5321,7 +5321,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Umsatz/MA n.d.; specialista bordi in legno</t>
+          <t>Umsatz/MA n.d.; specialista bordi in legno Controllata di INDUS Holding AG (gruppo quotato) dal 2016; dato dimensionale da integrare con fonte e anno.</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -8249,7 +8249,7 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>~100 dip. (Wikipedia/DDW); Umsatz n.d.; storica manifattura</t>
+          <t>~100 dip. (Wikipedia/DDW); Umsatz n.d.; storica manifattura Nota: socio di maggioranza Fintura Corporate Finance (Berlino) dal 2021, post-insolvenza in Eigenverwaltung.</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
@@ -8349,7 +8349,7 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>n.d. — NB: controllata del gruppo Halloren (verificare indipendenza)</t>
+          <t>n.d. — NB: controllata del gruppo Halloren (verificare indipendenza) Controllata di United Chocolate GmbH (Beherrschungs-/Gewinnabführungsvertrag) — non di Halloren.</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
@@ -8445,7 +8445,7 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Umsatz/MA n.d.; membrane in elastomero (~70 anni)</t>
+          <t>Umsatz/MA n.d.; membrane in elastomero (~70 anni) Controllata della Woco Gruppe (Woco Franz Josef Wolf Holding GmbH) — valutare la compliance a livello di capogruppo.</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
@@ -8733,7 +8733,7 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>~100 MA, Umsatz n.d.; maggior ricostruttore pneumatici indip. DE (borderline)</t>
+          <t>~100 MA, Umsatz n.d.; maggior ricostruttore pneumatici indip. DE (borderline) Controllata della Hörger Gruppe (WRZ Hörger GmbH u.; Co.; KG, Sontheim) dal 2017.</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
@@ -10086,7 +10086,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Liikevaihto 3,4 M€ (2024); 19 dip. (Asiakastieto)</t>
+          <t>Liikevaihto 3,4 M€ (2024); 19 dip. (Asiakastieto) Controllata di Auroora Yhtiöt Oyj (Tampere) — riqualificare il lead sulla capogruppo o scartare.</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -12626,7 +12626,7 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Liikevaihto ~16,2 M€ (2025), ~64 dip.</t>
+          <t>Liikevaihto ~16,2 M€ (2025), ~64 dip. /note: controllata dal gruppo belga Asteria Group (ex Tilgmann Group); compliance decisa a livello di capogruppo.</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
@@ -14196,7 +14196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J87"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -15251,7 +15251,7 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>110 dip. (proff.dk, CVR 22629115); codice NACE 310900 Fremstilling af andre møbler; fatturato non pubblicato. Stima ~15-25 M€ sulla base degli addetti: da verificare</t>
+          <t>110 dip. (proff.dk, CVR 22629115); codice NACE 310900 Fremstilling af andre møbler; fatturato non pubblicato. Stima ~15-25 M€ sulla base degli addetti: da verificare Controllata da KVIST HOLDING A/S, partecipata dal fondo Dansk Ejerkapital; fatturato non pubblicato (bilancio classe B).</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -15801,22 +15801,22 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Skagerak Denmark A/S</t>
+          <t>TIMBERMAN DENMARK A/S</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Legno/Arredo — arredi indoor/outdoor</t>
+          <t>Legno/Arredo — import parquet/pavimenti in legno</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Utile lordo 53,7 M DKK ≈ 7,2 M€ nel 2021 (39,2 M DKK nel 2020) / 40 dip. – 33 FTE dic. 2022 (estatistik.dk, CVR 28855990); fatturato non pubblicato. Stima ricavi ~15-22 M€: da verificare</t>
+          <t>22 dipendenti. Fatturato non pubblicato nelle fonti consultate; ultimo esercizio 2025: risultato ante imposte 43,07 M DKK (~5,8 M€), risultato netto 33,6 M DKK, patrimonio netto 72,4 M DKK — indicatori coerenti con una fascia di ricavi nel target. CVR 25776380, costituita 01.12.2000, sede Havnevej 11, 9560 Hadsund. Centralino +45 99 52 52 52. Codice NACE: commercio all'ingrosso di legno e materiali da costruzione. LEGAME DI GRUPPO: controllata da Timberman Holding ApS; nel CdA figurano Lovisa Märtha Maria Krantz e il presidente Fredrick John Sylva (azionariato nordico). Controllata del gruppo svedese quotato Volati AB dal dicembre 2024 (in precedenza Corticeira Amorim); Mogens Albaek Fisker resta direktor e comproprietario.</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Josef Theodor Kaiser</t>
+          <t>Mogens Albæk Fisker</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -15826,49 +15826,49 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/trip-trap-denmark-a-s</t>
+          <t>https://www.linkedin.com/company/timberman-denmark-a-s/</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>hello@skagerak.dk</t>
+          <t>timberman@timberman.dk</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>https://www.skagerak.dk/</t>
+          <t>https://www.timberman.dk/</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>Aalborg, Region Nordjylland</t>
+          <t>Hadsund (Mariagerfjord), Region Nordjylland</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>https://estatistik.dk/virksomhed/skagerak-denmark-as/28855990</t>
+          <t>https://www.proff.dk/firma/timberman-denmark-as/hadsund/t%C3%B8mmer-tr%C3%A6last-og-byggevarer-agentur-og-engros/GL4I5LI10LA</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>TIMBERMAN DENMARK A/S</t>
+          <t>VERMUND LARSEN A/S (VELA / VERMUND)</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Legno/Arredo — import parquet/pavimenti in legno</t>
+          <t>Legno/Arredo — sedute e tavoli (contract/healthcare)</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>22 dipendenti. Fatturato non pubblicato nelle fonti consultate; ultimo esercizio 2025: risultato ante imposte 43,07 M DKK (~5,8 M€), risultato netto 33,6 M DKK, patrimonio netto 72,4 M DKK — indicatori coerenti con una fascia di ricavi nel target. CVR 25776380, costituita 01.12.2000, sede Havnevej 11, 9560 Hadsund. Centralino +45 99 52 52 52. Codice NACE: commercio all'ingrosso di legno e materiali da costruzione. LEGAME DI GRUPPO: controllata da Timberman Holding ApS; nel CdA figurano Lovisa Märtha Maria Krantz e il presidente Fredrick John Sylva (azionariato nordico).</t>
+          <t>≈150 dip. in 5 paesi (2026, da.wikipedia/azienda); utile d'esercizio 17,1 M DKK nel bilancio 2025 (lasso.dk); fatturato non pubblicato. Azienda di confine verso l'alto (stima ricavi ~25-40 M€) ma indipendente, di proprietà della famiglia Larsen</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Mogens Albæk Fisker</t>
+          <t>Per Buus</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -15878,49 +15878,49 @@
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/timberman-denmark-a-s/</t>
+          <t>https://dk.linkedin.com/company/vela-vermund-larsen</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>timberman@timberman.dk</t>
+          <t>mail@vela.dk</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>https://www.timberman.dk/</t>
+          <t>https://vermund.eu/</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>Hadsund (Mariagerfjord), Region Nordjylland</t>
+          <t>Aalborg SV, Region Nordjylland</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>https://www.proff.dk/firma/timberman-denmark-as/hadsund/t%C3%B8mmer-tr%C3%A6last-og-byggevarer-agentur-og-engros/GL4I5LI10LA</t>
+          <t>https://lasso.dk/firmaer/52796628/vermund-larsen-as</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>VERMUND LARSEN A/S (VELA / VERMUND)</t>
+          <t>SKOVS KORN A/S. KORN- OG FODERSTOFAGENTUR</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Legno/Arredo — sedute e tavoli (contract/healthcare)</t>
+          <t>Mangimi/Soia — trading korn og foderstof</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>≈150 dip. in 5 paesi (2026, da.wikipedia/azienda); utile d'esercizio 17,1 M DKK nel bilancio 2025 (lasso.dk); fatturato non pubblicato. Azienda di confine verso l'alto (stima ricavi ~25-40 M€) ma indipendente, di proprietà della famiglia Larsen</t>
+          <t>8 dipendenti; bruttofortjeneste 12 M DKK (2025) ≈ 1,6 M€. Fatturato non pubblicato (societa' di agenzia/intermediazione: il volume intermediato e' molto superiore al margine iscritto a bilancio). Presidente CdA: Hans Ove Skov. Fonte: proff.dk / lasso.dk, dati 2025. CVR 10309905. TAGLIA SOTTO IL TARGET sui dati pubblicati. Broker internazionale di cereali, mangimi e semi oleosi dal 1987, con uffici in Danimarca, Polonia, Lituania e Germania. Sede: Stævnen 44 st. tv, 7100 Vejle, tel. +45 74 52 20 00.</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Per Buus</t>
+          <t>Christian Petersen</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -15928,84 +15928,84 @@
           <t>Direktør</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>https://dk.linkedin.com/company/vela-vermund-larsen</t>
-        </is>
-      </c>
+      <c r="F35" s="3" t="inlineStr"/>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>mail@vela.dk</t>
+          <t>kim@skovskorn.dk</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>https://vermund.eu/</t>
+          <t>http://skovskorn.dk/</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>Aalborg SV, Region Nordjylland</t>
+          <t>Vejle, Region Syddanmark</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>https://lasso.dk/firmaer/52796628/vermund-larsen-as</t>
+          <t>https://www.proff.dk/firma/skovs-korn-as.-korn-og-foderstofagentur/vejle/jordbrugsr%C3%A5varer-levende-dyr-tekstilr%C3%A5varer-og-indsatsvarer-agentur/064Z69I10OL ; email/sito da https://skovskorn.dk/kontakt/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>SKOVS KORN A/S. KORN- OG FODERSTOFAGENTUR</t>
+          <t>ALL CREATIVE A/S</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Mangimi/Soia — trading korn og foderstof</t>
+          <t>Carta/Packaging — imballaggi</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>8 dipendenti; bruttofortjeneste 12 M DKK (2025) ≈ 1,6 M€. Fatturato non pubblicato (societa' di agenzia/intermediazione: il volume intermediato e' molto superiore al margine iscritto a bilancio). Presidente CdA: Hans Ove Skov. Fonte: proff.dk / lasso.dk, dati 2025. CVR 10309905. TAGLIA SOTTO IL TARGET sui dati pubblicati. Broker internazionale di cereali, mangimi e semi oleosi dal 1987, con uffici in Danimarca, Polonia, Lituania e Germania. Sede: Stævnen 44 st. tv, 7100 Vejle, tel. +45 74 52 20 00.</t>
+          <t>11-50 dipendenti (LinkedIn/proff.dk). CVR 21124796, NACE 172100 (fremstilling af bølgepap, pap og emballage af papir og pap), sede Islevdalvej 214, unità anche a Vejle e Havndal. Fatturato NON pubblicato su fonti verificabili: dato di fatturato da confermare su CVR/regnskab. ATTENZIONE: probabile fascia sotto i 10 M€ target.</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Christian Petersen</t>
+          <t>Mette Juhl Christensen</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Direktør</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="inlineStr"/>
+          <t>Adm. direktør</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>https://dk.linkedin.com/company/allcreativedk</t>
+        </is>
+      </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>kim@skovskorn.dk</t>
+          <t>info@allcreative.dk</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>http://skovskorn.dk/</t>
+          <t>https://allcreative.dk/</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>Vejle, Region Syddanmark</t>
+          <t>Rødovre (Hovedstaden)</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>https://www.proff.dk/firma/skovs-korn-as.-korn-og-foderstofagentur/vejle/jordbrugsr%C3%A5varer-levende-dyr-tekstilr%C3%A5varer-og-indsatsvarer-agentur/064Z69I10OL ; email/sito da https://skovskorn.dk/kontakt/</t>
+          <t>https://www.proff.dk/firma/all-creative-as/r%C3%B8dovre/papir-og-papirprodukter-produktion/GSG8C7I10K1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>ALL CREATIVE A/S</t>
+          <t>BOXEN EMBALLAGE A/S</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -16015,197 +16015,193 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>11-50 dipendenti (LinkedIn/proff.dk). CVR 21124796, NACE 172100 (fremstilling af bølgepap, pap og emballage af papir og pap), sede Islevdalvej 214, unità anche a Vejle e Havndal. Fatturato NON pubblicato su fonti verificabili: dato di fatturato da confermare su CVR/regnskab. ATTENZIONE: probabile fascia sotto i 10 M€ target.</t>
+          <t>31 dipendenti; bruttofortjeneste (margine lordo) 17 mio DKK nel 2024 (~2,3 M€ di margine lordo, cambio 7,46). CVR 31155975, NACE 172100, Bøgildsmindevej 3. Fatturato non pubblicato (classe contabile B): stima fascia 5-15 M€ da confermare. Gruppo di 3 società, capogruppo CRHJ Holding ApS (controllo familiare, indipendente).</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Mette Juhl Christensen</t>
+          <t>Christian Rune Passer Jørgensen</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Adm. direktør</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>https://dk.linkedin.com/company/allcreativedk</t>
-        </is>
-      </c>
+          <t>Administrerende direktør</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr"/>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>info@allcreative.dk</t>
+          <t>info@boxenemballage.dk</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>https://allcreative.dk/</t>
+          <t>https://www.boxenemballage.dk/</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>Rødovre (Hovedstaden)</t>
+          <t>Nørresundby (Nordjylland)</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>https://www.proff.dk/firma/all-creative-as/r%C3%B8dovre/papir-og-papirprodukter-produktion/GSG8C7I10K1</t>
+          <t>https://www.proff.dk/firma/boxen-emballage-as/n%C3%B8rresundby/producenter/GQAW39I016D</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>BOXEN EMBALLAGE A/S</t>
+          <t>BUCHS A/S</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Carta/Packaging — imballaggi</t>
+          <t>Carta/Packaging — stampa</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>31 dipendenti; bruttofortjeneste (margine lordo) 17 mio DKK nel 2024 (~2,3 M€ di margine lordo, cambio 7,46). CVR 31155975, NACE 172100, Bøgildsmindevej 3. Fatturato non pubblicato (classe contabile B): stima fascia 5-15 M€ da confermare. Gruppo di 3 società, capogruppo CRHJ Holding ApS (controllo familiare, indipendente).</t>
+          <t>27 specialisti in Buchs A/S; il gruppo (Buchs + Buchs Labels, Randers/Silkeborg/Ho Chi Minh City) si avvicina a 100 dipendenti. CVR 29845646. Produzione interna oggi all'80% imballaggi; dal 2023 nuova tipografia di etichette (Buchs Labels A/S). Fatturato non pubblicato: DA VERIFICARE su regnskab; fascia stimata 5-15 M€ a livello di gruppo.</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Christian Rune Passer Jørgensen</t>
+          <t>Henrik Olesen</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>Administrerende direktør</t>
-        </is>
-      </c>
-      <c r="F38" s="5" t="inlineStr"/>
+          <t>Adm. direktør</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>https://dk.linkedin.com/company/buchs-a-s</t>
+        </is>
+      </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>info@boxenemballage.dk</t>
+          <t>buchs@buchs.dk</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>https://www.boxenemballage.dk/</t>
+          <t>https://buchs.dk/</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>Nørresundby (Nordjylland)</t>
+          <t>Randers SV (Midtjylland)</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>https://www.proff.dk/firma/boxen-emballage-as/n%C3%B8rresundby/producenter/GQAW39I016D</t>
+          <t>https://www.proff.dk/firma/buchs-as/randers-sv/trykeritjenester/GKN0O3I07QV</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>BUCHS A/S</t>
+          <t>COLOR LABEL A/S</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Carta/Packaging — stampa</t>
+          <t>Carta/Packaging — etichette</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>27 specialisti in Buchs A/S; il gruppo (Buchs + Buchs Labels, Randers/Silkeborg/Ho Chi Minh City) si avvicina a 100 dipendenti. CVR 29845646. Produzione interna oggi all'80% imballaggi; dal 2023 nuova tipografia di etichette (Buchs Labels A/S). Fatturato non pubblicato: DA VERIFICARE su regnskab; fascia stimata 5-15 M€ a livello di gruppo.</t>
+          <t>13 dipendenti; bruttofortjeneste 14,756 mio DKK nel 2024 (~2,0 M€ di margine lordo), risultato ante imposte 5,169 mio DKK. CVR 15136901, Vejlbjergvej 14, fondata 1991. Produzione di etichette autoadesive. SOTTO SOGLIA: fatturato stimato ben sotto i 10 M€, probabilmente vicino o sotto i 5 M€. Capogruppo Color Label Holding ApS.</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Henrik Olesen</t>
+          <t>Erik Grønning</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Adm. direktør</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>https://dk.linkedin.com/company/buchs-a-s</t>
-        </is>
-      </c>
-      <c r="G39" s="4" t="inlineStr">
-        <is>
-          <t>buchs@buchs.dk</t>
+          <t>Adm. direktør (fondatore)</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr"/>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>n.d.</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>https://buchs.dk/</t>
+          <t>https://www.colorlabel.dk/</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>Randers SV (Midtjylland)</t>
+          <t>Risskov, Aarhus (Midtjylland)</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>https://www.proff.dk/firma/buchs-as/randers-sv/trykeritjenester/GKN0O3I07QV</t>
+          <t>https://www.proff.dk/firma/color-label-as/risskov/b%C3%B8ger-aviser-og-blader-engros/090FPHI10MF</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>COLOR LABEL A/S</t>
+          <t>EMBALLAGEFABRIKKEN THY PAP</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Carta/Packaging — etichette</t>
+          <t>Carta/Packaging — imballaggi</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>13 dipendenti; bruttofortjeneste 14,756 mio DKK nel 2024 (~2,0 M€ di margine lordo), risultato ante imposte 5,169 mio DKK. CVR 15136901, Vejlbjergvej 14, fondata 1991. Produzione di etichette autoadesive. SOTTO SOGLIA: fatturato stimato ben sotto i 10 M€, probabilmente vicino o sotto i 5 M€. Capogruppo Color Label Holding ApS.</t>
+          <t>n.d. - nessun dato di fatturato o addetti reperito su fonte verificabile. Produttore di imballaggi in cartone e astucci con oltre 25 anni di attività, lavora anche come terzista per tipografie; sede Industrivej 19 B, 7700 Thisted. DA VERIFICARE su CVR: ragione sociale esatta, dimensione e referente. CVR 25352769 (THY PAP, enkeltmandsvirksomhed).; Fatturato e addetti non pubblicati per forma giuridica; micro-impresa AMPIAMENTE SOTTO SOGLIA rispetto al target 5-40 M€.</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Erik Grønning</t>
+          <t>Carsten Boye Steen</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>Adm. direktør (fondatore)</t>
+          <t>Indehaver (enkeltmandsvirksomhed)</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr"/>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>n.d.</t>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>thy-pap@mail.dk</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>https://www.colorlabel.dk/</t>
+          <t>https://thy-pap.dk/</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>Risskov, Aarhus (Midtjylland)</t>
+          <t>Thisted (Nordjylland)</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>https://www.proff.dk/firma/color-label-as/risskov/b%C3%B8ger-aviser-og-blader-engros/090FPHI10MF</t>
+          <t>https://thy-pap.dk/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>EMBALLAGEFABRIKKEN THY PAP</t>
+          <t>H. EMBALLAGE ApS</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -16215,141 +16211,145 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>n.d. - nessun dato di fatturato o addetti reperito su fonte verificabile. Produttore di imballaggi in cartone e astucci con oltre 25 anni di attività, lavora anche come terzista per tipografie; sede Industrivej 19 B, 7700 Thisted. DA VERIFICARE su CVR: ragione sociale esatta, dimensione e referente.</t>
+          <t>21 dipendenti; ricavi/margine lordo dichiarati 9,211 mio DKK (~1,2 M€). CVR 38528742, NACE 172100, Højrupvej 11. SOTTO SOGLIA: ampiamente al di sotto della fascia minima 5 M€ - lead marginale, incluso solo perché già segnalato come lead parziale da verificare.</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Carsten Boye Steen</t>
+          <t>Jesper Hildebrandt Christensen</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Indehaver (enkeltmandsvirksomhed)</t>
+          <t>Adm. direktør og indehaver</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr"/>
-      <c r="G41" s="4" t="inlineStr">
-        <is>
-          <t>thy-pap@mail.dk</t>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>n.d.</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>https://thy-pap.dk/</t>
+          <t>https://h-emballage.dk/</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>Thisted (Nordjylland)</t>
+          <t>Glamsbjerg, Assens (Syddanmark)</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>https://thy-pap.dk/</t>
+          <t>https://www.proff.dk/firma/h.-emballage-aps/glamsbjerg/papir-og-papirprodukter/GWNSLZI0ZDH</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>H. EMBALLAGE ApS</t>
+          <t>IKAST ETIKET A/S</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Carta/Packaging — imballaggi</t>
+          <t>Carta/Packaging — etichette</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>21 dipendenti; ricavi/margine lordo dichiarati 9,211 mio DKK (~1,2 M€). CVR 38528742, NACE 172100, Højrupvej 11. SOTTO SOGLIA: ampiamente al di sotto della fascia minima 5 M€ - lead marginale, incluso solo perché già segnalato come lead parziale da verificare.</t>
+          <t>12 dipendenti; risultato netto 7,62 mio DKK nell'ultimo bilancio (prec. 8,3 mio DKK), patrimonio netto 10,9 mio DKK. CVR 10402980, Neptunvej 6, fondata 1986. SOTTO SOGLIA: fatturato non pubblicato ma dimensione ampiamente sotto i 5 M€ - lead piccolo. Consiglio amministrazione: Benny Nørmark Nyborg, Ulrik Lauritsen, Henning Hausted (nessun adm. direktør pubblicato).</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Jesper Hildebrandt Christensen</t>
+          <t>Ulrik Lauritsen</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>Adm. direktør og indehaver</t>
+          <t>Direktør</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr"/>
-      <c r="G42" s="5" t="inlineStr">
-        <is>
-          <t>n.d.</t>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>info@ikastetiket.dk</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>https://h-emballage.dk/</t>
+          <t>https://www.ikastetiket.dk/</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>Glamsbjerg, Assens (Syddanmark)</t>
+          <t>Ikast, Ikast-Brande (Midtjylland)</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>https://www.proff.dk/firma/h.-emballage-aps/glamsbjerg/papir-og-papirprodukter/GWNSLZI0ZDH</t>
+          <t>https://www.proff.dk/firma/ikast-etiket-as/ikast/engroshandel-annet/GJF022I10N6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>IKAST ETIKET A/S</t>
+          <t>JOHNSEN PRINT &amp; DIGITAL MEDIA A/S (già Johnsen Graphic Solutions A/S)</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Carta/Packaging — etichette</t>
+          <t>Carta/Packaging — stampa</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>12 dipendenti; risultato netto 7,62 mio DKK nell'ultimo bilancio (prec. 8,3 mio DKK), patrimonio netto 10,9 mio DKK. CVR 10402980, Neptunvej 6, fondata 1986. SOTTO SOGLIA: fatturato non pubblicato ma dimensione ampiamente sotto i 5 M€ - lead piccolo. Consiglio amministrazione: Benny Nørmark Nyborg, Ulrik Lauritsen, Henning Hausted (nessun adm. direktør pubblicato).</t>
+          <t>92 dipendenti. CVR 18624141, Bakkehegnet 3, fondata 1995. Capogruppo Johnsen + Holding A/S (controllo familiare danese, indipendente). Fatturato non pubblicato su fonte verificabile: con 92 addetti nel settore grafico la fascia stimata è 10-20 M€, DA CONFERMARE su regnskab. NB: sotto la stessa CVR compare anche la denominazione Johnsen Print &amp; Digital Media A/S.</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Ulrik Lauritsen</t>
+          <t>Steen Johnsen</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Direktør</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr"/>
+          <t>Adm. direktør</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>https://dk.linkedin.com/company/johnsen-offset-a-s</t>
+        </is>
+      </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>info@ikastetiket.dk</t>
+          <t>info@johnsen.dk</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>https://www.ikastetiket.dk/</t>
+          <t>https://johnsen.dk/</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>Ikast, Ikast-Brande (Midtjylland)</t>
+          <t>Grenaa, Norddjurs (Midtjylland)</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>https://www.proff.dk/firma/ikast-etiket-as/ikast/engroshandel-annet/GJF022I10N6</t>
+          <t>https://www.proff.dk/firma/johnsen-graphic-solutions-as/grenaa/trykeritjenester/0B36H9I07QV</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>JOHNSEN PRINT &amp; DIGITAL MEDIA A/S (già Johnsen Graphic Solutions A/S)</t>
+          <t>KAILOW A/S</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -16359,49 +16359,45 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>92 dipendenti. CVR 18624141, Bakkehegnet 3, fondata 1995. Capogruppo Johnsen + Holding A/S (controllo familiare danese, indipendente). Fatturato non pubblicato su fonte verificabile: con 92 addetti nel settore grafico la fascia stimata è 10-20 M€, DA CONFERMARE su regnskab. NB: sotto la stessa CVR compare anche la denominazione Johnsen Print &amp; Digital Media A/S.</t>
+          <t>28 dipendenti; bruttofortjeneste 18 mio DKK nel 2024 (~2,4 M€ di margine lordo). CVR 15945672, Floras Allé 11, fondata 1992. Capogruppo KAILOW GRUPPEN A/S (indipendente, familiare). Fatturato non pubblicato: stima fascia 5-10 M€ - AZIENDA DI CONFINE, al di sotto del target 10-20 M€.</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Steen Johnsen</t>
+          <t>Per Puch Holm-Larsen</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>Adm. direktør</t>
-        </is>
-      </c>
-      <c r="F44" s="6" t="inlineStr">
-        <is>
-          <t>https://dk.linkedin.com/company/johnsen-offset-a-s</t>
-        </is>
-      </c>
+          <t>Adm. direktør (dal 01.04.2025)</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr"/>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>info@johnsen.dk</t>
+          <t>kundeservice@kailow.dk</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>https://johnsen.dk/</t>
+          <t>https://www.kailow.dk/</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>Grenaa, Norddjurs (Midtjylland)</t>
+          <t>Vanløse, København (Hovedstaden)</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>https://www.proff.dk/firma/johnsen-graphic-solutions-as/grenaa/trykeritjenester/0B36H9I07QV</t>
+          <t>https://www.proff.dk/firma/kailow-as/vanl%C3%B8se/trykeritjenester/09HRRCI07QV</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>KAILOW A/S</t>
+          <t>KLS PUREPRINT A/S</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -16411,97 +16407,97 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>28 dipendenti; bruttofortjeneste 18 mio DKK nel 2024 (~2,4 M€ di margine lordo). CVR 15945672, Floras Allé 11, fondata 1992. Capogruppo KAILOW GRUPPEN A/S (indipendente, familiare). Fatturato non pubblicato: stima fascia 5-10 M€ - AZIENDA DI CONFINE, al di sotto del target 10-20 M€.</t>
+          <t>41 dipendenti. CVR 13918783, Jernholmen 42A. Tipografia certificata Cradle2Cradle, storica azienda familiare (ex K. Larsen &amp; Søn). LEGAME DI GRUPPO: capogruppo F. E. BORDING A/S (gruppo grafico danese quotato) - la decisione di acquisto potrebbe essere centralizzata. Fatturato non pubblicato a livello di controllata. Controllata (oggi integralmente) di F.; E.; BORDING A/S dopo il riacquisto della quota di Knud Erik Larsen a fine 2024.; Lead da valutare a livello di capogruppo Bording.</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Per Puch Holm-Larsen</t>
+          <t>Janni Toft Nielsen</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Adm. direktør (dal 01.04.2025)</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="inlineStr"/>
+          <t>Adm. direktør</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>https://dk.linkedin.com/company/klspureprint</t>
+        </is>
+      </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>kundeservice@kailow.dk</t>
+          <t>kls@kls.dk</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>https://www.kailow.dk/</t>
+          <t>https://klspureprint.dk/</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>Vanløse, København (Hovedstaden)</t>
+          <t>Hvidovre (Hovedstaden)</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>https://www.proff.dk/firma/kailow-as/vanl%C3%B8se/trykeritjenester/09HRRCI07QV</t>
+          <t>https://www.proff.dk/firma/kls-pureprint-as/hvidovre/trykeritjenester/GJRDH3I07QV</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>KLS PUREPRINT A/S</t>
+          <t>MC EMBALLAGE A/S</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Carta/Packaging — stampa</t>
+          <t>Carta/Packaging — imballaggi</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>41 dipendenti. CVR 13918783, Jernholmen 42A. Tipografia certificata Cradle2Cradle, storica azienda familiare (ex K. Larsen &amp; Søn). LEGAME DI GRUPPO: capogruppo F. E. BORDING A/S (gruppo grafico danese quotato) - la decisione di acquisto potrebbe essere centralizzata. Fatturato non pubblicato a livello di controllata.</t>
+          <t>79-87 dipendenti; bruttofortjeneste 110 mio DKK (~14,7 M€ di margine lordo). CVR 10887194, Delta 3, fondata 1987, engroshandel di imballaggi (incl. carta/cartone). Azienda a proprietà dei dipendenti (medarbejdereje), indipendente. AZIENDA DI CONFINE: essendo distributore, il fatturato è verosimilmente &gt;40 M€ - verificare regnskab prima di classificarla nel target.</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Janni Toft Nielsen</t>
+          <t>Peder Kristian Eriksen</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>Adm. direktør</t>
-        </is>
-      </c>
-      <c r="F46" s="6" t="inlineStr">
-        <is>
-          <t>https://dk.linkedin.com/company/klspureprint</t>
-        </is>
-      </c>
+          <t>Direktør</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr"/>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>kls@kls.dk</t>
+          <t>mcemballage@mcemballage.dk</t>
         </is>
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>https://klspureprint.dk/</t>
+          <t>https://www.mcemballage.dk/</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>Hvidovre (Hovedstaden)</t>
+          <t>Hinnerup, Favrskov (Midtjylland)</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>https://www.proff.dk/firma/kls-pureprint-as/hvidovre/trykeritjenester/GJRDH3I07QV</t>
+          <t>https://www.proff.dk/firma/mc-emballage-as/hinnerup/grossister/06HCM2I10NS</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>MC EMBALLAGE A/S</t>
+          <t>SCANLUX PACKAGING A/S</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -16511,164 +16507,164 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>79-87 dipendenti; bruttofortjeneste 110 mio DKK (~14,7 M€ di margine lordo). CVR 10887194, Delta 3, fondata 1987, engroshandel di imballaggi (incl. carta/cartone). Azienda a proprietà dei dipendenti (medarbejdereje), indipendente. AZIENDA DI CONFINE: essendo distributore, il fatturato è verosimilmente &gt;40 M€ - verificare regnskab prima di classificarla nel target.</t>
+          <t>28-38 dipendenti (fonti divergenti); bruttofortjeneste 22,0 mio DKK 2023 vs 19,4 mio DKK 2022 (~2,9 M€ di margine lordo). CVR 71051218, Kratbjerg 308, attività registrata come engroshandel/imballaggi. Capogruppo Kornelius II ApS. DA VERIFICARE: quota effettiva di imballaggi in carta/cartone rispetto ad altri materiali; fatturato non pubblicato.</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Peder Kristian Eriksen</t>
+          <t>Jan Kornelius Pedersen</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Direktør</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="inlineStr"/>
+          <t>Administrerende direktør</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/scan-lux-packaging-a-s</t>
+        </is>
+      </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>mcemballage@mcemballage.dk</t>
+          <t>scanlux@scanlux.com</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>https://www.mcemballage.dk/</t>
+          <t>https://scanlux-packaging.com/</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>Hinnerup, Favrskov (Midtjylland)</t>
+          <t>Fredensborg (Hovedstaden)</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>https://www.proff.dk/firma/mc-emballage-as/hinnerup/grossister/06HCM2I10NS</t>
+          <t>https://www.proff.dk/firma/scanlux-packaging-as/fredensborg/engroshandel-annet/16AVGYI10N6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>SCANLUX PACKAGING A/S</t>
+          <t>SKJERN PAPER A/S (già Skjern Papirfabrik A/S)</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Carta/Packaging — imballaggi</t>
+          <t>Carta/Packaging — cartiera</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>28-38 dipendenti (fonti divergenti); bruttofortjeneste 22,0 mio DKK 2023 vs 19,4 mio DKK 2022 (~2,9 M€ di margine lordo). CVR 71051218, Kratbjerg 308, attività registrata come engroshandel/imballaggi. Capogruppo Kornelius II ApS. DA VERIFICARE: quota effettiva di imballaggi in carta/cartone rispetto ad altri materiali; fatturato non pubblicato.</t>
+          <t>75 dipendenti; produzione ~70.000 t/anno di carta (dato 2021). Proprietà Buur Invest A/S + dirigenti operativi (indipendente danese dal 2005). Fatturato non reperito su fonte verificabile: con questi volumi è AZIENDA DI CONFINE, plausibilmente sopra i 40 M€ - verificare regnskab prima del contatto.</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Jan Kornelius Pedersen</t>
+          <t>Nikolaj Bjerre Thybo</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>Administrerende direktør</t>
+          <t>Administrerende direktør (dal 2020)</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/scan-lux-packaging-a-s</t>
+          <t>https://dk.linkedin.com/company/skjern-papirfabrik-a-s</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>scanlux@scanlux.com</t>
+          <t>contact@skjernpaper.com</t>
         </is>
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>https://scanlux-packaging.com/</t>
+          <t>https://www.skjernpaper.com/</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>Fredensborg (Hovedstaden)</t>
+          <t>Skjern, Ringkøbing-Skjern (Midtjylland)</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>https://www.proff.dk/firma/scanlux-packaging-as/fredensborg/engroshandel-annet/16AVGYI10N6</t>
+          <t>https://energiforskning.dk/medlemmer/skjern-papirfabrik-as</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>SKJERN PAPER A/S (già Skjern Papirfabrik A/S)</t>
+          <t>STIBO COMPLETE A/S (già Rosendahls A/S - Print Design Media)</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Carta/Packaging — cartiera</t>
+          <t>Carta/Packaging — stampa</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>75 dipendenti; produzione ~70.000 t/anno di carta (dato 2021). Proprietà Buur Invest A/S + dirigenti operativi (indipendente danese dal 2005). Fatturato non reperito su fonte verificabile: con questi volumi è AZIENDA DI CONFINE, plausibilmente sopra i 40 M€ - verificare regnskab prima del contatto.</t>
+          <t>150 dipendenti; fatturato ~200 mio DKK (~26,8 M€, cambio 7,46). CVR 37120928, Oddesundvej 1. AZIENDA DI CONFINE: sopra la fascia 10-20 M€ ma dentro il tollerabile 5-40 M€. LEGAME DI GRUPPO: ex Rosendahls, acquisita e ridenominata Stibo Complete A/S nel 2022 (gruppo Stibo, danese, fondazione).</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Nikolaj Bjerre Thybo</t>
+          <t>Søren Schønberg Henriksen</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Administrerende direktør (dal 2020)</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>https://dk.linkedin.com/company/skjern-papirfabrik-a-s</t>
-        </is>
-      </c>
+          <t>Administrerende direktør</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr"/>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>contact@skjernpaper.com</t>
+          <t>info@stibocomplete.com</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>https://www.skjernpaper.com/</t>
+          <t>https://stibocomplete.com/</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>Skjern, Ringkøbing-Skjern (Midtjylland)</t>
+          <t>Esbjerg N (Syddanmark)</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>https://energiforskning.dk/medlemmer/skjern-papirfabrik-as</t>
+          <t>https://www.proff.dk/firma/rosendahls-as-print-design-media/esbjerg-n/trykeritjenester/GKF0WAI07QV/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>STIBO COMPLETE A/S (già Rosendahls A/S - Print Design Media)</t>
+          <t>STOK EMBALLAGE K/S</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Carta/Packaging — stampa</t>
+          <t>Carta/Packaging — imballaggi</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>150 dipendenti; fatturato ~200 mio DKK (~26,8 M€, cambio 7,46). CVR 37120928, Oddesundvej 1. AZIENDA DI CONFINE: sopra la fascia 10-20 M€ ma dentro il tollerabile 5-40 M€. LEGAME DI GRUPPO: ex Rosendahls, acquisita e ridenominata Stibo Complete A/S nel 2022 (gruppo Stibo, danese, fondazione).</t>
+          <t>100-200 dipendenti complessivi (62 a Langeskov, 10 a Vejle); bruttofortjeneste 146 mio DKK nel 2024 (~19,6 M€ di solo margine lordo). CVR 16427284, NACE 172100, Erik Stoks Allé 4. Capogruppo STOK Denmark ApS. AZIENDA DI CONFINE / SOPRA FASCIA: il fatturato è verosimilmente &gt;50 M€ - da verificare prima del contatto, potenzialmente da escludere.</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Søren Schønberg Henriksen</t>
+          <t>Martin Frederiksen</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -16679,144 +16675,148 @@
       <c r="F50" s="5" t="inlineStr"/>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>info@stibocomplete.com</t>
+          <t>info@stok.dk</t>
         </is>
       </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>https://stibocomplete.com/</t>
+          <t>https://www.stok.dk/</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>Esbjerg N (Syddanmark)</t>
+          <t>Langeskov, Kerteminde (Syddanmark); stabilimento bølgepap a Middelfart</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>https://www.proff.dk/firma/rosendahls-as-print-design-media/esbjerg-n/trykeritjenester/GKF0WAI07QV/</t>
+          <t>https://www.proff.dk/firma/stok-emballage-ks/langeskov/papir-og-papirprodukter/09S3DGI0ZDH</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>STOK EMBALLAGE K/S</t>
+          <t>CAFÉU DENMARK ApS</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Carta/Packaging — imballaggi</t>
+          <t>Caffè — engros B2B</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>100-200 dipendenti complessivi (62 a Langeskov, 10 a Vejle); bruttofortjeneste 146 mio DKK nel 2024 (~19,6 M€ di solo margine lordo). CVR 16427284, NACE 172100, Erik Stoks Allé 4. Capogruppo STOK Denmark ApS. AZIENDA DI CONFINE / SOPRA FASCIA: il fatturato è verosimilmente &gt;50 M€ - da verificare prima del contatto, potenzialmente da escludere.</t>
+          <t>Bruttofortjeneste 7,3 mio. DKK nell'ultimo bilancio disponibile (+421% in 5 anni); dipendenti non pubblicati. Capogruppo: STEFFAN TOBIESEN HOLDING ApS. Fonte: food-supply.dk / proff.dk. SOTTO IL TARGET. · CVR 33243537</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Martin Frederiksen</t>
+          <t>Steffan Nørgård Tobiesen</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Administrerende direktør</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="inlineStr"/>
+          <t>Direktør (fondatore)</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>https://dk.linkedin.com/company/caf%C3%A9u</t>
+        </is>
+      </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>info@stok.dk</t>
+          <t>info@cafeu.dk</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>https://www.stok.dk/</t>
+          <t>https://cafeu.dk/</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>Langeskov, Kerteminde (Syddanmark); stabilimento bølgepap a Middelfart</t>
+          <t>Esbjerg N (Storstrømsvej 42, 6715), Regione Syddanmark</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>https://www.proff.dk/firma/stok-emballage-ks/langeskov/papir-og-papirprodukter/09S3DGI0ZDH</t>
+          <t>https://www.proff.dk/firma/caf%C3%A9u-denmark-aps/esbjerg-n/kaffe-og-te-agentur-og-engros/GT4AIYI0Z8T</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>CAFÉU DENMARK ApS</t>
+          <t>Copenhagen Coffee Lab ApS</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>Caffè — engros B2B</t>
+          <t>Caffè — torrefazione/engros B2B</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>Bruttofortjeneste 7,3 mio. DKK nell'ultimo bilancio disponibile (+421% in 5 anni); dipendenti non pubblicati. Capogruppo: STEFFAN TOBIESEN HOLDING ApS. Fonte: food-supply.dk / proff.dk. SOTTO IL TARGET. · CVR 33243537</t>
+          <t>16 dipendenti; risultato ante imposte ~4,7 mio. DKK es. 2024; utile 2023 1,3 mio. DKK (2 mio. DKK nel 2022). Fatturato non pubblicato. Fonte: proff.dk. SOTTO IL TARGET. · CVR 40207929 Capogruppo Copenhagen Coffee Lab Holding ApS (gruppo di 6 societa'); 70% Steen Skallebæk e Ole Kristoffersen, 30% i fondatori Allan Krogsgaard Nielsen e Jacob Karlsen.; Controllo danese, non estero.; Referente Allan Krogsgaard Nielsen (direktør) confermato.</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Steffan Nørgård Tobiesen</t>
+          <t>Allan Krogsgaard Nielsen</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>Direktør (fondatore)</t>
+          <t>Direktør</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/company/caf%C3%A9u</t>
+          <t>https://www.linkedin.com/company/cphcoffeelab/</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>info@cafeu.dk</t>
+          <t>webshop@cphcoffeelab.com</t>
         </is>
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>https://cafeu.dk/</t>
+          <t>https://copenhagencoffeelab.com/en</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>Esbjerg N (Storstrømsvej 42, 6715), Regione Syddanmark</t>
+          <t>København SV (Bådehavnsgade 44F, 2450), Regione Hovedstaden</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>https://www.proff.dk/firma/caf%C3%A9u-denmark-aps/esbjerg-n/kaffe-og-te-agentur-og-engros/GT4AIYI0Z8T</t>
+          <t>https://www.proff.dk/firma/copenhagen-coffee-lab-aps/k%C3%B8benhavn-sv/producenter/GXVBRXI016D</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen Coffee Lab ApS</t>
+          <t>DANSK KAFFE ApS</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Caffè — torrefazione/engros B2B</t>
+          <t>Caffè — import/export caffè verde</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>16 dipendenti; risultato ante imposte ~4,7 mio. DKK es. 2024; utile 2023 1,3 mio. DKK (2 mio. DKK nel 2022). Fatturato non pubblicato. Fonte: proff.dk. SOTTO IL TARGET. · CVR 40207929</t>
+          <t>Micro-impresa: capitale sociale 80 t.DKK; dipendenti e fatturato non pubblicati nelle fonti consultate. Codice NACE 463700 (engros di caffè, tè, cacao e spezie); oggetto sociale: import/export di caffè. Fonte: proff.dk. SOTTO IL TARGET ma importatore puro. · CVR 25081544 Capogruppo KAFFEA ApS (gruppo di 2 societa'), societa' costituita il 27.11.2013.; Micro-impresa MOLTO SOTTO SOGLIA rispetto al target 5-40 M€.</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Allan Krogsgaard Nielsen</t>
+          <t>Jens Erik Nielsen</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -16824,432 +16824,432 @@
           <t>Direktør</t>
         </is>
       </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/cphcoffeelab/</t>
-        </is>
-      </c>
-      <c r="G53" s="4" t="inlineStr">
-        <is>
-          <t>webshop@cphcoffeelab.com</t>
-        </is>
-      </c>
-      <c r="H53" s="4" t="inlineStr">
-        <is>
-          <t>https://copenhagencoffeelab.com/en</t>
-        </is>
-      </c>
+      <c r="F53" s="3" t="inlineStr"/>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr"/>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>København SV (Bådehavnsgade 44F, 2450), Regione Hovedstaden</t>
+          <t>Odense C (Filosofgangen 9, 5000), Regione Syddanmark</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>https://www.proff.dk/firma/copenhagen-coffee-lab-aps/k%C3%B8benhavn-sv/producenter/GXVBRXI016D</t>
+          <t>https://proff.dk/firma/dansk-kaffe-aps/odense-c/kaffe-og-te-agentur-og-engros/0EXL1KI0Z8T</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>DANSK KAFFE ApS</t>
+          <t>Estate Coffee Copenhagen A/S</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Caffè — import/export caffè verde</t>
+          <t>Caffè — torrefazione + cacao/cioccolato</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Micro-impresa: capitale sociale 80 t.DKK; dipendenti e fatturato non pubblicati nelle fonti consultate. Codice NACE 463700 (engros di caffè, tè, cacao e spezie); oggetto sociale: import/export di caffè. Fonte: proff.dk. SOTTO IL TARGET ma importatore puro. · CVR 25081544</t>
+          <t>10-20 dipendenti; bruttofortjeneste 10 mio. DKK (bilancio 2021); fatturato non pubblicato. Costituita nel 1994. Fonte: paqle.dk / proff.dk / retailnews.dk. SOTTO IL TARGET ma doppia commodity EUDR (caffè + cacao). NB: stesso CVR 18179407 ora registrato come Smage-Compagniet A/S (Holmevej 10, 5683 Haarby); marchi Estate Coffee, Chokolade Compagniet, Valrhona. · CVR 18179407</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Jens Erik Nielsen</t>
+          <t>Anders Laursen</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>Direktør</t>
-        </is>
-      </c>
-      <c r="F54" s="5" t="inlineStr"/>
-      <c r="G54" s="5" t="inlineStr">
-        <is>
-          <t>n.d.</t>
-        </is>
-      </c>
-      <c r="H54" s="5" t="inlineStr"/>
+          <t>Administrerende direktør (subentrato a Steen Aalund Olsen)</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>https://dk.linkedin.com/company/smage-compagniet</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>kontakt@estatecph.com</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>https://estatecoffee.dk/</t>
+        </is>
+      </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>Odense C (Filosofgangen 9, 5000), Regione Syddanmark</t>
+          <t>Haarby (Assens), Regione Syddanmark</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>https://proff.dk/firma/dansk-kaffe-aps/odense-c/kaffe-og-te-agentur-og-engros/0EXL1KI0Z8T</t>
+          <t>https://www.proff.dk/roller/estate-coffee-copenhagen-as/haarby/producenter/GLOZ6AI016D/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>Estate Coffee Copenhagen A/S</t>
+          <t>I.M. FRELLSEN K/S (Frellsen Kaffe &amp; Te / Frellsen Chokoladefabrik)</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Caffè — torrefazione + cacao/cioccolato</t>
+          <t>Caffè — import caffè verde + cacao/cioccolato</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>10-20 dipendenti; bruttofortjeneste 10 mio. DKK (bilancio 2021); fatturato non pubblicato. Costituita nel 1994. Fonte: paqle.dk / proff.dk / retailnews.dk. SOTTO IL TARGET ma doppia commodity EUDR (caffè + cacao). NB: stesso CVR 18179407 ora registrato come Smage-Compagniet A/S (Holmevej 10, 5683 Haarby); marchi Estate Coffee, Chokolade Compagniet, Valrhona. · CVR 18179407</t>
+          <t>Fatturato aggregato ~300 mio. DKK (~40 M€) nel 2022; dipendenti riportati tra 476 e 550 a seconda della fonte (include rete retail). Fonte: proff.dk / sn.dk. AL LIMITE SUPERIORE del range tollerabile; doppia commodity EUDR (caffè verde + cacao) - lead ad alta priorità. · CVR 25340604</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Anders Laursen</t>
+          <t>Peter Muldorff Frellsen</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Administrerende direktør (subentrato a Steen Aalund Olsen)</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>https://dk.linkedin.com/company/smage-compagniet</t>
-        </is>
-      </c>
+          <t>Direktør (con Henrik Muldorff Frellsen)</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr"/>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>kontakt@estatecph.com</t>
+          <t>kaffe@frellsen.dk</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>https://estatecoffee.dk/</t>
+          <t>https://frellsen.dk/</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>Haarby (Assens), Regione Syddanmark</t>
+          <t>Roskilde (Industrivej 14, 4000), Regione Sjælland</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>https://www.proff.dk/roller/estate-coffee-copenhagen-as/haarby/producenter/GLOZ6AI016D/</t>
+          <t>https://www.proff.dk/firma/i-m-frellsen-kaffe-te/roskilde/n%C3%A6rings-og-nydelsesmidler-produktion/GM5KIDI10JW</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>I.M. FRELLSEN K/S (Frellsen Kaffe &amp; Te / Frellsen Chokoladefabrik)</t>
+          <t>Just Coffee I/S</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>Caffè — import caffè verde + cacao/cioccolato</t>
+          <t>Caffè — import caffè verde bio + torrefazione</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Fatturato aggregato ~300 mio. DKK (~40 M€) nel 2022; dipendenti riportati tra 476 e 550 a seconda della fonte (include rete retail). Fonte: proff.dk / sn.dk. AL LIMITE SUPERIORE del range tollerabile; doppia commodity EUDR (caffè verde + cacao) - lead ad alta priorità. · CVR 25340604</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t>Peter Muldorff Frellsen</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>Direktør (con Henrik Muldorff Frellsen)</t>
-        </is>
-      </c>
-      <c r="F56" s="5" t="inlineStr"/>
+          <t>n.d. - impresa familiare, torrefazione propria; importa direttamente caffè verde certificato bio e sostenibile. Fatturato e dipendenti non pubblicati nelle fonti consultate. Fonte: sito aziendale / drypdryp.dk. Probabilmente SOTTO IL TARGET; operatore EUDR (import diretto). · ragione sociale CVR non verificata</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr"/>
+      <c r="E56" s="5" t="inlineStr"/>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>https://dk.linkedin.com/company/justcoffedk</t>
+        </is>
+      </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>kaffe@frellsen.dk</t>
+          <t>info@justcoffee.dk</t>
         </is>
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>https://frellsen.dk/</t>
+          <t>https://www.justcoffee.dk/</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>Roskilde (Industrivej 14, 4000), Regione Sjælland</t>
+          <t>Jyllinge (Roskilde), Regione Sjælland</t>
         </is>
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>https://www.proff.dk/firma/i-m-frellsen-kaffe-te/roskilde/n%C3%A6rings-og-nydelsesmidler-produktion/GM5KIDI10JW</t>
+          <t>https://www.justcoffee.dk/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>Just Coffee I/S</t>
+          <t>Kontra A/S (KONTRA Coffee)</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Caffè — import caffè verde bio + torrefazione</t>
+          <t>Caffè — torrefazione/engros (import caffè verde)</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>n.d. - impresa familiare, torrefazione propria; importa direttamente caffè verde certificato bio e sostenibile. Fatturato e dipendenti non pubblicati nelle fonti consultate. Fonte: sito aziendale / drypdryp.dk. Probabilmente SOTTO IL TARGET; operatore EUDR (import diretto). · ragione sociale CVR non verificata</t>
-        </is>
-      </c>
-      <c r="D57" s="3" t="inlineStr"/>
-      <c r="E57" s="3" t="inlineStr"/>
+          <t>28-29 dipendenti nell'unità produttiva di Hvidovre + 8 nel punto vendita di København Ø; fatturato non pubblicato nelle fonti consultate. Attiva dal 2005. Fonte: proff.dk. SOTTO IL TARGET (stima &lt;10 M€) ma torrefattore/importatore strutturato. · CVR 56312412</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Henrik Aagaard</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Adm. direktør</t>
+        </is>
+      </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/company/justcoffedk</t>
+          <t>https://dk.linkedin.com/company/kontra-coffee</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>info@justcoffee.dk</t>
+          <t>kontakt@kontracoffee.com</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>https://www.justcoffee.dk/</t>
+          <t>https://www.kontracoffee.com/</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>Jyllinge (Roskilde), Regione Sjælland</t>
+          <t>Hvidovre (Jernholmen 45E, 2650) - punto vendita København Ø, Regione Hovedstaden</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>https://www.justcoffee.dk/</t>
+          <t>https://www.proff.dk/firma/kontra-as/hvidovre/kaffe-og-te-agentur-og-engros/H0B8BKI0Z8T</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>Kontra A/S (KONTRA Coffee)</t>
+          <t>La Cabra Risteri ApS (gruppo La Cabra)</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>Caffè — torrefazione/engros (import caffè verde)</t>
+          <t>Caffè — torrefazione + import caffè verde</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>28-29 dipendenti nell'unità produttiva di Hvidovre + 8 nel punto vendita di København Ø; fatturato non pubblicato nelle fonti consultate. Attiva dal 2005. Fonte: proff.dk. SOTTO IL TARGET (stima &lt;10 M€) ma torrefattore/importatore strutturato. · CVR 56312412</t>
+          <t>Unità risteri: 59 dipendenti (CVR 43681176, costituita 01/11/2022). Fatturato di gruppo La Cabra 150 mio. DKK (~20 M€) es. 2023/24, raddoppiato sull'anno precedente (33 mio. DKK a marzo 2022); ~50% del fatturato da USA. Fonte: fodevarewatch.dk + proff.dk. IN TARGET. Risultato es. 2025 -2,7 mio.; DKK (virmo.dk, CVR 43681176).</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Henrik Aagaard</t>
+          <t>Esben Hageneier Piper</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>Adm. direktør</t>
+          <t>Direktør / co-fondatore e comproprietario del gruppo La Cabra</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/company/kontra-coffee</t>
-        </is>
-      </c>
-      <c r="G58" s="6" t="inlineStr">
-        <is>
-          <t>kontakt@kontracoffee.com</t>
+          <t>https://www.linkedin.com/company/la-cabra-coffee-roasters</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>n.d.</t>
         </is>
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>https://www.kontracoffee.com/</t>
+          <t>https://lacabra.com/</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>Hvidovre (Jernholmen 45E, 2650) - punto vendita København Ø, Regione Hovedstaden</t>
+          <t>Nordhavn, København (Århusgade 118X, 2150), Regione Hovedstaden</t>
         </is>
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>https://www.proff.dk/firma/kontra-as/hvidovre/kaffe-og-te-agentur-og-engros/H0B8BKI0Z8T</t>
+          <t>https://www.proff.dk/firma/la-cabra-risteri-aps/nordhavn/producenter/0Q08M0I016D</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>La Cabra Risteri ApS (gruppo La Cabra)</t>
+          <t>Nordic Coffee House ApS</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Caffè — torrefazione + import caffè verde</t>
+          <t>Caffè — engros e import</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Unità risteri: 59 dipendenti (CVR 43681176, costituita 01/11/2022). Fatturato di gruppo La Cabra 150 mio. DKK (~20 M€) es. 2023/24, raddoppiato sull'anno precedente (33 mio. DKK a marzo 2022); ~50% del fatturato da USA. Fonte: fodevarewatch.dk + proff.dk. IN TARGET.</t>
+          <t>n.d. - fatturato e dipendenti non pubblicati nelle fonti consultate. Registrata nella categoria 'Kaffe og te - agentur og engros'; risteri proprio a Nr. Bjertvej 67, 6000 Kolding, import diretto di caffè verde. Gazelle Børsen 2023 e 2024. Fonte: proff.dk / nordiccoffeehouse.dk. Taglia probabilmente sotto il target: da verificare. · CVR 39807122</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Esben Hageneier Piper</t>
+          <t>Michael Molbaek</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Direktør / co-fondatore e comproprietario del gruppo La Cabra</t>
+          <t>Direktør</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/la-cabra-coffee-roasters</t>
-        </is>
-      </c>
-      <c r="G59" s="3" t="inlineStr">
-        <is>
-          <t>n.d.</t>
+          <t>https://dk.linkedin.com/company/nordic-coffee-house-aps</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>info@nordiccoffeehouse.dk</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>https://lacabra.com/</t>
+          <t>https://nordiccoffeehouse.dk/</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>Nordhavn, København (Århusgade 118X, 2150), Regione Hovedstaden</t>
+          <t>Kolding, Regione Syddanmark</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>https://www.proff.dk/firma/la-cabra-risteri-aps/nordhavn/producenter/0Q08M0I016D</t>
+          <t>https://www.proff.dk/firma/nordic-coffee-house-aps/kolding/kaffe-og-te-agentur-og-engros/GXLJKUI0Z8T</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>Nordic Coffee House ApS</t>
+          <t>The Coffee Collective A/S</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>Caffè — engros e import</t>
+          <t>Caffè — torrefazione + import caffè verde</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>n.d. - fatturato e dipendenti non pubblicati nelle fonti consultate. Registrata nella categoria 'Kaffe og te - agentur og engros'; risteri proprio a Nr. Bjertvej 67, 6000 Kolding, import diretto di caffè verde. Gazelle Børsen 2023 e 2024. Fonte: proff.dk / nordiccoffeehouse.dk. Taglia probabilmente sotto il target: da verificare. · CVR 39807122</t>
+          <t>Nettoomsætning 81,1 mio. DKK (~10,9 M€) es. 2023/24, +14,2% su 71,1 mio. DKK; risultato ante imposte 1,8 mio. DKK. Dipendenti n.d. Fonte dati di bilancio 2023/24 (find-virksomhed.dk / proff.dk). IN TARGET. · CVR 30706595</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Michael Molbaek</t>
+          <t>Rebecca Vang</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>Direktør</t>
+          <t>Adm. direktør (CEO), dal 2024</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/company/nordic-coffee-house-aps</t>
+          <t>https://www.linkedin.com/company/coffee-collective</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>info@nordiccoffeehouse.dk</t>
+          <t>ordre@coffeecollective.dk</t>
         </is>
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
-          <t>https://nordiccoffeehouse.dk/</t>
+          <t>https://coffeecollective.dk/</t>
         </is>
       </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>Kolding, Regione Syddanmark</t>
+          <t>Frederiksberg / København, Regione Hovedstaden</t>
         </is>
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>https://www.proff.dk/firma/nordic-coffee-house-aps/kolding/kaffe-og-te-agentur-og-engros/GXLJKUI0Z8T</t>
+          <t>https://find-virksomhed.dk/firma/the-coffee-collective-a-s-30706595</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>The Coffee Collective A/S</t>
+          <t>AALBORG CHOKOLADEN ApS</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Caffè — torrefazione + import caffè verde</t>
+          <t>Cacao/Cioccolato</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Nettoomsætning 81,1 mio. DKK (~10,9 M€) es. 2023/24, +14,2% su 71,1 mio. DKK; risultato ante imposte 1,8 mio. DKK. Dipendenti n.d. Fonte dati di bilancio 2023/24 (find-virksomhed.dk / proff.dk). IN TARGET. · CVR 30706595</t>
+          <t>32 dipendenti; bruttofortjeneste 7,37 mio. DKK e risultato ante imposte 0,25 mio. DKK (2024). Fatturato non pubblicato. Capogruppo: ASLAK COMPANY ApS. Fonte: proff.dk. SOTTO IL TARGET (micro/piccola). · CVR 29842957</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Rebecca Vang</t>
+          <t>John Aslak Jensen</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Adm. direktør (CEO), dal 2024</t>
+          <t>Direktør</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/coffee-collective</t>
+          <t>https://dk.linkedin.com/company/aalborg-chokoladen</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>ordre@coffeecollective.dk</t>
+          <t>info@aalborgchokoladen.dk</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>https://coffeecollective.dk/</t>
+          <t>https://www.aalborgchokoladen.dk/</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>Frederiksberg / København, Regione Hovedstaden</t>
+          <t>Aalborg Øst (Troensevej 4M, 9220), Regione Nordjylland</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>https://find-virksomhed.dk/firma/the-coffee-collective-a-s-30706595</t>
+          <t>https://www.proff.dk/firma/aalborg-chokoladen-aps/aalborg-%C3%B8st/n%C3%A6rings-og-nydelsesmidler/GQUFGRI116S</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>AALBORG CHOKOLADEN ApS</t>
+          <t>COPENHAGEN CHOCOLATE FACTORY ApS</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
@@ -17259,49 +17259,49 @@
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>32 dipendenti; bruttofortjeneste 7,37 mio. DKK e risultato ante imposte 0,25 mio. DKK (2024). Fatturato non pubblicato. Capogruppo: ASLAK COMPANY ApS. Fonte: proff.dk. SOTTO IL TARGET (micro/piccola). · CVR 29842957</t>
+          <t>Fatturato 48,3 mio. DKK (~6,5 M€) nell'ultimo esercizio disponibile; 20-50 dipendenti. Costituita nel 2010. Opera con il marchio Simply Chocolate Copenhagen (Amager Landevej 123, 2770 Kastrup); presidente CdA David Robson Overby; capogruppo SOLSTRA INVESTMENTS ApS. Fonte: vainu.com (dati CVR) / paqle.dk / proff.dk / vismarating.dk. Nel range tollerabile inferiore.</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>John Aslak Jensen</t>
+          <t>Niels Østenkær</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>Direktør</t>
+          <t>Administrerende direktør</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/company/aalborg-chokoladen</t>
+          <t>https://www.linkedin.com/company/simply-chocolate-copenhagen</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>info@aalborgchokoladen.dk</t>
+          <t>info@simplychocolate.dk</t>
         </is>
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>https://www.aalborgchokoladen.dk/</t>
+          <t>https://www.simplychocolate.dk/</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>Aalborg Øst (Troensevej 4M, 9220), Regione Nordjylland</t>
+          <t>Kastrup (Tårnby), Regione Hovedstaden</t>
         </is>
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>https://www.proff.dk/firma/aalborg-chokoladen-aps/aalborg-%C3%B8st/n%C3%A6rings-og-nydelsesmidler/GQUFGRI116S</t>
+          <t>https://search.vainu.com/company/copenhagen-chocolate-factory-aps-omsaetning-og-noegletal/DK32761844/virksomhedsoplysninger</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>COPENHAGEN CHOCOLATE FACTORY ApS</t>
+          <t>PETER BEIER CHOKOLADE A/S</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -17311,149 +17311,149 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Fatturato 48,3 mio. DKK (~6,5 M€) nell'ultimo esercizio disponibile; 20-50 dipendenti. Costituita nel 2010. Opera con il marchio Simply Chocolate Copenhagen (Amager Landevej 123, 2770 Kastrup); presidente CdA David Robson Overby; capogruppo SOLSTRA INVESTMENTS ApS. Fonte: vainu.com (dati CVR) / paqle.dk / proff.dk / vismarating.dk. Nel range tollerabile inferiore.</t>
+          <t>64 dipendenti medi (dato di bilancio riportato, in crescita da 56); risultato netto 1,96 mio. DKK (+25% a/a) e patrimonio netto 13,4 mio. DKK nel bilancio citato dalle fonti. Fatturato non pubblicato. Concetto 'farm-to-table' con piantagione di cacao propria nella Repubblica Dominicana (operatore EUDR diretto). Fonte: proff.dk / sn.dk / food-supply.dk. Probabilmente sotto il target. · CVR 26058007</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>Niels Østenkær</t>
+          <t>Peter Beier</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Administrerende direktør</t>
+          <t>Direktør / fondatore</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/simply-chocolate-copenhagen</t>
+          <t>https://www.linkedin.com/company/peter-beier-chokolade-a-s</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>info@simplychocolate.dk</t>
+          <t>kundeservice@pbchokolade.dk</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>https://www.simplychocolate.dk/</t>
+          <t>https://pbchokolade.dk/</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>Kastrup (Tårnby), Regione Hovedstaden</t>
+          <t>Helsingør (Ørsholtvej 35A, 3000), Regione Hovedstaden</t>
         </is>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>https://search.vainu.com/company/copenhagen-chocolate-factory-aps-omsaetning-og-noegletal/DK32761844/virksomhedsoplysninger</t>
+          <t>https://www.proff.dk/firma/peter-beier-chokolade-as/helsing%C3%B8r/udleje/0FIIHJI01TD</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>PETER BEIER CHOKOLADE A/S</t>
+          <t>PR CHOKOLADE A/S</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>Cacao/Cioccolato</t>
+          <t>Cacao/Cioccolato — produzione ed engros</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>64 dipendenti medi (dato di bilancio riportato, in crescita da 56); risultato netto 1,96 mio. DKK (+25% a/a) e patrimonio netto 13,4 mio. DKK nel bilancio citato dalle fonti. Fatturato non pubblicato. Concetto 'farm-to-table' con piantagione di cacao propria nella Repubblica Dominicana (operatore EUDR diretto). Fonte: proff.dk / sn.dk / food-supply.dk. Probabilmente sotto il target. · CVR 26058007</t>
+          <t>46 dipendenti; bruttofortjeneste 17 mio. DKK (2024). Fatturato non pubblicato. Costituita 29/05/2000; NACE 463600 (engros zucchero/cioccolato) + 108200 (fabbricazione cacao e cioccolato). Fonte: proff.dk / lasso.dk. Sotto il target. · CVR 25391462</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Peter Beier</t>
+          <t>Kim Lund Bennedbæk Clausen</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>Direktør / fondatore</t>
-        </is>
-      </c>
-      <c r="F64" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/peter-beier-chokolade-a-s</t>
-        </is>
-      </c>
+          <t>Adm. direktør</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr"/>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>kundeservice@pbchokolade.dk</t>
+          <t>salg@prchokolade.dk</t>
         </is>
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>https://pbchokolade.dk/</t>
+          <t>https://www.prchokolade.dk/</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>Helsingør (Ørsholtvej 35A, 3000), Regione Hovedstaden</t>
+          <t>Kolding (Kokbjerg 29A, 6000), Regione Syddanmark</t>
         </is>
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>https://www.proff.dk/firma/peter-beier-chokolade-as/helsing%C3%B8r/udleje/0FIIHJI01TD</t>
+          <t>https://www.proff.dk/firma/pr-chokolade-as/kolding/producenter/GLUG9CI016D</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>PR CHOKOLADE A/S</t>
+          <t>SPANGSBERG CHOKOLADE A/S / Spangsberg Chokoladefabrik A/S</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Cacao/Cioccolato — produzione ed engros</t>
+          <t>Cacao/Cioccolato</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>46 dipendenti; bruttofortjeneste 17 mio. DKK (2024). Fatturato non pubblicato. Costituita 29/05/2000; NACE 463600 (engros zucchero/cioccolato) + 108200 (fabbricazione cacao e cioccolato). Fonte: proff.dk / lasso.dk. Sotto il target. · CVR 25391462</t>
+          <t>100-200 dipendenti (di cui 38 nell'unità produttiva di Taastrup); bruttofortjeneste 38 mio. DKK (2024) e 34 mio. DKK (2023); fatturato non pubblicato ma coerente con il target 10-20 M€. Presidente CdA: Peter Ernst Wengler-Jørgensen. Produzione e commercio di flødeboller, cioccolato e dolciumi. Fonte: proff.dk / paqle.dk. · CVR 26458005</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Kim Lund Bennedbæk Clausen</t>
+          <t>Michael Spangsberg</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Adm. direktør</t>
-        </is>
-      </c>
-      <c r="F65" s="3" t="inlineStr"/>
+          <t>Direktør</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>https://dk.linkedin.com/company/spangsberg</t>
+        </is>
+      </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>salg@prchokolade.dk</t>
+          <t>marketing@spangsbergchokolade.dk</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>https://www.prchokolade.dk/</t>
+          <t>https://spangsbergchokolade.dk/</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
-          <t>Kolding (Kokbjerg 29A, 6000), Regione Syddanmark</t>
+          <t>Taastrup (Taastrupgårdsvej 16-22, 2630), Regione Hovedstaden - unità anche a Esbjerg N</t>
         </is>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>https://www.proff.dk/firma/pr-chokolade-as/kolding/producenter/GLUG9CI016D</t>
+          <t>https://www.proff.dk/firma/spangsberg-chokoladefabrik-as/taastrup/producenter/GSWDT2I016D</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>SPANGSBERG CHOKOLADE A/S / Spangsberg Chokoladefabrik A/S</t>
+          <t>Summerbird A/S</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -17463,153 +17463,153 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>100-200 dipendenti (di cui 38 nell'unità produttiva di Taastrup); bruttofortjeneste 38 mio. DKK (2024) e 34 mio. DKK (2023); fatturato non pubblicato ma coerente con il target 10-20 M€. Presidente CdA: Peter Ernst Wengler-Jørgensen. Produzione e commercio di flødeboller, cioccolato e dolciumi. Fonte: proff.dk / paqle.dk. · CVR 26458005</t>
+          <t>193-221 dipendenti a seconda della fonte; bruttofortjeneste 63,7 mio. DKK (2022) e 79,0 mio. DKK (2021); risultato 2024 8,0 mio. DKK (7,3 mio. DKK nel 2023). Fatturato non pubblicato: stimabile ~150-200 mio. DKK (~20-27 M€) sulla base di margine e organico, ma NON verificato. Presidente CdA: Peter Eriksen Jensen. Fonte: proff.dk / estatistik.dk / fyens.dk. · CVR 24209644</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Michael Spangsberg</t>
+          <t>Mikael Grønlykke</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>Direktør</t>
+          <t>Administrerende direktør (dal 03/08/2009)</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/company/spangsberg</t>
+          <t>https://dk.linkedin.com/company/summerbirdorganic</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>marketing@spangsbergchokolade.dk</t>
+          <t>salg@summerbird.dk</t>
         </is>
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>https://spangsbergchokolade.dk/</t>
+          <t>https://summerbird.dk/</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>Taastrup (Taastrupgårdsvej 16-22, 2630), Regione Hovedstaden - unità anche a Esbjerg N</t>
+          <t>Assens (Fyn), Regione Syddanmark</t>
         </is>
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>https://www.proff.dk/firma/spangsberg-chokoladefabrik-as/taastrup/producenter/GSWDT2I016D</t>
+          <t>https://www.proff.dk/firma/summerbird-as/assens/producenter/GN6UXHI016D</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>Summerbird A/S</t>
+          <t>Xocolatl Christiansfeld ApS</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Cacao/Cioccolato</t>
+          <t>Cacao/Cioccolato — produzione ed engros</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>193-221 dipendenti a seconda della fonte; bruttofortjeneste 63,7 mio. DKK (2022) e 79,0 mio. DKK (2021); risultato 2024 8,0 mio. DKK (7,3 mio. DKK nel 2023). Fatturato non pubblicato: stimabile ~150-200 mio. DKK (~20-27 M€) sulla base di margine e organico, ma NON verificato. Presidente CdA: Peter Eriksen Jensen. Fonte: proff.dk / estatistik.dk / fyens.dk. · CVR 24209644</t>
+          <t>56 dipendenti (fonte paqle: 50-100); bruttofortjeneste 15 mio. DKK (2024), 14,5 mio. DKK (2023), 12,7 mio. DKK (2022). Fatturato non pubblicato. Capogruppo: MINKO INVEST ApS. Aderente a Cocoa Horizons. Fonte: proff.dk. Sotto il target ma con produzione propria da cacao. · CVR 34458375</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>Mikael Grønlykke</t>
+          <t>Gitte Kohls</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>Administrerende direktør (dal 03/08/2009)</t>
+          <t>Administrerende direktør</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/company/summerbirdorganic</t>
+          <t>https://www.linkedin.com/in/xocolatl-christiansfeld-aps-837b35b4/</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>salg@summerbird.dk</t>
+          <t>gitte@xocolatl.dk</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>https://summerbird.dk/</t>
+          <t>https://xocolatl.dk/</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>Assens (Fyn), Regione Syddanmark</t>
+          <t>Haderslev (Storegade 11A, 6100) - produzione a Hejls, Regione Syddanmark</t>
         </is>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>https://www.proff.dk/firma/summerbird-as/assens/producenter/GN6UXHI016D</t>
+          <t>https://www.proff.dk/firma/xocolatl-christiansfeld-aps/haderslev/producenter/0KIK93I016D</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>Xocolatl Christiansfeld ApS</t>
+          <t>AVK GUMMI A/S</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>Cacao/Cioccolato — produzione ed engros</t>
+          <t>Gomma</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>56 dipendenti (fonte paqle: 50-100); bruttofortjeneste 15 mio. DKK (2024), 14,5 mio. DKK (2023), 12,7 mio. DKK (2022). Fatturato non pubblicato. Capogruppo: MINKO INVEST ApS. Aderente a Cocoa Horizons. Fonte: proff.dk. Sotto il target ma con produzione propria da cacao. · CVR 34458375</t>
+          <t>Fatturato (omsætning) NON pubblicato in nessuna fonte consultata: la soglia dei 50 M EUR non e verificabile. Dati pubblicati: bruttofortjeneste 91,99 mio DKK (~12,3 M EUR) nel 2024, in calo da 105,49 mio DKK nel 2023; arets resultat 43,53 mio DKK (~5,8 M EUR) nel 2024 (56,41 mio DKK nel 2023); 229 dipendenti (2024). ATTENZIONE: azienda grande (parte del gruppo AVK Holding A/S), possibilmente sopra la fascia target - da verificare con bilancio integrale. Fonti: proff.dk/virmo.dk/estatistik.dk (CVR 55375313), anni 2023-2024</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Gitte Kohls</t>
+          <t>Peter Lorentzen</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>Administrerende direktør</t>
+          <t>Adm. direktør</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/xocolatl-christiansfeld-aps-837b35b4/</t>
+          <t>https://www.linkedin.com/company/avk-gummi-a-s</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>gitte@xocolatl.dk</t>
+          <t>avk@avkgummi.dk</t>
         </is>
       </c>
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>https://xocolatl.dk/</t>
+          <t>https://www.avkgummi.dk/</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>Haderslev (Storegade 11A, 6100) - produzione a Hejls, Regione Syddanmark</t>
+          <t>Låsby (area Galten/Skanderborg), Region Midtjylland</t>
         </is>
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>https://www.proff.dk/firma/xocolatl-christiansfeld-aps/haderslev/producenter/0KIK93I016D</t>
+          <t>https://www.proff.dk/firma/avk-gummi-as/l%C3%A5sby/gummi-og-plastprodukter/GKL15SI10NU</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>AVK GUMMI A/S</t>
+          <t>DANSK GUMMI INDUSTRI A/S</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -17619,49 +17619,49 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Fatturato (omsætning) NON pubblicato in nessuna fonte consultata: la soglia dei 50 M EUR non e verificabile. Dati pubblicati: bruttofortjeneste 91,99 mio DKK (~12,3 M EUR) nel 2024, in calo da 105,49 mio DKK nel 2023; arets resultat 43,53 mio DKK (~5,8 M EUR) nel 2024 (56,41 mio DKK nel 2023); 229 dipendenti (2024). ATTENZIONE: azienda grande (parte del gruppo AVK Holding A/S), possibilmente sopra la fascia target - da verificare con bilancio integrale. Fonti: proff.dk/virmo.dk/estatistik.dk (CVR 55375313), anni 2023-2024</t>
+          <t>Fatturato non pubblicato nelle fonti consultate (n.d.); ca. 40-62 dipendenti; utile 2025 ca. 16 mio DKK (~2,1 M EUR). Fonti: proff.dk (CVR 35405909) e jv.dk, anno 2025</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>Peter Lorentzen</t>
+          <t>Christian Kronberg Thomsen</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>Adm. direktør</t>
+          <t>Adm. direktør (CEO), 4a generazione</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/avk-gummi-a-s</t>
+          <t>https://dk.linkedin.com/company/dansk-gummi-industri</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>avk@avkgummi.dk</t>
+          <t>sales@danskgummi.dk</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>https://www.avkgummi.dk/</t>
+          <t>https://danskgummi.com/</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>Låsby (area Galten/Skanderborg), Region Midtjylland</t>
+          <t>Kolding (Profilvej 18, 6000), Region Syddanmark</t>
         </is>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>https://www.proff.dk/firma/avk-gummi-as/l%C3%A5sby/gummi-og-plastprodukter/GKL15SI10NU</t>
+          <t>https://www.proff.dk/firma/dansk-gummi-industri-as/kolding/gummi-og-plastprodukter/GUH82GI10NU</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>DANSK GUMMI INDUSTRI A/S</t>
+          <t>H.C. JACOBSEN A/S</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
@@ -17671,49 +17671,45 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Fatturato non pubblicato nelle fonti consultate (n.d.); ca. 40-62 dipendenti; utile 2025 ca. 16 mio DKK (~2,1 M EUR). Fonti: proff.dk (CVR 35405909) e jv.dk, anno 2025</t>
+          <t>Fatturato non pubblicato (n.d.); bruttofortjeneste 3,2 mio DKK (~0,4 M EUR) nel 2025. ATTENZIONE: sotto la fascia target. Fonte: proff.dk (CVR 75144911), anno 2025 Capogruppo BEA HOLDING ApS; presidente CdA Pernille Andersen; distributore di imballaggi ed elastici, FUORI dalla forbice 5-40 M EUR.</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Christian Kronberg Thomsen</t>
+          <t>Bjarni Engelhardt Andersen</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>Adm. direktør (CEO), 4a generazione</t>
-        </is>
-      </c>
-      <c r="F70" s="6" t="inlineStr">
-        <is>
-          <t>https://dk.linkedin.com/company/dansk-gummi-industri</t>
-        </is>
-      </c>
+          <t>Direktør</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="inlineStr"/>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>sales@danskgummi.dk</t>
+          <t>info@hc-jacobsen.dk</t>
         </is>
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>https://danskgummi.com/</t>
+          <t>https://hcemballage.dk/</t>
         </is>
       </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>Kolding (Profilvej 18, 6000), Region Syddanmark</t>
+          <t>Ganløse/Stenløse (Sandbakken 5, 3660), Region Hovedstaden</t>
         </is>
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>https://www.proff.dk/firma/dansk-gummi-industri-as/kolding/gummi-og-plastprodukter/GUH82GI10NU</t>
+          <t>https://www.proff.dk/firma/h.c.-jacobsen-as/stenl%C3%B8se/gummi-og-plastprodukter/GKU06AI10NU</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>H.C. JACOBSEN A/S</t>
+          <t>RG ROM GUMMI A/S</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -17723,45 +17719,49 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Fatturato non pubblicato (n.d.); bruttofortjeneste 3,2 mio DKK (~0,4 M EUR) nel 2025. ATTENZIONE: sotto la fascia target. Fonte: proff.dk (CVR 75144911), anno 2025</t>
+          <t>Fatturato non pubblicato (n.d.); bruttofortjeneste 53 mio DKK (~7,1 M EUR) nel 2023; 71-80 dipendenti. Fonti: proff.dk (CVR 76653313), romgummi.dk, anno 2023 Controllata tramite RGDE ApS, societa in portafoglio del fondo Dansk Ejerkapital.</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Bjarni Engelhardt Andersen</t>
+          <t>Jesper Berg Kristensen</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>Direktør</t>
-        </is>
-      </c>
-      <c r="F71" s="3" t="inlineStr"/>
+          <t>Adm. direktør (CEO)</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rg-rom-gummi</t>
+        </is>
+      </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>info@hc-jacobsen.dk</t>
+          <t>info@romgummi.dk</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>https://hcemballage.dk/</t>
+          <t>https://romgummi.dk/</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>Ganløse/Stenløse (Sandbakken 5, 3660), Region Hovedstaden</t>
+          <t>Lemvig, Region Midtjylland</t>
         </is>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>https://www.proff.dk/firma/h.c.-jacobsen-as/stenl%C3%B8se/gummi-og-plastprodukter/GKU06AI10NU</t>
+          <t>https://www.proff.dk/firma/rg-rom-gummi-as/lemvig/gummi-og-plastprodukter/19MY2PI10NU</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>RG ROM GUMMI A/S</t>
+          <t>Rubberproff ApS</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
@@ -17771,49 +17771,49 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>Fatturato non pubblicato (n.d.); bruttofortjeneste 53 mio DKK (~7,1 M EUR) nel 2023; 71-80 dipendenti. Fonti: proff.dk (CVR 76653313), romgummi.dk, anno 2023</t>
+          <t>Fatturato non pubblicato (n.d.); 2-10 dipendenti secondo il profilo LinkedIn aziendale; societa attiva dal 15.04.2019, controllata da MP17 Holding ApS. ATTENZIONE: sotto la fascia target. Fonti: proff.dk (CVR 40465790), linkedin.com/company/rubberproff</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Jesper Berg Kristensen</t>
+          <t>Mathias Pedersen</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>Adm. direktør (CEO)</t>
+          <t>Direktør e stifter (fondatore)</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/rg-rom-gummi</t>
+          <t>https://dk.linkedin.com/company/rubberproff</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>info@romgummi.dk</t>
+          <t>info@rubberproff.dk</t>
         </is>
       </c>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>https://romgummi.dk/</t>
+          <t>https://rubberproff.dk/</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>Lemvig, Region Midtjylland</t>
+          <t>Hals (Ulstedvej 36, 9370), Region Nordjylland</t>
         </is>
       </c>
       <c r="J72" s="5" t="inlineStr">
         <is>
-          <t>https://www.proff.dk/firma/rg-rom-gummi-as/lemvig/gummi-og-plastprodukter/19MY2PI10NU</t>
+          <t>https://www.proff.dk/firma/rubberproff-aps/n%C3%B8rresundby/engroshandel-annet/GY1KTSI10N6</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>Rubberproff ApS</t>
+          <t>SKANDINAVISK DÆK IMPORT A/S</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -17823,101 +17823,97 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Fatturato non pubblicato (n.d.); 2-10 dipendenti secondo il profilo LinkedIn aziendale; societa attiva dal 15.04.2019, controllata da MP17 Holding ApS. ATTENZIONE: sotto la fascia target. Fonti: proff.dk (CVR 40465790), linkedin.com/company/rubberproff</t>
+          <t>n.d. (fatturato e dipendenti non pubblicati nelle fonti accessibili); societa fondata nel 1984, commercio e produzione di pneumatici industriali. Fonte: proff.dk (CVR 87222810)</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>Mathias Pedersen</t>
+          <t>Michael Grouleff</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>Direktør e stifter (fondatore)</t>
+          <t>Adm. direktør/ejer</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/company/rubberproff</t>
+          <t>https://dk.linkedin.com/company/skandinavisk-daek-import-a-s</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>info@rubberproff.dk</t>
+          <t>mg@sdi.dk</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>https://rubberproff.dk/</t>
+          <t>https://sdi.dk/</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr">
         <is>
-          <t>Hals (Ulstedvej 36, 9370), Region Nordjylland</t>
+          <t>Havdrup (Industrivænget 14, 4622), Region Sjælland</t>
         </is>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>https://www.proff.dk/firma/rubberproff-aps/n%C3%B8rresundby/engroshandel-annet/GY1KTSI10N6</t>
+          <t>https://sdi.dk/kontakt/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>SKANDINAVISK DÆK IMPORT A/S</t>
+          <t>A-ONE DANMARK ApS</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>Gomma</t>
+          <t>Mangimi/Soia</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>n.d. (fatturato e dipendenti non pubblicati nelle fonti accessibili); societa fondata nel 1984, commercio e produzione di pneumatici industriali. Fonte: proff.dk (CVR 87222810)</t>
+          <t>Fatturato e numero dipendenti non pubblicati (ApS, bilancio in forma ridotta). Fonte: proff.dk (consultato 2026). CVR 33390971. Mangimi per scrofe e suinetti fino a 30 kg; parte del gruppo nordirlandese Devenish (quindi NON indipendente, ma entita' danese di taglia PMI). Sede: Ågade 16, 7800 Skive, tel. +45 86 65 26 55. Nota: fonte terza (ZoomInfo) indica 20-49 addetti - DA VERIFICARE. Nessuna email aziendale reperita nelle fonti consultate.</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Michael Grouleff</t>
+          <t>Jesper Skjøtt</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>Adm. direktør/ejer</t>
-        </is>
-      </c>
-      <c r="F74" s="6" t="inlineStr">
-        <is>
-          <t>https://dk.linkedin.com/company/skandinavisk-daek-import-a-s</t>
-        </is>
-      </c>
-      <c r="G74" s="6" t="inlineStr">
-        <is>
-          <t>mg@sdi.dk</t>
+          <t>Direktør</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="inlineStr"/>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>n.d.</t>
         </is>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>https://sdi.dk/</t>
+          <t>http://www.a-one-danmark.dk/</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>Havdrup (Industrivænget 14, 4622), Region Sjælland</t>
+          <t>Skive, Region Midtjylland</t>
         </is>
       </c>
       <c r="J74" s="5" t="inlineStr">
         <is>
-          <t>https://sdi.dk/kontakt/</t>
+          <t>https://www.proff.dk/firma/a-one-danmark-aps/skive/korn-r%C3%A5tobak-s%C3%A5varer-og-fodervarer-engros/GT8V6GI10P1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>A-ONE DANMARK ApS</t>
+          <t>AB NEO A/S (già AGRO KORN A/S)</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -17927,12 +17923,12 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Fatturato e numero dipendenti non pubblicati (ApS, bilancio in forma ridotta). Fonte: proff.dk (consultato 2026). CVR 33390971. Mangimi per scrofe e suinetti fino a 30 kg; parte del gruppo nordirlandese Devenish (quindi NON indipendente, ma entita' danese di taglia PMI). Sede: Ågade 16, 7800 Skive, tel. +45 86 65 26 55. Nota: fonte terza (ZoomInfo) indica 20-49 addetti - DA VERIFICARE. Nessuna email aziendale reperita nelle fonti consultate.</t>
+          <t>57 dipendenti (fonte proff.dk/erhvervplus.dk, 2025; altre fonti 50-100). Fatturato non pubblicato; risultato negativo -13 M DKK (es. 01/09/2023-31/08/2024) e -57 M DKK (es. 01/09/2024-31/08/2025). CVR 37404241. Produzione di mangimi completi per animali da allevamento. ATTENZIONE: controllata del gruppo britannico AB Agri/ABF - entita' danese di taglia PMI ma non indipendente. Sede: Skjernvej 42, 6920 Videbæk. Nessuna email aziendale reperita nelle fonti consultate.</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>Jesper Skjøtt</t>
+          <t>Jesper Riisgaard Nielsen</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
@@ -17948,39 +17944,39 @@
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>http://www.a-one-danmark.dk/</t>
+          <t>https://ab-neo.com/</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr">
         <is>
-          <t>Skive, Region Midtjylland</t>
+          <t>Videbæk (Ringkøbing-Skjern), Region Midtjylland</t>
         </is>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>https://www.proff.dk/firma/a-one-danmark-aps/skive/korn-r%C3%A5tobak-s%C3%A5varer-og-fodervarer-engros/GT8V6GI10P1</t>
+          <t>https://www.proff.dk/firma/ab-neo-as/videb%C3%A6k/foder/0M9PAPI00FB ; sito gruppo https://ab-neo.com/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>AB NEO A/S (già AGRO KORN A/S)</t>
+          <t>CEBECO FOURAGE A/S</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>Mangimi/Soia</t>
+          <t>Mangimi/Soia — kraftfoder bovini da latte</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>57 dipendenti (fonte proff.dk/erhvervplus.dk, 2025; altre fonti 50-100). Fatturato non pubblicato; risultato negativo -13 M DKK (es. 01/09/2023-31/08/2024) e -57 M DKK (es. 01/09/2024-31/08/2025). CVR 37404241. Produzione di mangimi completi per animali da allevamento. ATTENZIONE: controllata del gruppo britannico AB Agri/ABF - entita' danese di taglia PMI ma non indipendente. Sede: Skjernvej 42, 6920 Videbæk. Nessuna email aziendale reperita nelle fonti consultate.</t>
+          <t>Fatturato 10,8 M DKK ≈ 1,4 M€ (ultimo esercizio disponibile); 1 dipendente. TAGLIA MOLTO SOTTO IL TARGET (micro-impresa commerciale). Presidente CdA: Meindert Tjoelker. Fonte: proff.dk / Vainu. CVR 19628841. Commercio all'ingrosso di cereali e materie prime per mangimi; mangimi concentrati per vacche da latte. Sede: Pårupvej 17, 6933 Kibæk, tel. +45 40 17 40 96. Opera con il marchio Tjoelker Cebeco.</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Jesper Riisgaard Nielsen</t>
+          <t>Johannes Josef Westenbroek</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -17989,79 +17985,79 @@
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr"/>
-      <c r="G76" s="5" t="inlineStr">
-        <is>
-          <t>n.d.</t>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>info@cebeco.dk</t>
         </is>
       </c>
       <c r="H76" s="6" t="inlineStr">
         <is>
-          <t>https://ab-neo.com/</t>
+          <t>https://cebeco.dk/</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>Videbæk (Ringkøbing-Skjern), Region Midtjylland</t>
+          <t>Kibæk (Herning), Region Midtjylland</t>
         </is>
       </c>
       <c r="J76" s="5" t="inlineStr">
         <is>
-          <t>https://www.proff.dk/firma/ab-neo-as/videb%C3%A6k/foder/0M9PAPI00FB ; sito gruppo https://ab-neo.com/</t>
+          <t>https://www.proff.dk/firma/cebeco-fourage-as/kib%C3%A6k/korn-r%C3%A5tobak-s%C3%A5varer-og-fodervarer-engros/0BOPPLI10P1 ; email da https://cebeco.dk/kontakt/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>CEBECO FOURAGE A/S</t>
+          <t>CR FODERSERVICE K/S</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Mangimi/Soia — kraftfoder bovini da latte</t>
+          <t>Mangimi/Soia</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>Fatturato 10,8 M DKK ≈ 1,4 M€ (ultimo esercizio disponibile); 1 dipendente. TAGLIA MOLTO SOTTO IL TARGET (micro-impresa commerciale). Presidente CdA: Meindert Tjoelker. Fonte: proff.dk / Vainu. CVR 19628841. Commercio all'ingrosso di cereali e materie prime per mangimi; mangimi concentrati per vacche da latte. Sede: Pårupvej 17, 6933 Kibæk, tel. +45 40 17 40 96. Opera con il marchio Tjoelker Cebeco.</t>
+          <t>16 dipendenti (2025); bruttofortjeneste 8,94 M DKK (2024) ≈ 1,2 M€, era 10,21 M DKK (2023); risultato 0,53 M DKK. Fatturato NON pubblicato (K/S, bilancio ridotto): la dimensione effettiva del giro d'affari e' verosimilmente superiore ma non documentabile. Fonte: proff.dk / lasso.dk, dati 2024. CVR 33078366. Miscelazione mangimi con unita' mobili presso l'allevamento (hjemmeblanding), acquisto di soia/materie prime proteiche. Sede: Huggetvej 27, 5400 Bogense, tel. +45 64 83 12 75.</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>Johannes Josef Westenbroek</t>
+          <t>Niels Frost Rasmussen</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>Direktør</t>
+          <t>Direktør (fondatore)</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr"/>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>info@cebeco.dk</t>
+          <t>NFR@CR-F.dk</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>https://cebeco.dk/</t>
+          <t>https://cr-f.dk/</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t>Kibæk (Herning), Region Midtjylland</t>
+          <t>Bogense (Nordfyn), Region Syddanmark</t>
         </is>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>https://www.proff.dk/firma/cebeco-fourage-as/kib%C3%A6k/korn-r%C3%A5tobak-s%C3%A5varer-og-fodervarer-engros/0BOPPLI10P1 ; email da https://cebeco.dk/kontakt/</t>
+          <t>https://www.proff.dk/firma/cr-foderservice-ks/bogense/jordbrug/GT1OQ7I10OF/ ; email da https://118.dk/firma/Cr+Foderservice+KS/5400-Bogense</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>CR FODERSERVICE K/S</t>
+          <t>NORDVEST FODER A/S</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
@@ -18071,45 +18067,49 @@
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>16 dipendenti (2025); bruttofortjeneste 8,94 M DKK (2024) ≈ 1,2 M€, era 10,21 M DKK (2023); risultato 0,53 M DKK. Fatturato NON pubblicato (K/S, bilancio ridotto): la dimensione effettiva del giro d'affari e' verosimilmente superiore ma non documentabile. Fonte: proff.dk / lasso.dk, dati 2024. CVR 33078366. Miscelazione mangimi con unita' mobili presso l'allevamento (hjemmeblanding), acquisto di soia/materie prime proteiche. Sede: Huggetvej 27, 5400 Bogense, tel. +45 64 83 12 75.</t>
+          <t>Fatturato non pubblicato (su proff.dk il campo omsaetning risulta '-'); numero dipendenti n.d. Societa' controllata da Jysk Agri Holding A/S. Fonte: proff.dk (consultato 2026). CVR 14333045. Commercio all'ingrosso di cereali, sementi e materie prime per mangimi (NACE 46210) - operatore EUDR potenziale su soia. Due sedi: Tygstrupvej 1-3, 7770 Vestervig (tel. 97 94 18 44) e Skalmstrup.</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Niels Frost Rasmussen</t>
+          <t>Rasmus Toft</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>Direktør (fondatore)</t>
-        </is>
-      </c>
-      <c r="F78" s="5" t="inlineStr"/>
+          <t>adm. direktør</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>https://dk.linkedin.com/company/nordvest-foder-a-s</t>
+        </is>
+      </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>NFR@CR-F.dk</t>
+          <t>nordvestfoder@nordvestfoder.dk</t>
         </is>
       </c>
       <c r="H78" s="6" t="inlineStr">
         <is>
-          <t>https://cr-f.dk/</t>
+          <t>https://www.nordvestfoder.dk/</t>
         </is>
       </c>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>Bogense (Nordfyn), Region Syddanmark</t>
+          <t>Vestervig (Thisted, Thy), Region Nordjylland</t>
         </is>
       </c>
       <c r="J78" s="5" t="inlineStr">
         <is>
-          <t>https://www.proff.dk/firma/cr-foderservice-ks/bogense/jordbrug/GT1OQ7I10OF/ ; email da https://118.dk/firma/Cr+Foderservice+KS/5400-Bogense</t>
+          <t>https://www.proff.dk/firma/nordvest-foder-as/vestervig/n%C3%A6rings-og-nydelsesmidler/GJSZAMI116S ; email da https://www.nordvestfoder.dk/kontakt/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>NORDVEST FODER A/S</t>
+          <t>NUTRIMIN A/S</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -18119,141 +18119,141 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Fatturato non pubblicato (su proff.dk il campo omsaetning risulta '-'); numero dipendenti n.d. Societa' controllata da Jysk Agri Holding A/S. Fonte: proff.dk (consultato 2026). CVR 14333045. Commercio all'ingrosso di cereali, sementi e materie prime per mangimi (NACE 46210) - operatore EUDR potenziale su soia. Due sedi: Tygstrupvej 1-3, 7770 Vestervig (tel. 97 94 18 44) e Skalmstrup.</t>
+          <t>66 dipendenti; bruttofortjeneste 41,98 M DKK (2022, era 55,31 M DKK nel 2021), risultato netto 8,82 M DKK (2022). Fatturato non pubblicato (bilancio in forma ridotta) - taglia stimata nella fascia PMI ma DA VERIFICARE. Fonte: proff.dk, dati 2022. CVR 28513518. Terzo fornitore danese di premix vitaminico-minerali, concentrati, mangimi per suinetti e latte per vitelli (uso di soia/proteine vegetali). Sede operativa: Bodalen 11, 8643 Ans By, tel. +45 8750 0880. Controllata di Nutreco N.V. (gruppo SHV, Paesi Bassi) - Trouw Nutrition, dal 01/12/2021.</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>Rasmus Toft</t>
+          <t>Torben Jensen</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>adm. direktør</t>
+          <t>Adm. direktør</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/company/nordvest-foder-a-s</t>
+          <t>https://dk.linkedin.com/company/nutrimin-a-s</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>nordvestfoder@nordvestfoder.dk</t>
+          <t>info@nutrimin.dk</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>https://www.nordvestfoder.dk/</t>
+          <t>https://www.nutrimin.dk/</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr">
         <is>
-          <t>Vestervig (Thisted, Thy), Region Nordjylland</t>
+          <t>Ans By (Silkeborg), Region Midtjylland</t>
         </is>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>https://www.proff.dk/firma/nordvest-foder-as/vestervig/n%C3%A6rings-og-nydelsesmidler/GJSZAMI116S ; email da https://www.nordvestfoder.dk/kontakt/</t>
+          <t>https://www.proff.dk/firma/nutrimin-as/ans-by/foder/0GZ566I00FB ; email da https://www.nutrimin.dk/en/contact/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>NUTRIMIN A/S</t>
+          <t>TJØRNEHØJ MØLLE A/S</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>Mangimi/Soia</t>
+          <t>Mangimi/Soia — mangimi per suinetti e cavalli</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>66 dipendenti; bruttofortjeneste 41,98 M DKK (2022, era 55,31 M DKK nel 2021), risultato netto 8,82 M DKK (2022). Fatturato non pubblicato (bilancio in forma ridotta) - taglia stimata nella fascia PMI ma DA VERIFICARE. Fonte: proff.dk, dati 2022. CVR 28513518. Terzo fornitore danese di premix vitaminico-minerali, concentrati, mangimi per suinetti e latte per vitelli (uso di soia/proteine vegetali). Sede operativa: Bodalen 11, 8643 Ans By, tel. +45 8750 0880.</t>
-        </is>
-      </c>
-      <c r="D80" s="5" t="inlineStr">
-        <is>
-          <t>Torben Jensen</t>
-        </is>
-      </c>
-      <c r="E80" s="5" t="inlineStr">
-        <is>
-          <t>Adm. direktør</t>
-        </is>
-      </c>
-      <c r="F80" s="6" t="inlineStr">
-        <is>
-          <t>https://dk.linkedin.com/company/nutrimin-a-s</t>
-        </is>
-      </c>
-      <c r="G80" s="6" t="inlineStr">
-        <is>
-          <t>info@nutrimin.dk</t>
-        </is>
-      </c>
-      <c r="H80" s="6" t="inlineStr">
-        <is>
-          <t>https://www.nutrimin.dk/</t>
+          <t>DATO STORICO: fatturato lordo 80 M DKK ≈ 10,7 M€ nel 2003 (fonte: articolo Maskinbladet 'Foderspecialisten til smågrise'), di cui circa il 63% da miscele per lo svezzamento precoce dei suinetti. Produttore di mangimi per suini e cavalli. CVR, dati finanziari attuali, numero dipendenti e stato di attivita' NON VERIFICATI: lead da confermare su CVR/proff prima dell'uso. Il dato 2003 collocherebbe l'azienda nel target 10-20 M€ ma non e' attuale. Controllata del gruppo DLG (grande operatore, fuori target lead).</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr"/>
+      <c r="E80" s="5" t="inlineStr"/>
+      <c r="F80" s="5" t="inlineStr"/>
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>n.d.</t>
         </is>
       </c>
       <c r="I80" s="5" t="inlineStr">
         <is>
-          <t>Ans By (Silkeborg), Region Midtjylland</t>
+          <t>Hedehusene (Høje-Taastrup), Region Hovedstaden — DA CONFERMARE</t>
         </is>
       </c>
       <c r="J80" s="5" t="inlineStr">
         <is>
-          <t>https://www.proff.dk/firma/nutrimin-as/ans-by/foder/0GZ566I00FB ; email da https://www.nutrimin.dk/en/contact/</t>
+          <t>https://www.maskinbladet.dk/artikel/20250-foderspecialisten-til-smaagrise</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>TJØRNEHØJ MØLLE A/S</t>
+          <t>Naturli' Foods</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Mangimi/Soia — mangimi per suinetti e cavalli</t>
+          <t>Olio di palma</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>DATO STORICO: fatturato lordo 80 M DKK ≈ 10,7 M€ nel 2003 (fonte: articolo Maskinbladet 'Foderspecialisten til smågrise'), di cui circa il 63% da miscele per lo svezzamento precoce dei suinetti. Produttore di mangimi per suini e cavalli. CVR, dati finanziari attuali, numero dipendenti e stato di attivita' NON VERIFICATI: lead da confermare su CVR/proff prima dell'uso. Il dato 2003 collocherebbe l'azienda nel target 10-20 M€ ma non e' attuale.</t>
-        </is>
-      </c>
-      <c r="D81" s="3" t="inlineStr"/>
-      <c r="E81" s="3" t="inlineStr"/>
-      <c r="F81" s="3" t="inlineStr"/>
-      <c r="G81" s="3" t="inlineStr">
-        <is>
-          <t>n.d.</t>
-        </is>
-      </c>
-      <c r="H81" s="3" t="inlineStr">
-        <is>
-          <t>n.d.</t>
+          <t>n.d. (fatturato e dipendenti non pubblicati nelle fonti accessibili); produttore plant-based che dichiara l'uso di olio di palma certificato RSPO in parte della gamma; parte del gruppo Dragsbæk/Orkla (CVR 25476573)</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>Henrik Lund</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>adm. direktør</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/naturli-foods</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>info@naturli-foods.dk</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>https://www.naturli-foods.dk/</t>
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr">
         <is>
-          <t>Hedehusene (Høje-Taastrup), Region Hovedstaden — DA CONFERMARE</t>
+          <t>Vejen, Region Syddanmark</t>
         </is>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>https://www.maskinbladet.dk/artikel/20250-foderspecialisten-til-smaagrise</t>
+          <t>https://www.naturli-foods.com/faq/oils/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>Naturli' Foods</t>
+          <t>TBC INGREDIENTS ApS</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
@@ -18263,101 +18263,97 @@
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>n.d. (fatturato e dipendenti non pubblicati nelle fonti accessibili); produttore plant-based che dichiara l'uso di olio di palma certificato RSPO in parte della gamma; parte del gruppo Dragsbæk/Orkla (CVR 25476573)</t>
+          <t>Fatturato non pubblicato (n.d.); bruttofortjeneste 10,27 mio DKK (~1,4 M EUR); 4-5 dipendenti (2-10 secondo LinkedIn); importatore/rivenditore di oli vegetali con l'olio di palma come componente principale; oltre 150 mio kg di ingredienti/anno. Fonti: proff.dk (CVR 28119666), LinkedIn aziendale e piano d'azione palma su etiskhandel.dk (2021)</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Henrik Lund</t>
+          <t>Jens Aksel Christensen</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>adm. direktør</t>
+          <t>Direktør</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/naturli-foods</t>
+          <t>https://www.linkedin.com/company/tbc-ingredients-aps</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr">
         <is>
-          <t>info@naturli-foods.dk</t>
+          <t>info@tbcingr.com</t>
         </is>
       </c>
       <c r="H82" s="6" t="inlineStr">
         <is>
-          <t>https://www.naturli-foods.dk/</t>
+          <t>https://tbcingr.com/</t>
         </is>
       </c>
       <c r="I82" s="5" t="inlineStr">
         <is>
-          <t>Vejen, Region Syddanmark</t>
+          <t>Odder (Knudsminde 3B, 8300), Region Midtjylland</t>
         </is>
       </c>
       <c r="J82" s="5" t="inlineStr">
         <is>
-          <t>https://www.naturli-foods.com/faq/oils/</t>
+          <t>https://etiskhandel.dk/wp-content/uploads/Palmeoliehandlingsplan-tbc-ingredients-2021.pdf</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>TBC INGREDIENTS ApS</t>
+          <t>BØJE KØD ENGROS ApS (Bøje &amp; David Kød Engros)</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Olio di palma</t>
+          <t>Bovini/Carne</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>Fatturato non pubblicato (n.d.); bruttofortjeneste 10,27 mio DKK (~1,4 M EUR); 4-5 dipendenti (2-10 secondo LinkedIn); importatore/rivenditore di oli vegetali con l'olio di palma come componente principale; oltre 150 mio kg di ingredienti/anno. Fonti: proff.dk (CVR 28119666), LinkedIn aziendale e piano d'azione palma su etiskhandel.dk (2021)</t>
+          <t>Fatturato non pubblicato (n.d.); 17 dipendenti; grossista di carne per ristorazione/mense, fondata il 31.08.2000. ATTENZIONE: probabilmente sotto la fascia target. Fonti: proff.dk/ownr.dk (CVR 25588037)</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>Jens Aksel Christensen</t>
+          <t>Erik Bøje Andersen (co-direttore: David Sagik Rachdi Banks)</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>Direktør</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/tbc-ingredients-aps</t>
-        </is>
-      </c>
+          <t>Direktør e reale proprietario (50%)</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr"/>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>info@tbcingr.com</t>
+          <t>salg@bojekod.dk</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>https://tbcingr.com/</t>
+          <t>https://www.bojekod.dk/</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr">
         <is>
-          <t>Odder (Knudsminde 3B, 8300), Region Midtjylland</t>
+          <t>Kastrup (Kirstinehøj 75, 2770), Region Hovedstaden</t>
         </is>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>https://etiskhandel.dk/wp-content/uploads/Palmeoliehandlingsplan-tbc-ingredients-2021.pdf</t>
+          <t>https://www.proff.dk/firma/b%C3%B8je-k%C3%B8d-engros-aps/kastrup/k%C3%B8d-og-vildt-engros/GO2BIII10OV</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>BØJE KØD ENGROS ApS (Bøje &amp; David Kød Engros)</t>
+          <t>Grambogård</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
@@ -18367,45 +18363,49 @@
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>Fatturato non pubblicato (n.d.); 17 dipendenti; grossista di carne per ristorazione/mense, fondata il 31.08.2000. ATTENZIONE: probabilmente sotto la fascia target. Fonti: proff.dk/ownr.dk (CVR 25588037)</t>
+          <t>Fatturato ca. 45 mio DKK (~6,0 M EUR); macello/lavorazione carni con linea bovina da manze e manzi. Fonte: effektivtlandbrug.landbrugnet.dk, articolo 2023 Controllata di FoodService Danmark A/S (gruppo Dagrofa).</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Erik Bøje Andersen (co-direttore: David Sagik Rachdi Banks)</t>
+          <t>Niels Beier</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>Direktør e reale proprietario (50%)</t>
-        </is>
-      </c>
-      <c r="F84" s="5" t="inlineStr"/>
+          <t>Direktør</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/grambogaard</t>
+        </is>
+      </c>
       <c r="G84" s="6" t="inlineStr">
         <is>
-          <t>salg@bojekod.dk</t>
+          <t>info@grambogaard.dk</t>
         </is>
       </c>
       <c r="H84" s="6" t="inlineStr">
         <is>
-          <t>https://www.bojekod.dk/</t>
+          <t>https://grambogaard.dk/</t>
         </is>
       </c>
       <c r="I84" s="5" t="inlineStr">
         <is>
-          <t>Kastrup (Kirstinehøj 75, 2770), Region Hovedstaden</t>
+          <t>Tommerup (Fyn), Region Syddanmark</t>
         </is>
       </c>
       <c r="J84" s="5" t="inlineStr">
         <is>
-          <t>https://www.proff.dk/firma/b%C3%B8je-k%C3%B8d-engros-aps/kastrup/k%C3%B8d-og-vildt-engros/GO2BIII10OV</t>
+          <t>https://effektivtlandbrug.landbrugnet.dk/artikler/svin/85640/-det-handler-om-smag-og-kvalitet</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>Grambogård</t>
+          <t>JN Meat International</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -18415,49 +18415,49 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>Fatturato ca. 45 mio DKK (~6,0 M EUR); macello/lavorazione carni con linea bovina da manze e manzi. Fonte: effektivtlandbrug.landbrugnet.dk, articolo 2023</t>
+          <t>Fatturato non pubblicato (n.d.); 70 dipendenti; sezionamento proprio di carne bovina e di vitello (marchio SASHI). Fonti: jnmeat.dk e LinkedIn aziendale</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>Niels Beier</t>
+          <t>John Sashi Nielsen</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>Direktør</t>
+          <t>adm. direktør</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/grambogaard</t>
+          <t>https://dk.linkedin.com/company/jnmeat</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>info@grambogaard.dk</t>
+          <t>ordre@jnmeat.dk</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>https://grambogaard.dk/</t>
+          <t>https://jnmeat.dk/</t>
         </is>
       </c>
       <c r="I85" s="3" t="inlineStr">
         <is>
-          <t>Tommerup (Fyn), Region Syddanmark</t>
+          <t>Slagelse, Region Sjælland</t>
         </is>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>https://effektivtlandbrug.landbrugnet.dk/artikler/svin/85640/-det-handler-om-smag-og-kvalitet</t>
+          <t>https://jnmeat.dk/en</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>JN Meat International</t>
+          <t>Randers Kød Engros ApS</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
@@ -18467,95 +18467,43 @@
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>Fatturato non pubblicato (n.d.); 70 dipendenti; sezionamento proprio di carne bovina e di vitello (marchio SASHI). Fonti: jnmeat.dk e LinkedIn aziendale</t>
+          <t>Fatturato non pubblicato (n.d.); ca. 51 dipendenti (38 FTE); grossista di carne dal 1976, gamma con oksekød/kalvekød. Fonti: estatistik.dk e proff.dk (CVR 25539222)</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>John Sashi Nielsen</t>
+          <t>Kaspar Kærskov Jakobsen</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>adm. direktør</t>
-        </is>
-      </c>
-      <c r="F86" s="6" t="inlineStr">
-        <is>
-          <t>https://dk.linkedin.com/company/jnmeat</t>
-        </is>
-      </c>
+          <t>Direktør (dal 21.01.2015)</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="inlineStr"/>
       <c r="G86" s="6" t="inlineStr">
         <is>
-          <t>ordre@jnmeat.dk</t>
+          <t>salg@randerskoed.dk</t>
         </is>
       </c>
       <c r="H86" s="6" t="inlineStr">
         <is>
-          <t>https://jnmeat.dk/</t>
+          <t>https://randerskoed.dk/</t>
         </is>
       </c>
       <c r="I86" s="5" t="inlineStr">
         <is>
-          <t>Slagelse, Region Sjælland</t>
+          <t>Randers, Region Midtjylland</t>
         </is>
       </c>
       <c r="J86" s="5" t="inlineStr">
         <is>
-          <t>https://jnmeat.dk/en</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="3" t="inlineStr">
-        <is>
-          <t>Randers Kød Engros ApS</t>
-        </is>
-      </c>
-      <c r="B87" s="3" t="inlineStr">
-        <is>
-          <t>Bovini/Carne</t>
-        </is>
-      </c>
-      <c r="C87" s="3" t="inlineStr">
-        <is>
-          <t>Fatturato non pubblicato (n.d.); ca. 51 dipendenti (38 FTE); grossista di carne dal 1976, gamma con oksekød/kalvekød. Fonti: estatistik.dk e proff.dk (CVR 25539222)</t>
-        </is>
-      </c>
-      <c r="D87" s="3" t="inlineStr">
-        <is>
-          <t>Kaspar Kærskov Jakobsen</t>
-        </is>
-      </c>
-      <c r="E87" s="3" t="inlineStr">
-        <is>
-          <t>Direktør (dal 21.01.2015)</t>
-        </is>
-      </c>
-      <c r="F87" s="3" t="inlineStr"/>
-      <c r="G87" s="4" t="inlineStr">
-        <is>
-          <t>salg@randerskoed.dk</t>
-        </is>
-      </c>
-      <c r="H87" s="4" t="inlineStr">
-        <is>
           <t>https://randerskoed.dk/</t>
         </is>
       </c>
-      <c r="I87" s="3" t="inlineStr">
-        <is>
-          <t>Randers, Region Midtjylland</t>
-        </is>
-      </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>https://randerskoed.dk/</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:J87"/>
+  <autoFilter ref="A2:J86"/>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
@@ -18649,63 +18597,63 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId87"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId93"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId97"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId106"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId107"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId111"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId116"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId117"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId119"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F51" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId127"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId128"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId129"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId130"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F55" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId137"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId138"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId139"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F57" r:id="rId140"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId141"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId142"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F58" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F59" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F59" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId146"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId147"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F60" r:id="rId148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId149"/>
@@ -18719,9 +18667,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F63" r:id="rId157"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId158"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F64" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F65" r:id="rId162"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId163"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId164"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F66" r:id="rId165"/>
@@ -18736,9 +18684,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F69" r:id="rId174"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId175"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F70" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F71" r:id="rId179"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId180"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId181"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F72" r:id="rId182"/>
@@ -18747,37 +18695,34 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F73" r:id="rId185"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId186"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F74" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F78" r:id="rId194"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId195"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId196"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F79" r:id="rId197"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId198"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F80" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F81" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId202"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F82" r:id="rId203"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId204"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F83" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F84" r:id="rId208"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId209"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId210"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F85" r:id="rId211"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId212"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F86" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId215"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18976,7 +18921,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>≈7,9 M€ / 12 dip. (allabolag: 89 711 KSEK) · org.nr 556081-8782 · sotto la fascia target 10-20 M€, tenuta per copertura · produzione ~40 000 m³/anno</t>
+          <t>≈7,9 M€ / 12 dip. (allabolag: 89 711 KSEK) · org.nr 556081-8782 · sotto la fascia target 10-20 M€, tenuta per copertura · produzione ~40 000 m³/anno Koncern di 2 società, moderbolag Karlaträ Försäljning AB (holding di vendita del medesimo gruppo familiare).</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -19028,7 +18973,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>≈10,1 M€ / 38 dip. (allabolag 2025: 114 525 KSEK) · org.nr 556637-7171 · legame di gruppo: controllata di Green Wood Sverige AB (stessa proprietà di Bäckebrons e Nordanå Trä) · calo -70,1% sul 2024, verificare durata esercizio</t>
+          <t>≈10,1 M€ / 38 dip. (allabolag 2025: 114 525 KSEK) · org.nr 556637-7171 · legame di gruppo: controllata di Green Wood Sverige AB (stessa proprietà di Bäckebrons e Nordanå Trä) · calo -70,1% sul 2024, verificare durata esercizio Controllata di Green Wood Sverige AB; koncernmoderbolag Profuragruppen AB (dal 2025, dopo il fallimento di Ziegler Group).</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -19180,7 +19125,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>≈12,7 M€ / 32 dip. (allabolag/bolagsfakta 2024: 143 413 KSEK, +25,6%) · org.nr 556415-5066 · membro SÅGAB-Sågverken Norrland · target ideale</t>
+          <t>≈12,7 M€ / 32 dip. (allabolag/bolagsfakta 2024: 143 413 KSEK, +25,6%) · org.nr 556415-5066 · membro SÅGAB-Sågverken Norrland · target ideale Koncern con moderbolag Brattby Trading Aktiebolag.</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -19324,7 +19269,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>≈12,6 M€ / 39 dip. (allabolag 2025: 142 474 KSEK) · org.nr 556099-7008 · NOTA: nel 2023 il fatturato era 326 MSEK (≈29 M€), calo -66,7% nel 2025 (possibile esercizio ridotto) · legame di gruppo: controllata di Green Wood Sverige AB, capogruppo Ziegler Holding GmbH</t>
+          <t>≈12,6 M€ / 39 dip. (allabolag 2025: 142 474 KSEK) · org.nr 556099-7008 · NOTA: nel 2023 il fatturato era 326 MSEK (≈29 M€), calo -66,7% nel 2025 (possibile esercizio ridotto) · legame di gruppo: controllata di Green Wood Sverige AB, capogruppo Ziegler Holding GmbH Controllata di Green Wood Sverige AB; koncernmoderbolag Profuragruppen AB (dopo il fallimento di Ziegler Group).</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -19376,7 +19321,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Fatturato 83.213 KSEK (~7,4 M€) e 74 dipendenti nel 2025 (fonte allabolag.se). Org.nr 556309-7038 (ex Trätrappor Norsjö AB). Sotto il target 10-20 M€ ma dentro la fascia tollerata.</t>
+          <t>Fatturato 83.213 KSEK (~7,4 M€) e 74 dipendenti nel 2025 (fonte allabolag.se). Org.nr 556309-7038 (ex Trätrappor Norsjö AB). Sotto il target 10-20 M€ ma dentro la fascia tollerata. Moderbolag Förvaltnings AB Klätterbjörken; fatturato in calo da 126,4 MSEK (2024) a 83,2 MSEK (2025).</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -19580,7 +19525,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Fatturato 165 564 KSEK = 165,6 MSEK ≈ 14,7 M€ (2024, -6,4%); 78 dipendenti (2024); org.nr 556120-7837 – fonte allabolag.se. Pienamente in target. Legame di gruppo: controllata di Garpco AB, con 2 sub-controllate; ha acquisito Fanerami Sweden (impiallacciature)</t>
+          <t>Fatturato 165 564 KSEK = 165,6 MSEK ≈ 14,7 M€ (2024, -6,4%); 78 dipendenti (2024); org.nr 556120-7837 – fonte allabolag.se. Pienamente in target. Legame di gruppo: controllata di Garpco AB, con 2 sub-controllate; ha acquisito Fanerami Sweden (impiallacciature) Controllata di Garpco Aktiebolag (dal 2007), koncern di 25 società / 311 addetti / 667 MSEK.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -19732,7 +19677,7 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Fatturato 140.766 KSEK (~12,5 M€) e 86 dipendenti nel 2025 (fonte allabolag.se). Org.nr 556232-9135. Pienamente in target. Azionista di controllo: gruppo Pulsen (dal 2011).</t>
+          <t>Fatturato 140.766 KSEK (~12,5 M€) e 86 dipendenti nel 2025 (fonte allabolag.se). Org.nr 556232-9135. Pienamente in target. Azionista di controllo: gruppo Pulsen (dal 2011). Perdita d'esercizio 2025 (marginalità -32,6%); koncern Pulsen AB, 56 società.</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -19780,7 +19725,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Fatturato 103 MSEK ≈ 9,1 M€ (esercizio 2022, +77% sul 2021); 50 dipendenti (2022, +11 sull'anno precedente); org.nr 556365-1974 – fonte allabolag.se / Mark-Posten. ATTENZIONE: dato non aggiornato al 2024, da riverificare. Fa parte di un gruppo di 3 società</t>
+          <t>Fatturato 103 MSEK ≈ 9,1 M€ (esercizio 2022, +77% sul 2021); 50 dipendenti (2022, +11 sull'anno precedente); org.nr 556365-1974 – fonte allabolag.se / Mark-Posten. ATTENZIONE: dato non aggiornato al 2024, da riverificare. Fa parte di un gruppo di 3 società Capogruppo Horreds Holding AB / Horreds Möbel Utvecklings AB (org.nr 559016-3324), gruppo di 3 società.</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -19832,7 +19777,7 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Fatturato 251 117 KSEK = 251,1 MSEK ≈ 22,2 M€ (2024); 70 dipendenti (2024; 80 a marzo 2025); org.nr 556358-5206 – fonte allabolag.se. Azienda di confine: leggermente sopra il target ideale 10-20 M€ ma entro la fascia tollerabile 5-40 M€</t>
+          <t>Fatturato 251 117 KSEK = 251,1 MSEK ≈ 22,2 M€ (2024); 70 dipendenti (2024; 80 a marzo 2025); org.nr 556358-5206 – fonte allabolag.se. Azienda di confine: leggermente sopra il target ideale 10-20 M€ ma entro la fascia tollerabile 5-40 M€ Capogruppo Johanson Design Invest Aktiebolag (org.nr 556691-6457), gruppo di 5 società; 3 controllate dirette.</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -20136,7 +20081,7 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Fatturato 79 707 KSEK = 79,7 MSEK ≈ 7,1 M€ (2025); risultato 166 KSEK; 14 dipendenti; org.nr 556249-9177 – fonte allabolag.se. Sotto il target ideale ma entro la fascia tollerabile. Attività di produzione mobili ufficio + commercio all'ingrosso (SNI 46471): rilevante come operatore EUDR</t>
+          <t>Fatturato 79 707 KSEK = 79,7 MSEK ≈ 7,1 M€ (2025); risultato 166 KSEK; 14 dipendenti; org.nr 556249-9177 – fonte allabolag.se. Sotto il target ideale ma entro la fascia tollerabile. Attività di produzione mobili ufficio + commercio all'ingrosso (SNI 46471): rilevante come operatore EUDR Capogruppo Materia Group AB (gruppo di arredo); lead da valutare a livello di capogruppo.</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -20236,7 +20181,7 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Fatturato 86 155 KSEK = 86,2 MSEK ≈ 7,6 M€ (2024, -2,6%); risultato 2 629 KSEK; 22 dipendenti; org.nr 556207-4442 – fonte allabolag.se. Sotto il target ideale ma entro la fascia tollerabile</t>
+          <t>Fatturato 86 155 KSEK = 86,2 MSEK ≈ 7,6 M€ (2024, -2,6%); risultato 2 629 KSEK; 22 dipendenti; org.nr 556207-4442 – fonte allabolag.se. Sotto il target ideale ma entro la fascia tollerabile Capogruppo Sentensen Aktiebolag (gruppo di 3 società, 88,0 MSEK).</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -20444,7 +20389,7 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>≈28,6 M€ / 41 dip. (allabolag 2023: 323 425 KSEK; 2022: 364 MSEK) · org.nr 556075-2825 · azienda di confine sulla fascia alta del range tollerabile · segheria familiare dal 1908, ~100 000 m³/anno</t>
+          <t>≈28,6 M€ / 41 dip. (allabolag 2023: 323 425 KSEK; 2022: 364 MSEK) · org.nr 556075-2825 · azienda di confine sulla fascia alta del range tollerabile · segheria familiare dal 1908, ~100 000 m³/anno Capogruppo Nydala Trä Holding AB (gruppo di 2 società).</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -20644,7 +20589,7 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Fatturato 67 063 KSEK = 67,1 MSEK ≈ 5,9 M€ (2024; 60 142 KSEK nel 2023); 27-29 dipendenti; org.nr 556085-1825 – fonte allabolag.se. Azienda di confine: appena sopra la soglia minima di 5 M€. Legame di gruppo: capogruppo Idun Woodcraft AB; controllata Svenska Hyvelbänkar. Produzione di banchi, mobili e componenti in legno massello</t>
+          <t>Fatturato 67 063 KSEK = 67,1 MSEK ≈ 5,9 M€ (2024; 60 142 KSEK nel 2023); 27-29 dipendenti; org.nr 556085-1825 – fonte allabolag.se. Azienda di confine: appena sopra la soglia minima di 5 M€. Legame di gruppo: capogruppo Idun Woodcraft AB; controllata Svenska Hyvelbänkar. Produzione di banchi, mobili e componenti in legno massello Gruppo Idun Woodcraft AB, 74 società (gruppo Idun).</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -20748,7 +20693,7 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>≈14,6 M€ / 26 dip. (allabolag 2023: 164 742 KSEK; 2022: 187 418 KSEK con 31 dip.) · org.nr 556136-0248 · ex Rydaholms Träförädling AB · target ideale</t>
+          <t>≈14,6 M€ / 26 dip. (allabolag 2023: 164 742 KSEK; 2022: 187 418 KSEK con 31 dip.) · org.nr 556136-0248 · ex Rydaholms Träförädling AB · target ideale Controllata da Green Wood Sverige AB (org.nr 559248-6616), holding del legno con sede a Sunne.</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -20796,7 +20741,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>≈26 M€ / 15 dip. (fatturato 296,6 MSEK, riconoscimento Gasell Dagens Industri; allabolag 2020: 98 352 KSEK) · org.nr 556579-8435 · crescita +269% in 4 anni, azienda di confine sulla fascia alta · produzione ~70 000 m³/anno</t>
+          <t>≈26 M€ / 15 dip. (fatturato 296,6 MSEK, riconoscimento Gasell Dagens Industri; allabolag 2020: 98 352 KSEK) · org.nr 556579-8435 · crescita +269% in 4 anni, azienda di confine sulla fascia alta · produzione ~70 000 m³/anno Controllata dal gruppo Stockhult (Stockhult Timber AB / Stockhult Holding AB).</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -20848,7 +20793,7 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Fatturato 83,3 MSEK ≈ 7,4 M€ (2024; risultato -5,6 MSEK); 50 dipendenti (2024); org.nr 556182-5224 – fonte allabolag.se / proff.se. Sotto il target ideale ma entro la fascia tollerabile. Ha acquisito Albin i Hyssna (produzione svedese)</t>
+          <t>Fatturato 83,3 MSEK ≈ 7,4 M€ (2024; risultato -5,6 MSEK); 50 dipendenti (2024); org.nr 556182-5224 – fonte allabolag.se / proff.se. Sotto il target ideale ma entro la fascia tollerabile. Ha acquisito Albin i Hyssna (produzione svedese) Capogruppo Martinvest i Smålandsstenar AB / Moid AB (holding familiare, 4 società).</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -20900,7 +20845,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Fatturato 101.636 KSEK (~9,0 M€) e 40 dipendenti nel 2024 (fonte allabolag.se). Org.nr 556708-7282. Di poco sotto il target 10-20 M€, dentro la fascia tollerata.</t>
+          <t>Fatturato 101.636 KSEK (~9,0 M€) e 40 dipendenti nel 2024 (fonte allabolag.se). Org.nr 556708-7282. Di poco sotto il target 10-20 M€, dentro la fascia tollerata. Controllata da Sunnerbo Windows &amp; Doors AB (org.nr 556986-4902); esercizio 2024 in perdita -1,3 MSEK.</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -20948,7 +20893,7 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Fatturato 165 761 KSEK = 165,8 MSEK ≈ 14,7 M€ (2024, -1,3%); risultato 4 153 KSEK; 87 dipendenti (2024); org.nr 556280-1323 – fonte allabolag.se. Pienamente in target 10-20 M€</t>
+          <t>Fatturato 165 761 KSEK = 165,8 MSEK ≈ 14,7 M€ (2024, -1,3%); risultato 4 153 KSEK; 87 dipendenti (2024); org.nr 556280-1323 – fonte allabolag.se. Pienamente in target 10-20 M€ Capogruppo Patino Group AB (holding della proprietà).</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -21000,7 +20945,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Fatturato 151.086 KSEK (~13,4 M€) e 53 dipendenti nel 2024 (fonte allabolag.se). Org.nr 556477-6911. Pienamente in target. Fa parte del gruppo SVENSKA HUSCOMPAGNIET AB (7 società).</t>
+          <t>Fatturato 151.086 KSEK (~13,4 M€) e 53 dipendenti nel 2024 (fonte allabolag.se). Org.nr 556477-6911. Pienamente in target. Fa parte del gruppo SVENSKA HUSCOMPAGNIET AB (7 società). Controllata del gruppo danese HusCompagniet A/S tramite Svenska HusCompagniet AB — lead da valutare a livello di capogruppo.</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -21140,7 +21085,7 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Fatturato 123,4 MSEK ≈ 10,9 M€ (esercizio 2025; 106 963 KSEK nel 2023); risultato operativo 9,1 MSEK; 20 dipendenti (2023), 28 a livello di gruppo; org.nr 556651-5689 – fonte allabolag.se/proff.se. Pienamente in target</t>
+          <t>Fatturato 123,4 MSEK ≈ 10,9 M€ (esercizio 2025; 106 963 KSEK nel 2023); risultato operativo 9,1 MSEK; 20 dipendenti (2023), 28 a livello di gruppo; org.nr 556651-5689 – fonte allabolag.se/proff.se. Pienamente in target Capogruppo ZilenZio Selling Silence AB / Easier AB.</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -21240,7 +21185,7 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>≈22,6 M€ / 80 dip. (allabolag 2024: 255 909 KSEK) · org.nr 556093-5156 · maggior produttore svedese di pallet (HS 4415, Allegato I EUDR) · fascia alta del range tollerabile</t>
+          <t>≈22,6 M€ / 80 dip. (allabolag 2024: 255 909 KSEK) · org.nr 556093-5156 · maggior produttore svedese di pallet (HS 4415, Allegato I EUDR) · fascia alta del range tollerabile Capogruppo Åsljunga-Pallen Service Aktiebolag (org.nr 556398-3211).</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -21292,7 +21237,7 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Fatturato 282.998 KSEK (~25,0 M€) e 81 dipendenti — bilancio 2024 (fonte allabolag/bolagsfakta); org.nr 556051-6188. Sopra la fascia ideale ma entro il tollerabile.</t>
+          <t>Fatturato 282.998 KSEK (~25,0 M€) e 81 dipendenti — bilancio 2024 (fonte allabolag/bolagsfakta); org.nr 556051-6188. Sopra la fascia ideale ma entro il tollerabile. Capogruppo Janmon AB.</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -21436,7 +21381,7 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Fatturato 118.377 KSEK (~10,5 M€) e 39-42 dipendenti — ultimo esercizio disponibile 2024/2025 (fonte allabolag/bolagsfakta); org.nr 556068-0448. In pieno target.</t>
+          <t>Fatturato 118.377 KSEK (~10,5 M€) e 39-42 dipendenti — ultimo esercizio disponibile 2024/2025 (fonte allabolag/bolagsfakta); org.nr 556068-0448. In pieno target. Capogruppo Rubber Förvaltning Aktiebolag (gruppo di 5 società).</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -21540,7 +21485,7 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Fatturato 91.326 KSEK (~8,1 M€) e 42 dipendenti — fonte allabolag/bolagsfakta, es. 2023. Org.nr 556239-7090. AZIENDA DI CONFINE: sotto il target 10-20 M€ ma dentro la fascia tollerabile 5-40 M€. Nota: la stessa entità compare anche come Bording PurePrint AB; legame con il gruppo danese Bording.</t>
+          <t>Fatturato 91.326 KSEK (~8,1 M€) e 42 dipendenti — fonte allabolag/bolagsfakta, es. 2023. Org.nr 556239-7090. AZIENDA DI CONFINE: sotto il target 10-20 M€ ma dentro la fascia tollerabile 5-40 M€. Nota: la stessa entità compare anche come Bording PurePrint AB; legame con il gruppo danese Bording. Controllata di F E Bording A/S (DK) — lead da valutare a livello di capogruppo danese.</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -21592,7 +21537,7 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Fatturato 127.623 KSEK (~11,3 M€) e 10 dipendenti — fonte allabolag/bolagsfakta, es. 2024. Org.nr 556262-9211. IN TARGET per fatturato, ma organico ridotto (modello distributivo/commerciale su soluzioni di imballaggio). Nota legame di gruppo: capogruppo S-Pack AB.</t>
+          <t>Fatturato 127.623 KSEK (~11,3 M€) e 10 dipendenti — fonte allabolag/bolagsfakta, es. 2024. Org.nr 556262-9211. IN TARGET per fatturato, ma organico ridotto (modello distributivo/commerciale su soluzioni di imballaggio). Nota legame di gruppo: capogruppo S-Pack AB. Capogruppo operativa S-Pack AB (aPak AB, Crispo Paper AB, Econopack AB); capogruppo ultima Lameja Invest AB; gruppo 8 societa', 100 dip., 930 MSEK.; Interlocutore compliance da valutare a livello S-Pack.</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
@@ -21748,7 +21693,7 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Fatturato 264.323 KSEK (~23,4 M€) e 54 dipendenti — fonte allabolag/bolagsfakta, es. 2024. Org.nr 556530-3228. AZIENDA DI CONFINE: sopra il target 10-20 M€ ma dentro la fascia tollerabile 5-40 M€. Cartiera (produzione di carta e locazione immobili), sede Bruksallén 9, Klippan, tel. 0435-291 00; presidente Stefan Uno Sundh, VD Jan Mauritzson (nominato dal 1° novembre 2021, fonte comunicato klippansbruk.se/lesprom). Lo stabilimento opera storicamente anche sotto l'insegna Svenska Pappersbruket AB.</t>
+          <t>Fatturato 264.323 KSEK (~23,4 M€) e 54 dipendenti — fonte allabolag/bolagsfakta, es. 2024. Org.nr 556530-3228. AZIENDA DI CONFINE: sopra il target 10-20 M€ ma dentro la fascia tollerabile 5-40 M€. Cartiera (produzione di carta e locazione immobili), sede Bruksallén 9, Klippan, tel. 0435-291 00; presidente Stefan Uno Sundh, VD Jan Mauritzson (nominato dal 1° novembre 2021, fonte comunicato klippansbruk.se/lesprom). Lo stabilimento opera storicamente anche sotto l'insegna Svenska Pappersbruket AB. Capogruppo Sundh Center AB (holding di proprieta' della famiglia Sundh).</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
@@ -21800,7 +21745,7 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Fatturato 122.940 KSEK (~10,9 M€) e 42 dipendenti — fonte allabolag/bolagssoket, es. 2024. Org.nr 556323-6776 (da riverificare: fonti aggregate riportano numerazioni divergenti). IN TARGET. Nota legame di gruppo: collegata a Scandinavian Print Group (proprietà danese); VD non pubblicato nelle fonti consultate — in cda risultano Henrik Corvenius Frydendahl ed Esben Mols Kabell.</t>
+          <t>Fatturato 122.940 KSEK (~10,9 M€) e 42 dipendenti — fonte allabolag/bolagssoket, es. 2024. Org.nr 556323-6776 (da riverificare: fonti aggregate riportano numerazioni divergenti). IN TARGET. Nota legame di gruppo: collegata a Scandinavian Print Group (proprietà danese); VD non pubblicato nelle fonti consultate — in cda risultano Henrik Corvenius Frydendahl ed Esben Mols Kabell. Controllata (100%) di Scandinavian Print Group (DK) dal 1/9/2021; capogruppo di riferimento per la compliance: Scandinavian Print Group.</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr"/>
@@ -22464,7 +22409,7 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Fatturato 54,7 MSEK (~4,8 M€) 2024 (+8,4%); 17 dipendenti (14 nel 2023) (fonte: allabolag.se, bilancio 2024). Org.nr 556083-2379. SNI 46370 kaffe/te agenturer. Taglia appena sotto la fascia tollerabile ma importatore/agente puro.</t>
+          <t>Fatturato 54,7 MSEK (~4,8 M€) 2024 (+8,4%); 17 dipendenti (14 nel 2023) (fonte: allabolag.se, bilancio 2024). Org.nr 556083-2379. SNI 46370 kaffe/te agenturer. Taglia appena sotto la fascia tollerabile ma importatore/agente puro. Capogruppo WB Stockholm AB (org.nr 556705-8754, stessa sede) - holding/operativa di proprieta familiare; gruppo di 5 societa, 3 controllate.</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr"/>
@@ -22648,7 +22593,7 @@
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Fatturato 396,6 MSEK (~35,1 M€) esercizio 2025 (+12,2%); 125 dipendenti (fonte: allabolag.se / bolagsfakta.se). Org.nr 556119-4720. Gruppo di 8 società, capogruppo Belvéns Bageri AB. Entro la fascia tollerabile (5-40 M€).</t>
+          <t>Fatturato 396,6 MSEK (~35,1 M€) esercizio 2025 (+12,2%); 125 dipendenti (fonte: allabolag.se / bolagsfakta.se). Org.nr 556119-4720. Gruppo di 8 società, capogruppo Belvéns Bageri AB. Entro la fascia tollerabile (5-40 M€). Moderbolag diretto Belveens Bageri AB; capogruppo di vertice Eldkvarn AB (gruppo di 8 societa)'.</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
@@ -22700,7 +22645,7 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Fatturato 259,7 MSEK (~23,0 M€) 2024; 208,6 MSEK 2023; 60-65 dipendenti (fonte: allabolag.se / bolagsfakta.se). Org.nr 556724-8884.</t>
+          <t>Fatturato 259,7 MSEK (~23,0 M€) 2024; 208,6 MSEK 2023; 60-65 dipendenti (fonte: allabolag.se / bolagsfakta.se). Org.nr 556724-8884. Controllata dal gruppo quotato Humble Group AB - compliance decisa a livello di capogruppo. Esercizio 2024 in perdita (-2,2 MSEK) nonostante +24,5% di fatturato'.</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
@@ -23080,7 +23025,7 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Fatturato 346.300 KSEK (~30,6 M€) nel 2024 e 93-98 dipendenti (93 nel 2023, fatturato 375.373 KSEK) (fonte bolagsfakta/allabolag); org.nr 556041-6348. Sopra la fascia ideale ma entro il tollerabile.</t>
+          <t>Fatturato 346.300 KSEK (~30,6 M€) nel 2024 e 93-98 dipendenti (93 nel 2023, fatturato 375.373 KSEK) (fonte bolagsfakta/allabolag); org.nr 556041-6348. Sopra la fascia ideale ma entro il tollerabile. Controllata via Liljeholmens Group AB / ALG Holding AB, capogruppo di vertice Tibia Intressenter AB; controlla Liljeholmens Fastighets AB e ASP-HOLMBLAD A/S (DK). Fatturato 2024 in calo dell'8% sul 2023'.</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
@@ -23172,7 +23117,7 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>Fatturato 222.064 KSEK (~19,7 M€) e 81 dipendenti — bilancio 2024 (fonte bolagsfakta/allabolag); org.nr 559256-8256. In pieno target.</t>
+          <t>Fatturato 222.064 KSEK (~19,7 M€) e 81 dipendenti — bilancio 2024 (fonte bolagsfakta/allabolag); org.nr 559256-8256. In pieno target. Capogruppo Siljans Chark Holding AB (holding dei soci Par Nilsson e Mats Arjes); societa subentrata alla precedente Siljans Chark dopo il fallimento; controlla Norrlandsgarden AB e Siljanfood AB'.</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
@@ -23220,7 +23165,7 @@
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>Fatturato 209.054 KSEK (~18,5 M€) e 27 dipendenti — bilancio 2024 (fonte bolagsfakta/allabolag); org.nr 556514-4861. In pieno target.</t>
+          <t>Fatturato 209.054 KSEK (~18,5 M€) e 27 dipendenti — bilancio 2024 (fonte bolagsfakta/allabolag); org.nr 556514-4861. In pieno target. Controllata da Kott &amp; Charkgruppen i Narke AB (gruppo di 5 societa)'.</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
@@ -25849,7 +25794,7 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Fatturato ca. 15,5 M€ (fonte bedrijvenregister.nl, dato 2017 - ultimo pubblicato; bilanci recenti depositati in forma abbreviata). 21-50 dipendenti (fonte bedrijvenregister.nl / drukkerij-gids.nl, 2024). KVK 05071502. Tipografia offset e legatoria (brochure, riviste, cataloghi, libri). Direzione condivisa con Erwin de Lange dal 2002. Partecipazione di minoranza della società di investimento Wadinko NV — legame di gruppo parziale.</t>
+          <t>Fatturato ca. 15,5 M€ (fonte bedrijvenregister.nl, dato 2017 - ultimo pubblicato; bilanci recenti depositati in forma abbreviata). 21-50 dipendenti (fonte bedrijvenregister.nl / drukkerij-gids.nl, 2024). KVK 05071502. Tipografia offset e legatoria (brochure, riviste, cataloghi, libri). Direzione condivisa con Erwin de Lange dal 2002. Partecipazione di minoranza della società di investimento Wadinko NV — legame di gruppo parziale. Partecipazione di minoranza Wadinko NV dal dicembre 2023.</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -26145,7 +26090,7 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Fatturato ~4,8 M€ con 40 dipendenti (fonte: New10, articolo aziendale). Sede Kerkstraat 96 Amsterdam, torrefazione a Dronten; primo specialty roaster olandese, B Corp. SOTTO la fascia 5-40 M€ (borderline). Nota legame: il fondatore Menno Simons è anche fondatore dell'importatore di caffè verde Trabocca B.V.</t>
+          <t>Fatturato ~4,8 M€ con 40 dipendenti (fonte: New10, articolo aziendale). Sede Kerkstraat 96 Amsterdam, torrefazione a Dronten; primo specialty roaster olandese, B Corp. SOTTO la fascia 5-40 M€ (borderline). Nota legame: il fondatore Menno Simons è anche fondatore dell'importatore di caffè verde Trabocca B.V. Acquisizione di Single Estate Coffee Roasters da Cavesco; fatturato e organico da riaggiornare post-operazione.</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -30481,7 +30426,7 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>DATO DI FATTURATO NON REPERITO su fonti pubbliche accessibili (bilancio NBB da consultare direttamente). Produttore indipendente di imballaggi in cartone ondulato su misura (scatole americane stampate e imballaggi industriali pesanti), fondato nel 1994, rivolto specificamente alle PMI; stabilimento di 10.000 m² dal 2000. Sede Doornpark 20, 9120 Beveren-Waas. Certificata FSC. DA QUALIFICARE: dimensione presumibilmente nella fascia bassa 5-15 M€, da verificare.</t>
+          <t>DATO DI FATTURATO NON REPERITO su fonti pubbliche accessibili (bilancio NBB da consultare direttamente). Produttore indipendente di imballaggi in cartone ondulato su misura (scatole americane stampate e imballaggi industriali pesanti), fondato nel 1994, rivolto specificamente alle PMI; stabilimento di 10.000 m² dal 2000. Sede Doornpark 20, 9120 Beveren-Waas. Certificata FSC. DA QUALIFICARE: dimensione presumibilmente nella fascia bassa 5-15 M€, da verificare. N. impresa BE 0452.991.978. 44,3 FTE (bilancio NBB depositato 17-07-2026); fatturato non pubblicato, stimato 10-25 M€ (Kompass).</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr"/>
@@ -32761,7 +32706,7 @@
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Fatturato ca. 11 milioni EUR (VILT, stampa settoriale agroalimentare belga); organico ca. 50 persone (40 operai + 10 impiegati); capacita' 75.000 bovini ed equini/anno, ca. 125.000 bovini macellati per conto terzi. Numero d'impresa BE non verificato su fonte pubblica. Fa parte del gruppo Cadus NV (macelli in Belgio) ed e' socio Febev.</t>
+          <t>Fatturato ca. 11 milioni EUR (VILT, stampa settoriale agroalimentare belga); organico ca. 50 persone (40 operai + 10 impiegati); capacita' 75.000 bovini ed equini/anno, ca. 125.000 bovini macellati per conto terzi. Numero d'impresa BE non verificato su fonte pubblica. Fa parte del gruppo Cadus NV (macelli in Belgio) ed e' socio Febev. N. impresa BE 0832.292.464.</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr"/>
@@ -32849,7 +32794,7 @@
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>Fatturato 4.287.787 EUR e 4,8 FTE nella societa' di macellazione (ultimo bilancio NBB, via Companyweb/Trends Top); n. impresa BE 0436.764.571. SOTTO LA SOGLIA dei 5 M€ come singola entita': il fatturato riflette solo i servizi di macellazione: il gruppo familiare Swaegers &amp; Co dichiara 70.000 bovini/anno e 22.000 t di capacita' annua, quindi volumi EUDR molto superiori al fatturato contabile.</t>
+          <t>Fatturato 4.287.787 EUR e 4,8 FTE nella societa' di macellazione (ultimo bilancio NBB, via Companyweb/Trends Top); n. impresa BE 0436.764.571. SOTTO LA SOGLIA dei 5 M€ come singola entita': il fatturato riflette solo i servizi di macellazione: il gruppo familiare Swaegers &amp; Co dichiara 70.000 bovini/anno e 22.000 t di capacita' annua, quindi volumi EUDR molto superiori al fatturato contabile. Il gruppo familiare ha rilevato anche il macello di Bastogne.</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr"/>
@@ -35859,7 +35804,7 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Fatturato stimato ca. 42 Mio. € (fonte die-deutsche-wirtschaft.de, stima su dati 2023) - 51-200 dipendenti (fonte LinkedIn/firmenabc); nel 2007 24,5 Mio. € con 95 dipendenti (noe.ORF.at). Produzione ca. 30.000 t di carta/anno. Firmenbuch FN 312367p, LG St. Pölten. AZIENDA DI CONFINE: la stima 42 Mio. € supera di poco la fascia tollerabile 5-40 M€ ma resta ben sotto la soglia di esclusione ~50 M€. Impresa familiare all'8a generazione, parte della Salzer Gruppe (Papier, Industrie-Service, Holz). Co-Geschäftsführer citato in stampa: Dr. Harald Egger. Membro Austropapier.</t>
+          <t>Fatturato stimato ca. 42 Mio. € (fonte die-deutsche-wirtschaft.de, stima su dati 2023) - 51-200 dipendenti (fonte LinkedIn/firmenabc); nel 2007 24,5 Mio. € con 95 dipendenti (noe.ORF.at). Produzione ca. 30.000 t di carta/anno. Firmenbuch FN 312367p, LG St. Pölten. AZIENDA DI CONFINE: la stima 42 Mio. € supera di poco la fascia tollerabile 5-40 M€ ma resta ben sotto la soglia di esclusione ~50 M€. Impresa familiare all'8a generazione, parte della Salzer Gruppe (Papier, Industrie-Service, Holz). Co-Geschäftsführer citato in stampa: Dr. Harald Egger. Membro Austropapier. FN 211554i, LG St.; Pölten.</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -37635,7 +37580,7 @@
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>ca. 110-120 dipendenti su due stabilimenti a Villach (frierss.at / feines-haus.at, 2025); fatturato non pubblicato. Azienda familiare dal 1898, 5ª generazione. Firmenbuch FN 114403 (LG Klagenfurt)</t>
+          <t>ca. 110-120 dipendenti su due stabilimenti a Villach (frierss.at / feines-haus.at, 2025); fatturato non pubblicato. Azienda familiare dal 1898, 5ª generazione. Firmenbuch FN 114403 (LG Klagenfurt) Bilanzsumme 13,3 Mio. € al 31.03.2025 (firmenabc.at).</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">

--- a/MyEUDR_Lead_Mapping_v2.xlsx
+++ b/MyEUDR_Lead_Mapping_v2.xlsx
@@ -14283,7 +14283,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>11 dip. (proff.dk, CVR 35480943, NACE 310000 Fremstilling af møbler); fatturato non pubblicato. Taglia sotto 5 M€ mantenuta per copertura del cluster Syddanmark; co-direttore Kim Nordentoft Frederiksen</t>
+          <t>19 dipendenti (krak.dk/proff.dk, CVR 35480943; il valore '11' riportato altrove si riferisce alla produktionsenhed, non alla societa'); bruttofortjeneste 6,657 mio DKK (~0,89 M€, cambio 7,46) nell'ultimo bilancio disponibile - anno non esposto dalla fonte; afkastningsgrad 29,45%. Fatturato non pubblicato (A/S, bilancio in forma ridotta). NACE 310000 Fremstilling af moebler, Vejrup Storegade 63, 6740 Bramming; produttore di mobili di design familiare da oltre 50 anni. MOLTO SOTTO la forbice 5-40 M€: mantenuto per copertura del cluster Syddanmark. Co-direttore Kim Nordentoft Frederiksen.</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -16063,7 +16063,7 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>27 specialisti in Buchs A/S; il gruppo (Buchs + Buchs Labels, Randers/Silkeborg/Ho Chi Minh City) si avvicina a 100 dipendenti. CVR 29845646. Produzione interna oggi all'80% imballaggi; dal 2023 nuova tipografia di etichette (Buchs Labels A/S). Fatturato non pubblicato: DA VERIFICARE su regnskab; fascia stimata 5-15 M€ a livello di gruppo.</t>
+          <t>Bruttofortjeneste 14.746.681 DKK nel 2024 (~1,98 M€, cambio 7,46), contro 16.092.571 DKK nel 2023; risultato d'esercizio -418.569 DKK (perdita); 28 dipendenti (fascia paqle 20-50). Fatturato non pubblicato (A/S con bilancio in forma ridotta: viene esposto solo il margine lordo). CVR 29845646, costituita il 07.09.2006, Kertemindevej 15, 8940 Randers SV. Produzione interna oggi all'80% imballaggi; dal 2023 tipografia di etichette Buchs Labels A/S (CVR 44349051, Randers SV). MOLTO SOTTO la forbice 5-40 M€ come singola societa': con ~2,0 M€ di margine lordo e 28 addetti il fatturato e' verosimilmente sotto i 5 M€. La stima precedente '5-15 M€ a livello di gruppo' non e' sostenuta da alcuna fonte.</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -16115,7 +16115,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>13 dipendenti; bruttofortjeneste 14,756 mio DKK nel 2024 (~2,0 M€ di margine lordo), risultato ante imposte 5,169 mio DKK. CVR 15136901, Vejlbjergvej 14, fondata 1991. Produzione di etichette autoadesive. SOTTO SOGLIA: fatturato stimato ben sotto i 10 M€, probabilmente vicino o sotto i 5 M€. Capogruppo Color Label Holding ApS.</t>
+          <t>13 dipendenti; bruttofortjeneste 14,756 mio DKK nel 2024 (~1,98 M€, cambio 7,46); risultato ante imposte 5,169 mio DKK. Fatturato non pubblicato (A/S, bilancio in forma ridotta). CVR 15136901, Vejlbjergvej 12-16, 8240 Risskov (Aarhus). Azienda fondata nel 1980 da Erik Groenning, tuttora in prima linea (l'attuale CVR 15136901 e' registrato nel 1991). Etichette autoadesive per food, chimica e retail; parco macchine flexo Nilpeter (10a macchina flexo nel 2018, nuova FA-17 a 8 colori nel 2022). Capogruppo Color Label Holding ApS. MOLTO SOTTO la forbice: fatturato stimabile ben sotto i 10 M€, probabilmente vicino o sotto i 5 M€.</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -16211,7 +16211,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>21 dipendenti; ricavi/margine lordo dichiarati 9,211 mio DKK (~1,2 M€). CVR 38528742, NACE 172100, Højrupvej 11. SOTTO SOGLIA: ampiamente al di sotto della fascia minima 5 M€ - lead marginale, incluso solo perché già segnalato come lead parziale da verificare.</t>
+          <t>Bruttofortjeneste 8.149.124 DKK nel 2024 (~1,09 M€, cambio 7,46), contro 7.847.995 DKK nel 2023; risultato d'esercizio -6.461.178 DKK (perdita). 21 dipendenti (fascia paqle 20-50). Fatturato non pubblicato (ApS, bilancio in forma ridotta: viene esposto solo il margine lordo). CVR 38528742, costituita il 27.03.2017, NACE 172100, Hoejrupvej 11, 5620 Glamsbjerg. Fabbricazione di carta ondulata e imballaggi di carta. Capogruppo HOEJRUP HOLDING ApS (gruppo di 5 societa'); nel management Jesper Hildebrandt Christensen. MOLTO SOTTO la forbice 5-40 M€ - lead marginale.</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -16611,7 +16611,7 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>150 dipendenti; fatturato ~200 mio DKK (~26,8 M€, cambio 7,46). CVR 37120928, Oddesundvej 1. AZIENDA DI CONFINE: sopra la fascia 10-20 M€ ma dentro il tollerabile 5-40 M€. LEGAME DI GRUPPO: ex Rosendahls, acquisita e ridenominata Stibo Complete A/S nel 2022 (gruppo Stibo, danese, fondazione).</t>
+          <t>Nettoomsaetning 748 mio DKK nell'esercizio 2025 (~100,3 M€, cambio 7,46), con perdita di 33,5 mio DKK dovuta principalmente alla chiusura della rotativa di Horsens; 278 dipendenti (fascia paqle 200-500). CVR 37120928, Oddesundvej 1, Horsens; esercizio 1 maggio - 30 aprile. Ex Rosendahls, acquisita e ridenominata Stibo Complete A/S nel 2022; parte di Stibo Complete Group A/S (CVR 35844120), gruppo grafico internazionale della fondazione danese Stibo. NETTAMENTE FUORI TAGLIA: ~100 M€ di fatturato, oltre il doppio della soglia dei 50 M€ e ben oltre la forbice tollerabile 5-40 M€.</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
@@ -16707,7 +16707,7 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Bruttofortjeneste 7,3 mio. DKK nell'ultimo bilancio disponibile (+421% in 5 anni); dipendenti non pubblicati. Capogruppo: STEFFAN TOBIESEN HOLDING ApS. Fonte: food-supply.dk / proff.dk. SOTTO IL TARGET. · CVR 33243537</t>
+          <t>Bruttofortjeneste 7,3 mio DKK (~0,98 M€, cambio 7,46) nell'ultimo bilancio pubblicato al momento dell'articolo (+421% in cinque anni); utile d'esercizio 2,17 mio DKK nell'esercizio 1.1.2023-31.12.2023 (proff.dk). Dipendenti non pubblicati. Fatturato non pubblicato (ApS, bilancio in forma ridotta). CVR 33243537, capitale 80.000 DKK, NACE 463700 'engroshandel med kaffe, te, kakao og krydderier', Storstroemsvej 42, 6715 Esbjerg N. Torrefazione propria e soluzioni caffe' per aziende. Capogruppo STEFFAN TOBIESEN HOLDING ApS. MOLTO SOTTO IL TARGET.</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -16855,7 +16855,7 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>10-20 dipendenti; bruttofortjeneste 10 mio. DKK (bilancio 2021); fatturato non pubblicato. Costituita nel 1994. Fonte: paqle.dk / proff.dk / retailnews.dk. SOTTO IL TARGET ma doppia commodity EUDR (caffè + cacao). NB: stesso CVR 18179407 ora registrato come Smage-Compagniet A/S (Holmevej 10, 5683 Haarby); marchi Estate Coffee, Chokolade Compagniet, Valrhona. · CVR 18179407</t>
+          <t>Bruttofortjeneste 15 mio DKK nel 2024 (~2,01 M€, cambio 7,46; 11 mio DKK nel 2023); fatturato non pubblicato (A/S, bilancio in forma ridotta). Dipendenti: 17 secondo una fonte, 22 secondo un'altra; fascia paqle 20-50. CVR 18179407, societa' costituita nel 1994 e oggi denominata Smage-Compagniet A/S, Holmevej 10, 5683 Haarby (Fionia). Torrefazione, magazzino e vendita di caffe' slow roast, te' biologici e cioccolato fine; marchi Estate Coffee, Valrhona, NUTe, T Town, Chokolade Compagniet, North OAK. Capogruppo Smage-Compagniet Holding A/S (CVR 44432382). Doppia commodity EUDR (caffe' + cacao). SOTTO IL TARGET.</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -29114,7 +29114,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Fatturato annuo dichiarato 'oltre 10 milioni di euro' (fonte: reportage Sterck Magazine); presente nel ranking settoriale 'houthandel' di Trends Top. Impresa BE 0400.079.171, fondata 01-07-1959. Sede: Singel 140, 9000 Gent. Organico snello (6-9 addetti secondo Kompass) rispetto ai volumi: tipico importatore/commerciante. Importatore diretto di legname tropicale (azobé, iroko, sapelli, wengé, afrormosia...) — operatore EUDR in senso stretto. Fatturato esatto da confermare su NBB. Nessuna pagina LinkedIn aziendale propria reperita; l'azienda è presente su LinkedIn tramite la joint venture 50/50 con Lemahieu 'LDCwood' (be.linkedin.com/company/ldcwood), specializzata in legno termotrattato.</t>
+          <t>Fatturato totale 38.585.036 € nell'ultimo bilancio depositato (deposito NBB del 27-01-2025, quindi esercizio 2023/2024); 9 FTE secondo lo stato del personale dello stesso bilancio. Trendstop colloca la societa' nella fascia 25-100 Mio €. BE 0400.079.171, fondata 01-07-1959, Singel 140, 9000 Gent. Importatore diretto di legname tropicale (azobe, iroko, sapelli, wenge, afrormosia) - operatore EUDR in senso stretto; organico snello tipico dell'importatore/commerciante. AL LIMITE SUPERIORE della forbice 5-40 M€, ben sopra il target ideale 10-20 M€.</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -35460,7 +35460,7 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Fatturato ca. 5,2 Mio. USD (~4,8 Mio. €) - 33 dipendenti (fonte profilo RocketReach, dato stimato). Firmenbuch FN 205435k. Sede Industrie Nord, Bildgasse 42, 6890 Lustenau. AZIENDA SOTTO LA SOGLIA MINIMA 5 M€ secondo la stima disponibile: dimensione DA VERIFICARE prima del contatto (l'azienda si presenta come una delle principali etichettifici dell'area di lingua tedesca, quindi il dato stimato potrebbe essere sottostimato). Impresa familiare fondata nel 1939, 4a generazione (Simon Sohm in direzione, tecnica applicativa e vendite).</t>
+          <t>Fatturato oltre 18 Mio. € nel 2010 (con 123 dipendenti; fonte Wirtschaftszeit.at); dato di fatturato piu' recente non pubblicato (GmbH, conto economico non depositato). Organico: ca. 150 dipendenti nella sede di Lustenau nel 2021 (neue.at), 160 dipendenti oggi fra amministrazione e produzione (carini.at / LinkedIn, 2025). Firmenbuch FN 205435k. Con 160 addetti e un fatturato gia' &gt;18 Mio. € nel 2010 l'azienda e' ampiamente sopra la soglia minima di 5 M€ e verosimilmente dentro/appena sopra la fascia 20-35 M€. La stima RocketReach (5,2 Mio. USD / 33 dipendenti) e' errata e va scartata.</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">

--- a/MyEUDR_Lead_Mapping_v2.xlsx
+++ b/MyEUDR_Lead_Mapping_v2.xlsx
@@ -4201,7 +4201,7 @@
       </c>
       <c r="I86" s="5" t="inlineStr">
         <is>
-          <t>Castelli Calepio (BG)</t>
+          <t>Foresto Sparso (BG)</t>
         </is>
       </c>
       <c r="J86" s="5" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="I92" s="5" t="inlineStr">
         <is>
-          <t>Fombio (LO)</t>
+          <t>Piacenza (PC) — sede legale; stabilimento a Fombio (LO)</t>
         </is>
       </c>
       <c r="J92" s="5" t="inlineStr">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>Mertendorf OT Görschen (Sachsen-Anhalt)</t>
+          <t>Mertendorf OT Görschen (Sachsen-Anhalt) — stabilimento; sede legale Schlüsselfeld (Bayern)</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
@@ -8519,7 +8519,7 @@
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>Friedrichshafen, Baden-Württemberg</t>
+          <t>Meckenbeuren (sede legale) / Friedrichshafen (sede operativa), Baden-Württemberg</t>
         </is>
       </c>
       <c r="J76" s="5" t="inlineStr">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>Utajärvi (Pohjois-Pohjanmaa)</t>
+          <t>Kuopio (Pohjois-Savo) — sede legale; stabilimento a Utajärvi (Pohjois-Pohjanmaa)</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -12796,7 +12796,7 @@
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>Akaa (Pirkanmaa)</t>
+          <t>Akaa (stabilimento) / Lempäälä (kotipaikka), Pirkanmaa</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
@@ -13280,7 +13280,7 @@
       </c>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>Luumäki, Etelä-Karjala</t>
+          <t>Helsinki (Uusimaa) — sede legale; paahtimo a Luumäki, Etelä-Karjala</t>
         </is>
       </c>
       <c r="J71" s="3" t="inlineStr">
@@ -16637,7 +16637,7 @@
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>Esbjerg N (Syddanmark)</t>
+          <t>Horsens (Midtjylland) — sede legale; unità operative a Esbjerg N e Søborg</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
@@ -18493,7 +18493,7 @@
       </c>
       <c r="I86" s="5" t="inlineStr">
         <is>
-          <t>Randers, Region Midtjylland</t>
+          <t>Randers SØ, Region Midtjylland</t>
         </is>
       </c>
       <c r="J86" s="5" t="inlineStr">
@@ -20111,7 +20111,7 @@
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>Tranås, Jönköpings län</t>
+          <t>Tranås, Jönköpings län (säte); stabilimento a Grännäs, Valdemarsvik, Östergötlands län</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
@@ -20771,7 +20771,7 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>Glommersträsk (Arvidsjaur), Norrbottens län</t>
+          <t>Glommersträsk (Arvidsjaur) — sede legale Luleå, Norrbottens län</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -21319,7 +21319,7 @@
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>Malmö, Skåne län</t>
+          <t>Borås, Västra Götalands län</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
@@ -30444,7 +30444,7 @@
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>Beveren-Waas, Provincia di Fiandre Orientali (Fiandre)</t>
+          <t>Beveren-Kruibeke-Zwijndrecht (ex Beveren-Waas), Provincia di Fiandre Orientali (Fiandre)</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
@@ -34358,7 +34358,7 @@
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>Kalsdorf bei Graz (Steiermark)</t>
+          <t>Premstätten (Steiermark)</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
@@ -34406,7 +34406,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Himberg (Niederösterreich)</t>
+          <t>Himberg (Niederösterreich) — sede operativa; sede legale 1080 Wien</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">

--- a/MyEUDR_Lead_Mapping_v2.xlsx
+++ b/MyEUDR_Lead_Mapping_v2.xlsx
@@ -21,7 +21,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Germania'!$A$2:$J$99</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Finlandia'!$A$2:$J$86</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Danimarca'!$A$2:$J$86</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Svezia'!$A$2:$J$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Svezia'!$A$2:$J$89</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Olanda'!$A$2:$J$100</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Belgio'!$A$2:$J$94</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Austria'!$A$2:$J$92</definedName>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>≈6,5M€ (2023) / 16-19 dip. (FatturatoItalia)</t>
+          <t>Fatturato 5.937.871 € (2024), in calo dai 6.546.179 € del 2023 e dai 7.872.713 € del 2021; perdita d'esercizio 213.556 € nel 2024. 18 dipendenti (piccola impresa, 10-49 addetti). Sede Via Stazione, Castello-Molina di Fiemme (TN); P.IVA 02000590220; taglio e piallatura del legno. Fonte: ufficiocamerale/reportaziende/Atoka su bilanci depositati. NB: al limite inferiore della forbice target 5-40 M€ e in contrazione.</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr"/>
@@ -4060,13 +4060,21 @@
       </c>
       <c r="D83" s="3" t="inlineStr"/>
       <c r="E83" s="3" t="inlineStr"/>
-      <c r="F83" s="3" t="inlineStr"/>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/company/fpparis</t>
+        </is>
+      </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
           <t>n.d.</t>
         </is>
       </c>
-      <c r="H83" s="3" t="inlineStr"/>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fpparis.com</t>
+        </is>
+      </c>
       <c r="I83" s="3" t="inlineStr">
         <is>
           <t>Castelli Calepio (BG)</t>
@@ -4431,7 +4439,7 @@
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>~49,5 mln € (2023) — limite alto, PMI indipendente</t>
+          <t>Fatturato 44.097.825 € (ultimo bilancio disponibile, esercizio 2024 pubblicato 2025); utile 332.730 €; 53 dipendenti; capitale sociale 3.500.000 €. Sede Via San Marco 14, 29121 Piacenza (PC); P.IVA 01223200336; mangimificio fondato nel 1972 (suini, ruminanti, avicoli e animali da cortile). Media impresa, al limite superiore della forbice target ma sotto i 50 M€.</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr"/>
@@ -4591,7 +4599,7 @@
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>~26,8 mln € (2024); ~21 dip.; lavorazione carni rosse (bovino/bufalino)</t>
+          <t>~26,8 mln € (2024); ~21 dip.; lavorazione carni rosse (bovino/bufalino) Legame di gruppo: società soggetta a direzione e coordinamento di Gruppo Balletta S.p.A.</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr"/>
@@ -4933,7 +4941,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>~20 MA, Umsatz n.d.; piccola conceria vegetale (marchio Rendenbach)</t>
+          <t>~20 dipendenti (hogn.de 2019, confermato da wer-zu-wem/sito kilger.de); volumi 1.000-1.500 pelli/mese; fatturato NON pubblicato (KG senza obbligo di deposito) — dimensione verosimilmente &lt; 5 Mio €, SOTTO la forbice target</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -4981,7 +4989,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>~20-35 Mio € Umsatz (2019: 35M; 2020: ~20M); conceria pelle bovina</t>
+          <t>~100 dipendenti nello stabilimento di Wegberg (sito aziendale heinen-leather.de, 2025); fatturato: 35 Mio € (2019, KfW Stories), classe di fatturato Creditreform 50-100 Mio € (non datata); bilanci depositati fino al 2024 ma cifre non pubbliche — anno recente non determinabile</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -5273,7 +5281,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Umsatz/MA n.d.</t>
+          <t>Bilanzsumme 1,8 Mio € (2023, Bundesanzeiger via Implisense); classe di fatturato 10-50 Mio € (wer-zu-wem / Implisense); AG Mannheim HRB 210482; numero dipendenti non pubblicato — fatturato puntuale non determinabile</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -5761,7 +5769,7 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>~5 Mio € Umsatz (stima) / ~100 MA (Die Deutsche Wirtschaft)</t>
+          <t>~130 dipendenti (2024-2025, Die Deutsche Wirtschaft / sito aziendale), 5 sedi in Meclemburgo-Pomerania, fondata 1992; AG Stralsund HRA 279; fatturato non pubblicato (GmbH &amp; Co. KG) — stima Implisense ~5 Mio € su 100 dip., ritenuta non attendibile</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -5809,7 +5817,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>~80 MA (Creditreform); Umsatz n.d.; impiallacciature/tavolame</t>
+          <t>~85 dipendenti (sito aziendale sg-veneers.com, 2025), 2ª generazione, fondata 1961; 8 mln m² di tranciati a magazzino + oltre 2.000 m³ di tavolame (Karlsruhe ed Ehrenkirchen); fatturato non pubblicato (AG Mannheim HRB 103479). NB: il dato RocketReach «14,2 M$ / 13 dip.» è incoerente, da non usare</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -6001,7 +6009,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>50–99 MA (wlw.com); NB: parte della Bernecker-Gruppe; Umsatz n.d.</t>
+          <t>50-99 dipendenti (wlw.com, senza anno); Bilanzsumme 2,0 Mio € (2023, -15,7% sul 2022, Bundesanzeiger via Implisense); fatturato non pubblicato. Controllata della Bernecker-Gruppe (Melsungen) dal 2015/2016; il 90% dei ricavi di stampa del gruppo viene da packaging secondario farmaceutico. AG Fritzlar HRB 12160 — decisione EUDR a livello di capogruppo Bernecker</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -6053,7 +6061,7 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>KMU; Umsatz/MA n.d.</t>
+          <t>~65 dipendenti (sito aziendale siepmanndruck.de, 2025); Bilanzsumme 4,0 Mio € (2023, Bundesanzeiger via Implisense); fatturato non pubblicato (deposito abbreviato). Sede Ruhrstraße 126, 22761 Amburgo; AG Hamburg HRB 25539; offset/digitale, astucci pieghevoli e packaging farmaceutico</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -6101,7 +6109,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Familienunternehmen (marchio madika); Umsatz/MA n.d. — NB: non è il gruppo pannelli EGGER</t>
+          <t>11-50 dipendenti (Creditreform / wer-zu-wem / LifeVERDE, 2025); azienda familiare di 5ª generazione fondata nel 1872, AG Augsburg HRB 9915, Landsberg am Lech; stampa di packaging in cartoncino + shop online madika.de; fatturato non pubblicato — con questo organico verosimilmente SOTTO la soglia di 5 Mio €</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -6201,7 +6209,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>&gt;60 MA (wer-zu-wem); Umsatz n.d.</t>
+          <t>Oltre 60 dipendenti e apprendisti nella sede di Leutershausen (sito aziendale fmsag.de, 2025), oltre 90 considerando entrambe le sedi (wer-zu-wem); capitale sociale 2.000.000 €; AG Ansbach HRB 5384; astucci pieghevoli, imballaggi e display per food, cosmetica, giocattoli, automotive; fatturato non pubblicato</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -6301,7 +6309,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>~115 MA (2020, print.de); Umsatz n.d.</t>
+          <t>&gt;100 dipendenti a tempo pieno (2025, emsachse.de / Creditreform; fascia LinkedIn 51-200), produzione su due turni; azienda familiare fondata nel 1951, sede Neuenhaus, AG Osnabrück HRA 130316; fatturato non pubblicato (GmbH &amp; Co. KG)</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -6349,7 +6357,7 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>~19 MA (2010, lieferanten.de); Umsatz n.d.</t>
+          <t>11-50 dipendenti (LinkedIn, dato attuale 2025; erano 19 nel 2010 secondo lieferanten.de); azienda fondata nel 1950, Brunckstr. 4, 67346 Speyer, AG Ludwigshafen HRB 52133; astucci pieghevoli e cartonaggi; fatturato non pubblicato — con questo organico verosimilmente SOTTO la soglia di 5 Mio €</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -6401,7 +6409,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Mittelstand familiare (gegr. 1958); Umsatz/MA n.d.</t>
+          <t>10-49 dipendenti (Creditreform, 2025; wer-zu-wem indica ~30); azienda familiare di medie dimensioni fondata nel 1958, AG Hannover HRA 26344; imballaggi e display in cartone teso e ondulato; fatturato non pubblicato (GmbH &amp; Co. KG) — verosimilmente al limite inferiore o sotto la forbice 5-40 Mio €</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -6593,7 +6601,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Familienunternehmen dal 1957; Umsatz/MA n.d.</t>
+          <t>Familienunternehmen dal 1957 (Espelkamp; produzione a Diepenau dal 1969). 73 dipendenti (Implisense, dati registro/Bundesanzeiger, ultimo aggiornamento disponibile); Bilanzsumme 3,3 Mio € (2019, Bundesanzeiger via Implisense). Fatturato non pubblicato. NB: taglia verosimilmente SOTTO la forbice target 5-40 Mio €.</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -7425,7 +7433,7 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>n.d. (torrefazione media, gegr. 1908). Legame di gruppo: controllata al 100% da Zentralkonsum eG (Berlino) — HRB 107856.</t>
+          <t>Torrefazione storica (gegr. 1908), Magdeburg; interamente controllata da Zentralkonsum eG. Dipendenti: oltre 200 (fonte azienda/portali, dato corrente s.d.; Wikipedia riportava oltre 150). Fatturato non pubblicato in chiaro: bilanci depositati fino all'esercizio 31/12/2023 (HRB 107856 AG Stendal, northdata) ma cifre non esposte.</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -7521,7 +7529,7 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>n.d. (torrefazione regionale, gegr. 1883, 3ª gen.)</t>
+          <t>Torrefazione regionale, gegr. 1883 a Danzica, sede Hannover dal 1919, 2ª/3ª gen. (Jörg-Walter e Maximilian Koch). Dipendenti: &lt;25 (Wikipedia) — altra fonte locale indica ~40 posti creati nel tempo. Patrimonio netto (Eigenkapital) 912.420 € nel 2021 (bilancio depositato). Fatturato non pubblicato. NB: taglia ampiamente SOTTO la forbice target 5-40 Mio €.</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -7765,7 +7773,7 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>~130 dip. + ~50 stagionali (DDW); Umsatz n.d.</t>
+          <t>Fatturato ~14,0 Mio € e ~150 dipendenti fra full-time e part-time (Die Deutsche Wirtschaft, stima di portale, anno non dichiarato); stima alternativa 101 dipendenti e ~11 Mio € di fatturato (Implisense/Creditreform). Il campo precedente indicava 130 dipendenti fissi + ~50 stagionali natalizi. Costituita 1989, Lauensteiner Straße 41, Ludwigsstadt (HRB 1536 AG Coburg). IN TARGET (11-14 Mio €).</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
@@ -7909,7 +7917,7 @@
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>~75 dip.; classe Umsatz 10–50 Mio € (northdata/wer-zu-wem)</t>
+          <t>Dipendenti: 75 (dato datato dicembre 2024, Bürgschaftsbank Brandenburg / bauernzeitung), in prevalenza donne. Fatturato: solo classe di portale 10-50 Mio € (wer-zu-wem/companyhouse, senza anno) — cifra puntuale NON pubblicata. Fondata 1992, ~2.000 mq fra produzione, magazzino, caffè e factory outlet; filiali proprie a Potsdam e Dresda; prodotti in 200 punti vendita in Germania.</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
@@ -8149,7 +8157,7 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>n.d. (impresa familiare indip. dal 1865; leader Mozartkugeln)</t>
+          <t>Impresa familiare indipendente dal 1865 (famiglia Botzleiner-Reber), sede Bad Reichenhall. Dipendenti: circa 300 nei periodi di picco (Wikipedia/stampa locale, s.d.). Volumi: ~500.000 Mozartkugeln/giorno, export in oltre 50 paesi; leader di mercato tedesco e, per dichiarazione propria, maggior produttore mondiale di Mozartkugeln. Fatturato NON pubblicato (KG, HRA 701 Traunstein, non deposita conto economico) — le stime di portale tipo rocketreach non sono citabili.</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
@@ -8249,7 +8257,7 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>~100 dip. (Wikipedia/DDW); Umsatz n.d.; storica manifattura Nota: socio di maggioranza Fintura Corporate Finance (Berlino) dal 2021, post-insolvenza in Eigenverwaltung.</t>
+          <t>Fatturato STIMATO ~32 Mio € (Die Deutsche Wirtschaft, stima di portale, non dato di bilancio); dipendenti: 80 secondo DDW, ~100 nello stabilimento di Berlin-Reinickendorf secondo azienda/Wikipedia. Manifattura di praline piu' antica di Berlino, fondata 1880 Unter den Linden; guidata dai coniugi Melanie e Benno Hübel, subentrati nel novembre 2013 (HRB 153823 B AG Charlottenburg). IN TARGET se la stima regge; dato di bilancio da confermare su Bundesanzeiger. Nota: socio di maggioranza Fintura Corporate Finance (Berlino) dal 2021, post-insolvenza in Eigenverwaltung.</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
@@ -8685,7 +8693,7 @@
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>Umsatzklasse fino a 10 Mio €, ~40 MA (Northdata/Kompass)</t>
+          <t>Bilanzsumme (totale di bilancio) 3 Mio € nell'esercizio 2023 (ultimo pubblicato, Bundesanzeiger via Implisense); 40 dipendenti in Germania; classe di fatturato fino a 10 Mio € (portale, senza anno). Fatturato puntuale non pubblicato. Stabilimento di gomma tecnica a Caputh/Schwielowsee (HRB 13965 AG Potsdam), 55 anni di attivita'. NB: taglia verosimilmente SOTTO la soglia inferiore della forbice target (5 Mio €).</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
@@ -9069,7 +9077,7 @@
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Umsatz ~10 Mio € (2023, Implisense)</t>
+          <t>Classe di fatturato 10-50 Mio € (wer-zu-wem, senza anno); fatturato puntuale NON pubblicato (KG, HRA 6208 AG Steinfurt). Volumi: 150.000 t di mangime/anno prodotte a Ladbergen dall'estate 2017 (sito ufficiale). Dipendenti non pubblicati. NB assetto: ETS Mischfutterwerk e' una JOINT VENTURE fra Eilers Futtermittel GmbH &amp; Co. KG (fondata 1903) e agritura Raiffeisen eG — non e' quindi una PMI indipendente in senso stretto.</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
@@ -9313,7 +9321,7 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>Umsatz ~46,86 Mio € (stima Companyhouse, incl. molino/pellet); 20–49 MA — limite superiore</t>
+          <t>Fatturato STIMATO ~46,86 Mio € (Companyhouse / wer-zu-wem / Die Deutsche Wirtschaft — stima di portale, anno di riferimento NON dichiarato): non e' un dato di bilancio, la KG non pubblica il conto economico. Dipendenti: fonti discordanti, 20-49 secondo alcuni portali, ~100 secondo altri. Fondata 1879; molino a cereali, mangimi, pellet ed energie rinnovabili; Schießplatzstr. 1-5, 88250 Weingarten (HRA 550174 AG Ulm). Limite superiore della forbice target.</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
@@ -9409,7 +9417,7 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>~150 MA nel mondo; Bilanzsumme ~40 Mio € (2023); familiare, tratta olio di palma</t>
+          <t>Totale di bilancio (Bilanzsumme) 40 Mio € nel 2023, in calo del 7,1% sull'anno precedente (Bundesanzeiger via Implisense); utile netto 2023 4,46 Mio €. Dipendenti: 150; capacita' produttiva annua 50.000 t nel mondo. FATTURATO NON PUBBLICATO — la Bilanzsumme non e' un ricavo. Azienda familiare fondata 1897 (HRB 5001 AG Stuttgart), nove filiali/impianti in Europa, USA e Asia; tratta anche olio di palma.</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
@@ -11650,7 +11658,7 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>≈22,6 M€ (2025; 17 M€ 2024) / ~17 dip. (Asiakastieto)</t>
+          <t>Liikevaihto 22,6 M€ (2025), 34 dip.; 17,0 M€ (2024), 35 dip. (Asiakastieto/Proff, Y-tunnus 0167908-6) — in forbice</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -12138,7 +12146,7 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>≈18,5 M€ (2022, largestcompanies/Åland)</t>
+          <t>Omsättning koncernen 21,8 M€ (2025, +~10%; moderbolaget 17,3 M€), rörelseresultat 0,76 M€; ~49 anställda — in forbice</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -12434,7 +12442,7 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Liikevaihto ~1,9 M€ (2024), ~29 dip. (scale-up) — sotto fascia</t>
+          <t>Liikevaihto 1,9 M€ (2024, +83,3%), 29 dip.; perdita operativa -4,5 M€ (2024, margine -225,5%) e tilikauden tulos -3,04 M€ (2023, liikevaihto 1,05 M€); scale-up finanziata da aumenti di capitale (1 M€ 2020, 3,5 M€ 2021) — MOLTO SOTTO FASCIA, verificare continuità aziendale</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -12578,7 +12586,7 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>~25 dip. (2024); liikevaihto n.d.</t>
+          <t>Liikevaihto ~6,0 M€ (ultimo esercizio pubblicato, 2024), 25 dip. (-3,9% sull'anno precedente); liiketoiminnan voitto 83.000 € (2024) — limite inferiore della forbice</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
@@ -12722,7 +12730,7 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Liikevaihto ~15,0 M€ (2022), ~24 dip. (2025)</t>
+          <t>24 dip. (2025), 51 dip. (2024); liiketulos 1,4 M€ (2025) e 1,3-1,5 M€ (2024); liikevaihto NON pubblicato nei registri (0 EUR in Proff/Asiakastieto per 2024 e 2025) — ultimo fatturato noto ~15,0 M€ (2022), non più rappresentativo</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
@@ -15888,7 +15896,7 @@
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>https://vermund.eu/</t>
+          <t>https://www.vela.dk/ (vermund.eu è il sito del marchio design Vermund)</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
@@ -18734,7 +18742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J90"/>
+  <dimension ref="A1:J89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -19088,7 +19096,7 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>https://se.linkedin.com/company/blastation</t>
+          <t>https://www.linkedin.com/company/bla_station_ab/</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
@@ -21735,118 +21743,126 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>Lenanders Grafiska AB</t>
+          <t>Lessebo Paper AB</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Carta/Packaging — stampa</t>
+          <t>Carta/Packaging — cartiera</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Fatturato 122.940 KSEK (~10,9 M€) e 42 dipendenti — fonte allabolag/bolagssoket, es. 2024. Org.nr 556323-6776 (da riverificare: fonti aggregate riportano numerazioni divergenti). IN TARGET. Nota legame di gruppo: collegata a Scandinavian Print Group (proprietà danese); VD non pubblicato nelle fonti consultate — in cda risultano Henrik Corvenius Frydendahl ed Esben Mols Kabell. Controllata (100%) di Scandinavian Print Group (DK) dal 1/9/2021; capogruppo di riferimento per la compliance: Scandinavian Print Group.</t>
-        </is>
-      </c>
-      <c r="D61" s="3" t="inlineStr"/>
-      <c r="E61" s="3" t="inlineStr"/>
+          <t>Fatturato 376.018 KSEK (~33,3 M€) e 91 dipendenti — fonte allabolag/bolagsfakta, es. 2024. Org.nr 556955-1616. AZIENDA DI CONFINE: sopra il target 10-20 M€ ma dentro la fascia tollerabile 5-40 M€. Cartiera indipendente (carta e pasta di carta). Nota legame di gruppo: capogruppo Lessebo Finance AB; presidente Karl Göran Johansson.</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Jens Olsson</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>VD (extern verkställande direktör)</t>
+        </is>
+      </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>https://se.linkedin.com/company/lenanders-grafiska-ab</t>
+          <t>https://www.linkedin.com/company/lessebo-paper-ab</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>info@lenanders.se</t>
+          <t>market@lessebopaper.com</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>https://www.lenanders.se/</t>
+          <t>https://lessebopaper.com/</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>Kalmar, Kalmar län</t>
+          <t>Lessebo, Kronobergs län</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>https://www.bolagssoket.se/foretag/lenanders-grafiska-ab/</t>
+          <t>https://www.allabolag.se/5569551616/lessebo-paper-ab</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Lessebo Paper AB</t>
+          <t>Ljungbergs Tryckeri i Klippan AB</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>Carta/Packaging — cartiera</t>
+          <t>Carta/Packaging — stampa</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Fatturato 376.018 KSEK (~33,3 M€) e 91 dipendenti — fonte allabolag/bolagsfakta, es. 2024. Org.nr 556955-1616. AZIENDA DI CONFINE: sopra il target 10-20 M€ ma dentro la fascia tollerabile 5-40 M€. Cartiera indipendente (carta e pasta di carta). Nota legame di gruppo: capogruppo Lessebo Finance AB; presidente Karl Göran Johansson.</t>
+          <t>Fatturato 144.190 KSEK (~12,8 M€) e 32 dipendenti — fonte allabolag/bolagsfakta, es. 2025. Org.nr 556884-2511. IN TARGET. Nota legame di gruppo: gruppo grafico di 9 società con capogruppo Scanner Colour i Klippan AB (con Norra Skåne Offset AB, Klippans Bokbinderi AB, RST Klippan AB; ~80 addetti complessivi).</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Jens Olsson</t>
+          <t>Sofia Ljungberg Igbe</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>VD (extern verkställande direktör)</t>
+          <t>VD</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/lessebo-paper-ab</t>
+          <t>https://se.linkedin.com/company/ljungbergs-tryckeri-ab</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>market@lessebopaper.com</t>
+          <t>offert@ljungbergs.se</t>
         </is>
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>https://lessebopaper.com/</t>
+          <t>https://www.ljungbergs.se/</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>Lessebo, Kronobergs län</t>
+          <t>Klippan, Skåne län</t>
         </is>
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>https://www.allabolag.se/5569551616/lessebo-paper-ab</t>
+          <t>https://www.allabolag.se/foretag/ljungbergs-tryckeri-i-klippan-ab/klippan/tryckerier/2K3JMDRI5YI3L</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>Ljungbergs Tryckeri i Klippan AB</t>
+          <t>NPA Nordiskt Papper AB</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Carta/Packaging — stampa</t>
+          <t>Carta/Packaging — sacchetti carta</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Fatturato 144.190 KSEK (~12,8 M€) e 32 dipendenti — fonte allabolag/bolagsfakta, es. 2025. Org.nr 556884-2511. IN TARGET. Nota legame di gruppo: gruppo grafico di 9 società con capogruppo Scanner Colour i Klippan AB (con Norra Skåne Offset AB, Klippans Bokbinderi AB, RST Klippan AB; ~80 addetti complessivi).</t>
+          <t>Fatturato 95.602 KSEK (~8,5 M€) e 29 dipendenti — fonte allabolag/bolagsfakta, es. 2024. Org.nr 556963-0683. AZIENDA DI CONFINE: sotto il target 10-20 M€ ma dentro la fascia tollerabile 5-40 M€. Attività: conversione e vendita di prodotti in carta e politene (sacchetti e borse di carta). Nota legame di gruppo: gruppo di 6 società, capogruppo NPA Gruppen AB.</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>Sofia Ljungberg Igbe</t>
+          <t>Mats Werner Lidbeck</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -21856,34 +21872,34 @@
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>https://se.linkedin.com/company/ljungbergs-tryckeri-ab</t>
+          <t>https://se.linkedin.com/company/npa-nordisktpapper-ab</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>offert@ljungbergs.se</t>
+          <t>order@nordisktpapper.se</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>https://www.ljungbergs.se/</t>
+          <t>https://nordisktpapper.se/</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>Klippan, Skåne län</t>
+          <t>Ljungby, Kronobergs län</t>
         </is>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>https://www.allabolag.se/foretag/ljungbergs-tryckeri-i-klippan-ab/klippan/tryckerier/2K3JMDRI5YI3L</t>
+          <t>https://www.allabolag.se/5569630683/npa-nordiskt-papper-ab</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>NPA Nordiskt Papper AB</t>
+          <t>Norbag AB</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
@@ -21893,116 +21909,116 @@
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Fatturato 95.602 KSEK (~8,5 M€) e 29 dipendenti — fonte allabolag/bolagsfakta, es. 2024. Org.nr 556963-0683. AZIENDA DI CONFINE: sotto il target 10-20 M€ ma dentro la fascia tollerabile 5-40 M€. Attività: conversione e vendita di prodotti in carta e politene (sacchetti e borse di carta). Nota legame di gruppo: gruppo di 6 società, capogruppo NPA Gruppen AB.</t>
+          <t>Fatturato 357.159 KSEK (~31,6 M€) e 121 dipendenti — fonte allabolag/bolagsfakta, es. 2024. Org.nr 556656-1782. AZIENDA DI CONFINE: sopra il target 10-20 M€ ma dentro la fascia tollerabile 5-40 M€. Produttore nordico di shopper e sacchetti di carta per pane e rifiuti organici. Nota legame di gruppo: gruppo di 18 società, capogruppo Tingstad Group AB, capogruppo ultima Danti Invest AB; presidente Dan Paul Jigberg.</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Mats Werner Lidbeck</t>
+          <t>Torbjörn Rodhe</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>VD</t>
+          <t>VD (extern verkställande direktör)</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>https://se.linkedin.com/company/npa-nordisktpapper-ab</t>
+          <t>https://www.linkedin.com/company/norbag-ab</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>order@nordisktpapper.se</t>
+          <t>info@norbag.com</t>
         </is>
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>https://nordisktpapper.se/</t>
+          <t>https://www.norbag.com/</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>Ljungby, Kronobergs län</t>
+          <t>Töcksfors (Årjäng), Värmlands län</t>
         </is>
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>https://www.allabolag.se/5569630683/npa-nordiskt-papper-ab</t>
+          <t>https://www.allabolag.se/foretag/norbag-ab/t%C3%B6cksfors/pappersvaror-produktion/2K26QK6I63IJV</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>Norbag AB</t>
+          <t>Pappersgrossisten i Jönköping Aktiebolag</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Carta/Packaging — sacchetti carta</t>
+          <t>Carta/Packaging — grossista carta</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Fatturato 357.159 KSEK (~31,6 M€) e 121 dipendenti — fonte allabolag/bolagsfakta, es. 2024. Org.nr 556656-1782. AZIENDA DI CONFINE: sopra il target 10-20 M€ ma dentro la fascia tollerabile 5-40 M€. Produttore nordico di shopper e sacchetti di carta per pane e rifiuti organici. Nota legame di gruppo: gruppo di 18 società, capogruppo Tingstad Group AB, capogruppo ultima Danti Invest AB; presidente Dan Paul Jigberg.</t>
+          <t>Fatturato 80.655 KSEK (~7,1 M€) e 14 dipendenti — fonte allabolag/bolagsfakta, es. 2024. Org.nr 556323-1132. AZIENDA DI CONFINE: sotto il target 10-20 M€ ma dentro la fascia tollerabile 5-40 M€. Nota legame di gruppo: capogruppo LOLAB Förvaltnings AB.</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Torbjörn Rodhe</t>
+          <t>Jan Olof Helge Larsson</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>VD (extern verkställande direktör)</t>
+          <t>VD</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/norbag-ab</t>
+          <t>https://se.linkedin.com/company/pappersgrossisten</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>info@norbag.com</t>
+          <t>info@pg24.se</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>https://www.norbag.com/</t>
+          <t>https://pg24.se/</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
-          <t>Töcksfors (Årjäng), Värmlands län</t>
+          <t>Jönköping, Jönköpings län</t>
         </is>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>https://www.allabolag.se/foretag/norbag-ab/t%C3%B6cksfors/pappersvaror-produktion/2K26QK6I63IJV</t>
+          <t>https://www.allabolag.se/5563231132/pappersgrossisten-i-jonkoping-aktiebolag</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Pappersgrossisten i Jönköping Aktiebolag</t>
+          <t>Svensk Emballageteknik Aktiebolag</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>Carta/Packaging — grossista carta</t>
+          <t>Carta/Packaging — imballaggi wellpapp</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Fatturato 80.655 KSEK (~7,1 M€) e 14 dipendenti — fonte allabolag/bolagsfakta, es. 2024. Org.nr 556323-1132. AZIENDA DI CONFINE: sotto il target 10-20 M€ ma dentro la fascia tollerabile 5-40 M€. Nota legame di gruppo: capogruppo LOLAB Förvaltnings AB.</t>
+          <t>Fatturato 158.400 KSEK (~14,0 M€) es. 2025 (156.002 KSEK nel 2024) e 36 dipendenti — fonte allabolag/merinfo. Org.nr 556324-8250. IN TARGET. Attività: progettazione, produzione e vendita di imballaggi in wellpapp (cartone ondulato), polistirolo espanso, legno, flightcases. Nota legame di gruppo: controllata di Team ET AB (8 società, 66 addetti, 263,0 MSEK).</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Jan Olof Helge Larsson</t>
+          <t>Göran Rune Forsmark</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -22012,153 +22028,153 @@
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>https://se.linkedin.com/company/pappersgrossisten</t>
+          <t>https://se.linkedin.com/company/svensk-emballageteknik-ab</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>info@pg24.se</t>
+          <t>sales@et.se</t>
         </is>
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>https://pg24.se/</t>
+          <t>https://et.se/</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>Jönköping, Jönköpings län</t>
+          <t>Järfälla, Stockholms län</t>
         </is>
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>https://www.allabolag.se/5563231132/pappersgrossisten-i-jonkoping-aktiebolag</t>
+          <t>https://www.allabolag.se/foretag/svensk-emballageteknik-aktiebolag/j%C3%A4rf%C3%A4lla/f%C3%B6rpackningar-industrin/2K07PTMI5YEN2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>Svensk Emballageteknik Aktiebolag</t>
+          <t>TMG Tabergs AB</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Carta/Packaging — imballaggi wellpapp</t>
+          <t>Carta/Packaging — stampa</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Fatturato 158.400 KSEK (~14,0 M€) es. 2025 (156.002 KSEK nel 2024) e 36 dipendenti — fonte allabolag/merinfo. Org.nr 556324-8250. IN TARGET. Attività: progettazione, produzione e vendita di imballaggi in wellpapp (cartone ondulato), polistirolo espanso, legno, flightcases. Nota legame di gruppo: controllata di Team ET AB (8 società, 66 addetti, 263,0 MSEK).</t>
+          <t>Fatturato 101.130 KSEK (~8,9 M€) e 38 dipendenti — fonte allabolag/krafman, es. 2023. Org.nr 556288-4113. AZIENDA DI CONFINE: poco sotto il target 10-20 M€, dentro la fascia tollerabile. Nota legame di gruppo: controllata di Taberg Media Group AB (org.nr 556600-6648, gruppo di 5 società, ~118-130 addetti, ~269 MSEK ≈ 23,8 M€ — il gruppo nel suo insieme è a target).</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>Göran Rune Forsmark</t>
+          <t>Anders Nyström</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>VD</t>
+          <t>VD (extern verkställande direktör)</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>https://se.linkedin.com/company/svensk-emballageteknik-ab</t>
+          <t>https://www.linkedin.com/company/tmg-tabergs</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>sales@et.se</t>
+          <t>info@tabergmediagroup.se</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>https://et.se/</t>
+          <t>https://tabergmediagroup.se/</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>Järfälla, Stockholms län</t>
+          <t>Taberg (Jönköping), Jönköpings län</t>
         </is>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>https://www.allabolag.se/foretag/svensk-emballageteknik-aktiebolag/j%C3%A4rf%C3%A4lla/f%C3%B6rpackningar-industrin/2K07PTMI5YEN2</t>
+          <t>https://www.allabolag.se/foretag/tmg-tabergs-ab/taberg/tryckerier/2JZZWUPI5YI3L</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>TMG Tabergs AB</t>
+          <t>Bergman &amp; Bergstrand Aktiebolag (Bergstrands Kafferosteri)</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>Carta/Packaging — stampa</t>
+          <t>Caffè — torrefazione + import caffè verde</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Fatturato 101.130 KSEK (~8,9 M€) e 38 dipendenti — fonte allabolag/krafman, es. 2023. Org.nr 556288-4113. AZIENDA DI CONFINE: poco sotto il target 10-20 M€, dentro la fascia tollerabile. Nota legame di gruppo: controllata di Taberg Media Group AB (org.nr 556600-6648, gruppo di 5 società, ~118-130 addetti, ~269 MSEK ≈ 23,8 M€ — il gruppo nel suo insieme è a target).</t>
+          <t>Fatturato 91,2 MSEK (~8,1 M€) 2024 (+18,5%); 16 dipendenti (fonte: allabolag.se, bilancio 2024). Org.nr 556027-6528. SNI 10830 framställning av te och kaffe. Sotto il target ideale, dentro la fascia tollerabile.</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Anders Nyström</t>
+          <t>Fannie Myrén</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>VD (extern verkställande direktör)</t>
+          <t>VD (verkställande direktör)</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/tmg-tabergs</t>
+          <t>https://www.linkedin.com/company/bergstrands-kafferosteri</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>info@tabergmediagroup.se</t>
+          <t>info@bergstrands.se</t>
         </is>
       </c>
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>https://tabergmediagroup.se/</t>
+          <t>https://bergstrands.se/</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>Taberg (Jönköping), Jönköpings län</t>
+          <t>Göteborg (Västra Götalands län)</t>
         </is>
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>https://www.allabolag.se/foretag/tmg-tabergs-ab/taberg/tryckerier/2JZZWUPI5YI3L</t>
+          <t>https://www.allabolag.se/foretag/bergman-bergstrand-aktiebolag/g%C3%B6teborg/livsmedel/2JYG0TSI5YFWD</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>Bergman &amp; Bergstrand Aktiebolag (Bergstrands Kafferosteri)</t>
+          <t>Johan &amp; Nyström Kafferostare &amp; Tehandlare AB</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Caffè — torrefazione + import caffè verde</t>
+          <t>Caffè — torrefazione + import caffè verde (specialty)</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Fatturato 91,2 MSEK (~8,1 M€) 2024 (+18,5%); 16 dipendenti (fonte: allabolag.se, bilancio 2024). Org.nr 556027-6528. SNI 10830 framställning av te och kaffe. Sotto il target ideale, dentro la fascia tollerabile.</t>
+          <t>Fatturato 196,8 MSEK (~17,4 M€) 2024 (-2,9%); 54 dipendenti (fonte: allabolag.se, bilancio 2024). Org.nr 556657-9446. Nota: dal 2016 controllata da Espresso House (EH Group AB). EH Group AB fa capo a JAB Holding: è lì il decisore di compliance.</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>Fannie Myrén</t>
+          <t>Johan Morén</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
@@ -22168,437 +22184,437 @@
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/bergstrands-kafferosteri</t>
+          <t>https://se.linkedin.com/company/johanochnystrom</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>info@bergstrands.se</t>
+          <t>info@johanochnystrom.se</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>https://bergstrands.se/</t>
+          <t>https://johanochnystrom.se/</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>Göteborg (Västra Götalands län)</t>
+          <t>Skogås / Huddinge (Stockholms län)</t>
         </is>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>https://www.allabolag.se/foretag/bergman-bergstrand-aktiebolag/g%C3%B6teborg/livsmedel/2JYG0TSI5YFWD</t>
+          <t>https://www.allabolag.se/foretag/johan-nystr%C3%B6m-kafferostare-tehandlare-ab/skog%C3%A5s/kaffe-och-te-agenturer/2K2746UI63IHV</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>Johan &amp; Nyström Kafferostare &amp; Tehandlare AB</t>
+          <t>Kahls Kaffe Aktiebolag</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>Caffè — torrefazione + import caffè verde (specialty)</t>
+          <t>Caffè — torrefazione + engros/wholesale (kaffe, te, kakao)</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Fatturato 196,8 MSEK (~17,4 M€) 2024 (-2,9%); 54 dipendenti (fonte: allabolag.se, bilancio 2024). Org.nr 556657-9446. Nota: dal 2016 controllata da Espresso House (EH Group AB).</t>
+          <t>Fatturato 344,8 MSEK (~30,5 M€) esercizio 2025 (+32,6%); 47 dipendenti (fonte: allabolag.se). Org.nr 556117-4920. Gruppo: Kahls Holding AB. Sopra il target ideale ma entro la fascia tollerabile (5-40 M€).</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Johan Morén</t>
+          <t>Peter Goodman</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>VD (verkställande direktör)</t>
-        </is>
-      </c>
-      <c r="F70" s="6" t="inlineStr">
-        <is>
-          <t>https://se.linkedin.com/company/johanochnystrom</t>
-        </is>
-      </c>
+          <t>VD (verkställande direktör, esterno)</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="inlineStr"/>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>info@johanochnystrom.se</t>
+          <t>info@kahls.se</t>
         </is>
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>https://johanochnystrom.se/</t>
+          <t>https://www.kahls.se/</t>
         </is>
       </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>Skogås / Huddinge (Stockholms län)</t>
+          <t>Västra Frölunda / Göteborg (Västra Götalands län)</t>
         </is>
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>https://www.allabolag.se/foretag/johan-nystr%C3%B6m-kafferostare-tehandlare-ab/skog%C3%A5s/kaffe-och-te-agenturer/2K2746UI63IHV</t>
+          <t>https://www.allabolag.se/foretag/kahls-kaffe-aktiebolag/v%C3%A4stra-fr%C3%B6lunda/kaffe-och-te-agenturer/2JYZA14I63IHV</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>Kahls Kaffe Aktiebolag</t>
+          <t>Lindvalls Kaffe Aktiebolag</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Caffè — torrefazione + engros/wholesale (kaffe, te, kakao)</t>
+          <t>Caffè — torrefazione + import caffè verde</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Fatturato 344,8 MSEK (~30,5 M€) esercizio 2025 (+32,6%); 47 dipendenti (fonte: allabolag.se). Org.nr 556117-4920. Gruppo: Kahls Holding AB. Sopra il target ideale ma entro la fascia tollerabile (5-40 M€).</t>
+          <t>Fatturato 192,6 MSEK (~17,0 M€) 2024; 181 MSEK 2023; 19 dipendenti (fonte: allabolag.se / bolagsfakta.se, bilanci 2023-2024). Org.nr 556049-5284. Nota: la torrefazione di Uppsala deve lasciare l'immobile entro il 2026 (esproprio Trafikverket).</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Peter Goodman</t>
+          <t>Ulf Lindvall</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>VD (verkställande direktör, esterno)</t>
-        </is>
-      </c>
-      <c r="F71" s="3" t="inlineStr"/>
-      <c r="G71" s="4" t="inlineStr">
-        <is>
-          <t>info@kahls.se</t>
+          <t>VD (verkställande direktör)</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/lindvalls-kaffe-ab</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>n.d.</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>https://www.kahls.se/</t>
+          <t>https://lindvallskaffe.se/</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>Västra Frölunda / Göteborg (Västra Götalands län)</t>
+          <t>Uppsala (Uppsala län)</t>
         </is>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>https://www.allabolag.se/foretag/kahls-kaffe-aktiebolag/v%C3%A4stra-fr%C3%B6lunda/kaffe-och-te-agenturer/2JYZA14I63IHV</t>
+          <t>https://www.allabolag.se/foretag/lindvalls-kaffe-aktiebolag/uppsala/livsmedel/2JYKPMCI5YFWD</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>Lindvalls Kaffe Aktiebolag</t>
+          <t>Lykke Coffee Farms AB</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>Caffè — torrefazione + import caffè verde</t>
+          <t>Caffè — coltivazione, import caffè verde + torrefazione</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>Fatturato 192,6 MSEK (~17,0 M€) 2024; 181 MSEK 2023; 19 dipendenti (fonte: allabolag.se / bolagsfakta.se, bilanci 2023-2024). Org.nr 556049-5284. Nota: la torrefazione di Uppsala deve lasciare l'immobile entro il 2026 (esproprio Trafikverket).</t>
+          <t>Fatturato 57,8 MSEK (~5,1 M€) 2024 (+28,7%); 13 dipendenti (gruppo di 4 società: 23 dipendenti, 55,0 MSEK) (fonte: allabolag.se / bolagsfakta.se, bilancio 2024). Org.nr 556764-1575.</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Ulf Lindvall</t>
+          <t>Johan Wellander</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>VD (verkställande direktör)</t>
+          <t>Ordförande / grundare (nessun VD registrato)</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/lindvalls-kaffe-ab</t>
-        </is>
-      </c>
-      <c r="G72" s="5" t="inlineStr">
-        <is>
-          <t>n.d.</t>
+          <t>https://sv.linkedin.com/company/lykke-coffee-farms</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>oj@lykkegardar.se</t>
         </is>
       </c>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>https://lindvallskaffe.se/</t>
+          <t>https://www.lykkegardar.se/</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>Uppsala (Uppsala län)</t>
+          <t>Farsta / Stockholm (Stockholms län)</t>
         </is>
       </c>
       <c r="J72" s="5" t="inlineStr">
         <is>
-          <t>https://www.allabolag.se/foretag/lindvalls-kaffe-aktiebolag/uppsala/livsmedel/2JYKPMCI5YFWD</t>
+          <t>https://www.allabolag.se/foretag/lykke-coffee-farms-ab/farsta/jordbruk/2K2TVQFI63IHJ</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>Lykke Coffee Farms AB</t>
+          <t>Nordiska Kaffebolaget H. Hansson &amp; Co Aktiebolag</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>Caffè — coltivazione, import caffè verde + torrefazione</t>
+          <t>Caffè — import/agenzia caffè e tè, engros</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Fatturato 57,8 MSEK (~5,1 M€) 2024 (+28,7%); 13 dipendenti (gruppo di 4 società: 23 dipendenti, 55,0 MSEK) (fonte: allabolag.se / bolagsfakta.se, bilancio 2024). Org.nr 556764-1575.</t>
-        </is>
-      </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>Johan Wellander</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="inlineStr">
-        <is>
-          <t>Ordförande / grundare (nessun VD registrato)</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>https://sv.linkedin.com/company/lykke-coffee-farms</t>
-        </is>
-      </c>
+          <t>Fatturato 54,7 MSEK (~4,8 M€) 2024 (+8,4%); 17 dipendenti (14 nel 2023) (fonte: allabolag.se, bilancio 2024). Org.nr 556083-2379. SNI 46370 kaffe/te agenturer. Taglia appena sotto la fascia tollerabile ma importatore/agente puro. Capogruppo WB Stockholm AB (org.nr 556705-8754, stessa sede) - holding/operativa di proprieta familiare; gruppo di 5 societa, 3 controllate.</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr"/>
+      <c r="E73" s="3" t="inlineStr"/>
+      <c r="F73" s="3" t="inlineStr"/>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>oj@lykkegardar.se</t>
+          <t>info@sibyllans.se</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>https://www.lykkegardar.se/</t>
+          <t>https://sibyllans.se/</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr">
         <is>
-          <t>Farsta / Stockholm (Stockholms län)</t>
+          <t>Stockholm (Stockholms län)</t>
         </is>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>https://www.allabolag.se/foretag/lykke-coffee-farms-ab/farsta/jordbruk/2K2TVQFI63IHJ</t>
+          <t>https://www.allabolag.se/foretag/nordiska-kaffebolaget-h.-hansson-co-aktiebolag/stockholm/kaffe-och-te-agenturer/2JYRXQ3I63IHV</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>Nordiska Kaffebolaget H. Hansson &amp; Co Aktiebolag</t>
+          <t>Tehuset Java Aktiebolag</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>Caffè — import/agenzia caffè e tè, engros</t>
+          <t>Caffè — import e commercio caffè e tè (engros + retail)</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Fatturato 54,7 MSEK (~4,8 M€) 2024 (+8,4%); 17 dipendenti (14 nel 2023) (fonte: allabolag.se, bilancio 2024). Org.nr 556083-2379. SNI 46370 kaffe/te agenturer. Taglia appena sotto la fascia tollerabile ma importatore/agente puro. Capogruppo WB Stockholm AB (org.nr 556705-8754, stessa sede) - holding/operativa di proprieta familiare; gruppo di 5 societa, 3 controllate.</t>
+          <t>Fatturato 62,4 MSEK (~5,5 M€); 26 dipendenti (fonte: allabolag.se / merinfo.se, ultimo bilancio disponibile). Org.nr 556311-4957. Controllata da Javaimporten i Sverige AB (org.nr 556779-5033, SNI 46370, VD Fredrik August Skeppstedt).</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr"/>
       <c r="E74" s="5" t="inlineStr"/>
-      <c r="F74" s="5" t="inlineStr"/>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/tehuset-java</t>
+        </is>
+      </c>
       <c r="G74" s="6" t="inlineStr">
         <is>
-          <t>info@sibyllans.se</t>
+          <t>order@tehusetjava.se</t>
         </is>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>https://sibyllans.se/</t>
+          <t>https://www.tehusetjava.se/</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>Stockholm (Stockholms län)</t>
+          <t>Lund (Skåne län)</t>
         </is>
       </c>
       <c r="J74" s="5" t="inlineStr">
         <is>
-          <t>https://www.allabolag.se/foretag/nordiska-kaffebolaget-h.-hansson-co-aktiebolag/stockholm/kaffe-och-te-agenturer/2JYRXQ3I63IHV</t>
+          <t>https://www.allabolag.se/foretag/tehuset-java-aktiebolag/lund/livsmedel/2K04UZ1I5YFWD</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>Tehuset Java Aktiebolag</t>
+          <t>Aktiebolaget Cool &amp; Candy</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Caffè — import e commercio caffè e tè (engros + retail)</t>
+          <t>Cacao/Cioccolato — engros/wholesale zucchero, cioccolato e confetteria</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Fatturato 62,4 MSEK (~5,5 M€); 26 dipendenti (fonte: allabolag.se / merinfo.se, ultimo bilancio disponibile). Org.nr 556311-4957. Controllata da Javaimporten i Sverige AB (org.nr 556779-5033, SNI 46370, VD Fredrik August Skeppstedt).</t>
-        </is>
-      </c>
-      <c r="D75" s="3" t="inlineStr"/>
-      <c r="E75" s="3" t="inlineStr"/>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/tehuset-java</t>
-        </is>
-      </c>
-      <c r="G75" s="4" t="inlineStr">
-        <is>
-          <t>order@tehusetjava.se</t>
-        </is>
-      </c>
-      <c r="H75" s="4" t="inlineStr">
-        <is>
-          <t>https://www.tehusetjava.se/</t>
+          <t>Fatturato 196,7 MSEK (~17,4 M€) esercizio 2022 (+9,0%); 19-22 dipendenti (fonte: allabolag.se / bolagsfakta.se). Org.nr 556330-4137. SNI 46360 partihandel med socker, choklad och sockerkonfektyrer. Fa parte del gruppo Humble Group AB.</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>Jens Peter Thomas Persson</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>VD (verkställande direktör, esterno)</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr"/>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>n.d.</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr">
         <is>
-          <t>Lund (Skåne län)</t>
+          <t>Ystad (Skåne län)</t>
         </is>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>https://www.allabolag.se/foretag/tehuset-java-aktiebolag/lund/livsmedel/2K04UZ1I5YFWD</t>
+          <t>https://www.allabolag.se/foretag/aktiebolaget-cool-candy/ystad/livsmedel-agenturer-och-grossister/2K08WY1I63IIN</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>Aktiebolaget Cool &amp; Candy</t>
+          <t>Candy People AB</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>Cacao/Cioccolato — engros/wholesale zucchero, cioccolato e confetteria</t>
+          <t>Cacao/Cioccolato — import/export ed engros di confetteria e cioccolato</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>Fatturato 196,7 MSEK (~17,4 M€) esercizio 2022 (+9,0%); 19-22 dipendenti (fonte: allabolag.se / bolagsfakta.se). Org.nr 556330-4137. SNI 46360 partihandel med socker, choklad och sockerkonfektyrer. Fa parte del gruppo Humble Group AB.</t>
+          <t>Fatturato 251,2 MSEK (~22,2 M€) 2024; 10 dipendenti nella società AB (fonte: allabolag.se / bolagsfakta.se, bilancio 2024). Org.nr 556696-8375. Gruppo di 5 società, capogruppo J &amp; J Holding AB.</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Jens Peter Thomas Persson</t>
+          <t>Anna Youssef Bebinno</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>VD (verkställande direktör, esterno)</t>
-        </is>
-      </c>
-      <c r="F76" s="5" t="inlineStr"/>
-      <c r="G76" s="5" t="inlineStr">
-        <is>
-          <t>n.d.</t>
-        </is>
-      </c>
-      <c r="H76" s="5" t="inlineStr">
-        <is>
-          <t>n.d.</t>
+          <t>VD (verkställande direktör)</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>https://se.linkedin.com/company/candy-people-ab</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>info@candypeople.com</t>
+        </is>
+      </c>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>https://candypeople.se/</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>Ystad (Skåne län)</t>
+          <t>Malmö (Skåne län)</t>
         </is>
       </c>
       <c r="J76" s="5" t="inlineStr">
         <is>
-          <t>https://www.allabolag.se/foretag/aktiebolaget-cool-candy/ystad/livsmedel-agenturer-och-grossister/2K08WY1I63IIN</t>
+          <t>https://www.allabolag.se/foretag/candy-people-ab/malm%C3%B6/livsmedel/2K2FGAFI5YFWD</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>Candy People AB</t>
+          <t>Delicato Bakverk Aktiebolag</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Cacao/Cioccolato — import/export ed engros di confetteria e cioccolato</t>
+          <t>Cacao/Cioccolato — produzione dolciaria con cioccolato e cacao</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>Fatturato 251,2 MSEK (~22,2 M€) 2024; 10 dipendenti nella società AB (fonte: allabolag.se / bolagsfakta.se, bilancio 2024). Org.nr 556696-8375. Gruppo di 5 società, capogruppo J &amp; J Holding AB.</t>
+          <t>Fatturato 396,6 MSEK (~35,1 M€) esercizio 2025 (+12,2%); 125 dipendenti (fonte: allabolag.se / bolagsfakta.se). Org.nr 556119-4720. Gruppo di 8 società, capogruppo Belvéns Bageri AB. Entro la fascia tollerabile (5-40 M€). Moderbolag diretto Belveens Bageri AB; capogruppo di vertice Eldkvarn AB (gruppo di 8 societa)'.</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>Anna Youssef Bebinno</t>
+          <t>Johan Berg</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>VD (verkställande direktör)</t>
+          <t>VD (verkställande direktör, esterno)</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>https://se.linkedin.com/company/candy-people-ab</t>
+          <t>https://se.linkedin.com/company/delicato-bakverk-ab</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>info@candypeople.com</t>
+          <t>info@delicato.se</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>https://candypeople.se/</t>
+          <t>https://www.delicato.se/</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t>Malmö (Skåne län)</t>
+          <t>Segeltorp / Huddinge (Stockholms län)</t>
         </is>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>https://www.allabolag.se/foretag/candy-people-ab/malm%C3%B6/livsmedel/2K2FGAFI5YFWD</t>
+          <t>https://www.allabolag.se/foretag/delicato-bakverk-aktiebolag/segeltorp/livsmedel-tillverkning/2JYZPB4I63IIO</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>Delicato Bakverk Aktiebolag</t>
+          <t>Grahns Konfektyr AB</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>Cacao/Cioccolato — produzione dolciaria con cioccolato e cacao</t>
+          <t>Cacao/Cioccolato — produzione confetteria e prodotti di cioccolato</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Fatturato 396,6 MSEK (~35,1 M€) esercizio 2025 (+12,2%); 125 dipendenti (fonte: allabolag.se / bolagsfakta.se). Org.nr 556119-4720. Gruppo di 8 società, capogruppo Belvéns Bageri AB. Entro la fascia tollerabile (5-40 M€). Moderbolag diretto Belveens Bageri AB; capogruppo di vertice Eldkvarn AB (gruppo di 8 societa)'.</t>
+          <t>Fatturato 259,7 MSEK (~23,0 M€) 2024; 208,6 MSEK 2023; 60-65 dipendenti (fonte: allabolag.se / bolagsfakta.se). Org.nr 556724-8884. Controllata dal gruppo quotato Humble Group AB - compliance decisa a livello di capogruppo. Esercizio 2024 in perdita (-2,2 MSEK) nonostante +24,5% di fatturato'.</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Johan Berg</t>
+          <t>Eric Jesper Lööw</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -22608,49 +22624,49 @@
       </c>
       <c r="F78" s="6" t="inlineStr">
         <is>
-          <t>https://se.linkedin.com/company/delicato-bakverk-ab</t>
+          <t>https://www.linkedin.com/company/grahns-konfektyr-ab</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>info@delicato.se</t>
+          <t>info@grahns.se</t>
         </is>
       </c>
       <c r="H78" s="6" t="inlineStr">
         <is>
-          <t>https://www.delicato.se/</t>
+          <t>https://www.grahns.se/</t>
         </is>
       </c>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>Segeltorp / Huddinge (Stockholms län)</t>
+          <t>Skövde (Västra Götalands län)</t>
         </is>
       </c>
       <c r="J78" s="5" t="inlineStr">
         <is>
-          <t>https://www.allabolag.se/foretag/delicato-bakverk-aktiebolag/segeltorp/livsmedel-tillverkning/2JYZPB4I63IIO</t>
+          <t>https://www.allabolag.se/foretag/grahns-konfektyr-ab/sk%C3%B6vde/konfektyrer-choklad-/2K2LGQCI5YF14</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>Grahns Konfektyr AB</t>
+          <t>Malmö Chokladfabrik AB</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Cacao/Cioccolato — produzione confetteria e prodotti di cioccolato</t>
+          <t>Cacao/Cioccolato — bean-to-bar, tostatura propria di fave di cacao</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Fatturato 259,7 MSEK (~23,0 M€) 2024; 208,6 MSEK 2023; 60-65 dipendenti (fonte: allabolag.se / bolagsfakta.se). Org.nr 556724-8884. Controllata dal gruppo quotato Humble Group AB - compliance decisa a livello di capogruppo. Esercizio 2024 in perdita (-2,2 MSEK) nonostante +24,5% di fatturato'.</t>
+          <t>Fatturato 42,6 MSEK (~3,8 M€) esercizio 2025 (+31,6%); 16 dipendenti (fonte: allabolag.se / bolagsfakta.se). Org.nr 556664-6286. Sotto la fascia tollerabile ma importatore diretto di fave di cacao (tostatura interna) e in forte crescita.</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>Eric Jesper Lööw</t>
+          <t>Roger Stenfeldt</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
@@ -22660,101 +22676,97 @@
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/grahns-konfektyr-ab</t>
+          <t>https://se.linkedin.com/company/malm%C3%B6-chokladfabrik-ab</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>info@grahns.se</t>
+          <t>order@malmochokladfabrik.se</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>https://www.grahns.se/</t>
+          <t>https://malmochokladfabrik.se/</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr">
         <is>
-          <t>Skövde (Västra Götalands län)</t>
+          <t>Oxie / Malmö (Skåne län)</t>
         </is>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>https://www.allabolag.se/foretag/grahns-konfektyr-ab/sk%C3%B6vde/konfektyrer-choklad-/2K2LGQCI5YF14</t>
+          <t>https://www.allabolag.se/foretag/malm%C3%B6-chokladfabrik-ab/oxie/livsmedel/2K28JRII5YFWD</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>Malmö Chokladfabrik AB</t>
+          <t>Svenska Gummihuset Aktiebolag</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>Cacao/Cioccolato — bean-to-bar, tostatura propria di fave di cacao</t>
+          <t>Gomma — commercio all'ingrosso di pneumatici e cerchi (däck och fälg)</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>Fatturato 42,6 MSEK (~3,8 M€) esercizio 2025 (+31,6%); 16 dipendenti (fonte: allabolag.se / bolagsfakta.se). Org.nr 556664-6286. Sotto la fascia tollerabile ma importatore diretto di fave di cacao (tostatura interna) e in forte crescita.</t>
+          <t>Fatturato 146.493 KSEK (~13,0 M€) e 12 dipendenti — bilancio 2025 (fonte allabolag/bolagsfakta); org.nr 556750-7297. In pieno target come fatturato; distributore, quindi organico ridotto.</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Roger Stenfeldt</t>
+          <t>Joakim Granath</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>VD (verkställande direktör, esterno)</t>
-        </is>
-      </c>
-      <c r="F80" s="6" t="inlineStr">
-        <is>
-          <t>https://se.linkedin.com/company/malm%C3%B6-chokladfabrik-ab</t>
-        </is>
-      </c>
-      <c r="G80" s="6" t="inlineStr">
-        <is>
-          <t>order@malmochokladfabrik.se</t>
+          <t>VD (verkställande direktör)</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="inlineStr"/>
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>n.d.</t>
         </is>
       </c>
       <c r="H80" s="6" t="inlineStr">
         <is>
-          <t>https://malmochokladfabrik.se/</t>
+          <t>https://www.gummihuset.se/</t>
         </is>
       </c>
       <c r="I80" s="5" t="inlineStr">
         <is>
-          <t>Oxie / Malmö (Skåne län)</t>
+          <t>Eskilstuna, Södermanlands län</t>
         </is>
       </c>
       <c r="J80" s="5" t="inlineStr">
         <is>
-          <t>https://www.allabolag.se/foretag/malm%C3%B6-chokladfabrik-ab/oxie/livsmedel/2K28JRII5YFWD</t>
+          <t>https://www.allabolag.se/5567507297/svenska-gummihuset-aktiebolag</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>Svenska Gummihuset Aktiebolag</t>
+          <t>Tretorn Sweden AB</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Gomma — commercio all'ingrosso di pneumatici e cerchi (däck och fälg)</t>
+          <t>Gomma — stivali in gomma (gummistövlar), palline da tennis e accessori</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>Fatturato 146.493 KSEK (~13,0 M€) e 12 dipendenti — bilancio 2025 (fonte allabolag/bolagsfakta); org.nr 556750-7297. In pieno target come fatturato; distributore, quindi organico ridotto.</t>
+          <t>Fatturato 322.415 KSEK (~28,5 M€) e 48 dipendenti — bilancio 2024 (fonte allabolag/bolagsfakta); org.nr 559012-5695. Sopra la fascia ideale ma entro il tollerabile; capogruppo Thevea Brands Group AB (svedese).</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>Joakim Granath</t>
+          <t>Vasko Markovski</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
@@ -22770,39 +22782,39 @@
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>https://www.gummihuset.se/</t>
+          <t>https://se.tretorn.com/</t>
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr">
         <is>
-          <t>Eskilstuna, Södermanlands län</t>
+          <t>Helsingborg, Skåne län</t>
         </is>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>https://www.allabolag.se/5567507297/svenska-gummihuset-aktiebolag</t>
+          <t>https://www.allabolag.se/foretag/tretorn-sweden-ab/helsingborg/konfektion/2KG7SLBI63II4</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>Tretorn Sweden AB</t>
+          <t>Aktiebolaget Johan Hansson</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>Gomma — stivali in gomma (gummistövlar), palline da tennis e accessori</t>
+          <t>Mangimi/Soia — produzione mangimi (EDELfoder) e commercio cereali/materie prime proteiche</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>Fatturato 322.415 KSEK (~28,5 M€) e 48 dipendenti — bilancio 2024 (fonte allabolag/bolagsfakta); org.nr 559012-5695. Sopra la fascia ideale ma entro il tollerabile; capogruppo Thevea Brands Group AB (svedese).</t>
+          <t>Fatturato 191.871 KSEK (~17,0 M€) e 13 dipendenti — bilancio 2025 (fonte bolagsfakta/allabolag); org.nr 556037-8746. In pieno target di fatturato; organico ridotto tipico del settore mangimi/cereali.</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Vasko Markovski</t>
+          <t>Jessica Anlér</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -22810,278 +22822,278 @@
           <t>VD (verkställande direktör)</t>
         </is>
       </c>
-      <c r="F82" s="5" t="inlineStr"/>
-      <c r="G82" s="5" t="inlineStr">
-        <is>
-          <t>n.d.</t>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>https://se.linkedin.com/company/ab-johan-hansson</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>kontakt@johanhansson.se</t>
         </is>
       </c>
       <c r="H82" s="6" t="inlineStr">
         <is>
-          <t>https://se.tretorn.com/</t>
+          <t>https://johanhansson.se/</t>
         </is>
       </c>
       <c r="I82" s="5" t="inlineStr">
         <is>
-          <t>Helsingborg, Skåne län</t>
+          <t>Uppsala, Uppsala län</t>
         </is>
       </c>
       <c r="J82" s="5" t="inlineStr">
         <is>
-          <t>https://www.allabolag.se/foretag/tretorn-sweden-ab/helsingborg/konfektion/2KG7SLBI63II4</t>
+          <t>https://www.bolagsfakta.se/5560378746-Aktiebolaget_Johan_Hansson</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>Aktiebolaget Johan Hansson</t>
+          <t>Aktiebolaget Västerbottens Fodercentral</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Mangimi/Soia — produzione mangimi (EDELfoder) e commercio cereali/materie prime proteiche</t>
+          <t>Mangimi/Soia — fabbrica mangimi composti per bovini/suini, cereali e materie prime</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>Fatturato 191.871 KSEK (~17,0 M€) e 13 dipendenti — bilancio 2025 (fonte bolagsfakta/allabolag); org.nr 556037-8746. In pieno target di fatturato; organico ridotto tipico del settore mangimi/cereali.</t>
-        </is>
-      </c>
-      <c r="D83" s="3" t="inlineStr">
-        <is>
-          <t>Jessica Anlér</t>
-        </is>
-      </c>
-      <c r="E83" s="3" t="inlineStr">
-        <is>
-          <t>VD (verkställande direktör)</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="inlineStr">
-        <is>
-          <t>https://se.linkedin.com/company/ab-johan-hansson</t>
-        </is>
-      </c>
+          <t>Fatturato 170.138 KSEK (~15,1 M€) e 14 dipendenti — bilancio 2022 (fonte bolagsfakta/allabolag); org.nr 556061-1765. In pieno target di fatturato; organico ridotto tipico del settore mangimi.</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr"/>
+      <c r="E83" s="3" t="inlineStr"/>
+      <c r="F83" s="3" t="inlineStr"/>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>kontakt@johanhansson.se</t>
+          <t>info@fodercentralen.se</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>https://johanhansson.se/</t>
+          <t>https://fodercentralen.se/</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr">
         <is>
-          <t>Uppsala, Uppsala län</t>
+          <t>Holmsund (Umeå), Västerbottens län</t>
         </is>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>https://www.bolagsfakta.se/5560378746-Aktiebolaget_Johan_Hansson</t>
+          <t>https://www.bolagsfakta.se/5560611765-Aktiebolaget_Vasterbottens_Fodercentral</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>Aktiebolaget Västerbottens Fodercentral</t>
+          <t>Forsbecks Eftr. Aktiebolag</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>Mangimi/Soia — fabbrica mangimi composti per bovini/suini, cereali e materie prime</t>
+          <t>Mangimi/Soia — commercio all'ingrosso di cereali, sementi e mangimi per zootecnia</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>Fatturato 170.138 KSEK (~15,1 M€) e 14 dipendenti — bilancio 2022 (fonte bolagsfakta/allabolag); org.nr 556061-1765. In pieno target di fatturato; organico ridotto tipico del settore mangimi.</t>
-        </is>
-      </c>
-      <c r="D84" s="5" t="inlineStr"/>
-      <c r="E84" s="5" t="inlineStr"/>
+          <t>ATTENZIONE TAGLIA: fatturato 589.951 KSEK (~52,2 M€) con soli 31-35 dipendenti — bilancio 2022 (fonte allabolag/bolagsfakta); org.nr 556002-3417. Sopra la soglia dei 40 M€ ma è PMI indipendente (famiglia Johansson dal 1953) con fatturato gonfiato dal costo della materia prima (ca. 100.000 t di cereali/anno).</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>Per Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>VD (verkställande direktör)</t>
+        </is>
+      </c>
       <c r="F84" s="5" t="inlineStr"/>
       <c r="G84" s="6" t="inlineStr">
         <is>
-          <t>info@fodercentralen.se</t>
+          <t>per-magnus.johansson@forsbecks.com</t>
         </is>
       </c>
       <c r="H84" s="6" t="inlineStr">
         <is>
-          <t>https://fodercentralen.se/</t>
+          <t>https://www.forsbecks.se/</t>
         </is>
       </c>
       <c r="I84" s="5" t="inlineStr">
         <is>
-          <t>Holmsund (Umeå), Västerbottens län</t>
+          <t>Skänninge (Mjölby), Östergötlands län</t>
         </is>
       </c>
       <c r="J84" s="5" t="inlineStr">
         <is>
-          <t>https://www.bolagsfakta.se/5560611765-Aktiebolaget_Vasterbottens_Fodercentral</t>
+          <t>https://www.allabolag.se/foretag/forsbecks-eftr.-aktiebolag/sk%C3%A4nninge/grossister/2JYALIXI63IGS</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>Forsbecks Eftr. Aktiebolag</t>
+          <t>Hönryds Kvarn Aktiebolag</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Mangimi/Soia — commercio all'ingrosso di cereali, sementi e mangimi per zootecnia</t>
+          <t>Mangimi/Soia — molino e produzione mangimi composti, stoccaggio e commercio cereali</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>ATTENZIONE TAGLIA: fatturato 589.951 KSEK (~52,2 M€) con soli 31-35 dipendenti — bilancio 2022 (fonte allabolag/bolagsfakta); org.nr 556002-3417. Sopra la soglia dei 40 M€ ma è PMI indipendente (famiglia Johansson dal 1953) con fatturato gonfiato dal costo della materia prima (ca. 100.000 t di cereali/anno).</t>
-        </is>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t>Per Magnus Johansson</t>
-        </is>
-      </c>
-      <c r="E85" s="3" t="inlineStr">
-        <is>
-          <t>VD (verkställande direktör)</t>
-        </is>
-      </c>
+          <t>Fatturato 198.432 KSEK (~17,6 M€) e 9-11 dipendenti — bilancio 2023 (11 dipendenti nel 2024) (fonte bolagsfakta/allabolag); org.nr 556421-9284. In pieno target di fatturato; organico ridotto tipico del settore mangimi.</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr"/>
+      <c r="E85" s="3" t="inlineStr"/>
       <c r="F85" s="3" t="inlineStr"/>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>per-magnus.johansson@forsbecks.com</t>
+          <t>erika@honrydskvarn.se</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>https://www.forsbecks.se/</t>
+          <t>https://www.honrydskvarn.se/</t>
         </is>
       </c>
       <c r="I85" s="3" t="inlineStr">
         <is>
-          <t>Skänninge (Mjölby), Östergötlands län</t>
+          <t>Morup (Falkenberg), Hallands län</t>
         </is>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>https://www.allabolag.se/foretag/forsbecks-eftr.-aktiebolag/sk%C3%A4nninge/grossister/2JYALIXI63IGS</t>
+          <t>https://www.bolagsfakta.se/5564219284-Honryds_Kvarn_Aktiebolag</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>Hönryds Kvarn Aktiebolag</t>
+          <t>Liljeholmens Stearinfabriks AB</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>Mangimi/Soia — molino e produzione mangimi composti, stoccaggio e commercio cereali</t>
+          <t>Olio di palma — candele in stearina (stearina di origine vegetale/palma), produzione a Oskarshamn</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>Fatturato 198.432 KSEK (~17,6 M€) e 9-11 dipendenti — bilancio 2023 (11 dipendenti nel 2024) (fonte bolagsfakta/allabolag); org.nr 556421-9284. In pieno target di fatturato; organico ridotto tipico del settore mangimi.</t>
-        </is>
-      </c>
-      <c r="D86" s="5" t="inlineStr"/>
-      <c r="E86" s="5" t="inlineStr"/>
-      <c r="F86" s="5" t="inlineStr"/>
+          <t>Fatturato 346.300 KSEK (~30,6 M€) nel 2024 e 93-98 dipendenti (93 nel 2023, fatturato 375.373 KSEK) (fonte bolagsfakta/allabolag); org.nr 556041-6348. Sopra la fascia ideale ma entro il tollerabile. Controllata via Liljeholmens Group AB / ALG Holding AB, capogruppo di vertice Tibia Intressenter AB; controlla Liljeholmens Fastighets AB e ASP-HOLMBLAD A/S (DK). Fatturato 2024 in calo dell'8% sul 2023'.</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>Anna Lundqvist</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>VD (verkställande direktör)</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>https://se.linkedin.com/company/liljeholmens-stearinfabriks-ab</t>
+        </is>
+      </c>
       <c r="G86" s="6" t="inlineStr">
         <is>
-          <t>erika@honrydskvarn.se</t>
+          <t>anna.lundqvist@liljeholmens.se</t>
         </is>
       </c>
       <c r="H86" s="6" t="inlineStr">
         <is>
-          <t>https://www.honrydskvarn.se/</t>
+          <t>https://liljeholmens.se/</t>
         </is>
       </c>
       <c r="I86" s="5" t="inlineStr">
         <is>
-          <t>Morup (Falkenberg), Hallands län</t>
+          <t>Oskarshamn, Kalmar län</t>
         </is>
       </c>
       <c r="J86" s="5" t="inlineStr">
         <is>
-          <t>https://www.bolagsfakta.se/5564219284-Honryds_Kvarn_Aktiebolag</t>
+          <t>https://www.bolagsfakta.se/5560416348-Liljeholmens_Stearinfabriks_AB</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>Liljeholmens Stearinfabriks AB</t>
+          <t>Aktiebolaget Ginsten Slakteri</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Olio di palma — candele in stearina (stearina di origine vegetale/palma), produzione a Oskarshamn</t>
+          <t>Bovini/Carne — macello (bovini, suini, ovini) e commercio carni, in gruppo familiare</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Fatturato 346.300 KSEK (~30,6 M€) nel 2024 e 93-98 dipendenti (93 nel 2023, fatturato 375.373 KSEK) (fonte bolagsfakta/allabolag); org.nr 556041-6348. Sopra la fascia ideale ma entro il tollerabile. Controllata via Liljeholmens Group AB / ALG Holding AB, capogruppo di vertice Tibia Intressenter AB; controlla Liljeholmens Fastighets AB e ASP-HOLMBLAD A/S (DK). Fatturato 2024 in calo dell'8% sul 2023'.</t>
-        </is>
-      </c>
-      <c r="D87" s="3" t="inlineStr">
-        <is>
-          <t>Anna Lundqvist</t>
-        </is>
-      </c>
-      <c r="E87" s="3" t="inlineStr">
-        <is>
-          <t>VD (verkställande direktör)</t>
-        </is>
-      </c>
-      <c r="F87" s="4" t="inlineStr">
-        <is>
-          <t>https://se.linkedin.com/company/liljeholmens-stearinfabriks-ab</t>
-        </is>
-      </c>
-      <c r="G87" s="4" t="inlineStr">
-        <is>
-          <t>anna.lundqvist@liljeholmens.se</t>
+          <t>Fatturato 227.210 KSEK (~20,1 M€) — bilancio 2024, +18,2% (fonte allabolag/bolagsfakta); org.nr 556257-9861. Nella società capofila risultano 0 dipendenti registrati (personale in società del gruppo). In pieno target di fatturato. Capogruppo: Aktiebolaget Joh. M. Johansson, Kött- &amp; Charkuteriaffär (gruppo familiare di 4 societa').</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr"/>
+      <c r="E87" s="3" t="inlineStr"/>
+      <c r="F87" s="3" t="inlineStr"/>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>n.d.</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>https://liljeholmens.se/</t>
+          <t>https://www.ginsten.se/</t>
         </is>
       </c>
       <c r="I87" s="3" t="inlineStr">
         <is>
-          <t>Oskarshamn, Kalmar län</t>
+          <t>Harplinge (Halmstad), Hallands län</t>
         </is>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>https://www.bolagsfakta.se/5560416348-Liljeholmens_Stearinfabriks_AB</t>
+          <t>https://www.allabolag.se/foretag/aktiebolaget-ginsten-slakteri/harplinge/livsmedel/2JZTE39I5YFWD</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>Aktiebolaget Ginsten Slakteri</t>
+          <t>Nya Siljans Chark AB</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>Bovini/Carne — macello (bovini, suini, ovini) e commercio carni, in gruppo familiare</t>
+          <t>Bovini/Carne — macello e salumificio (bovini, suini, selvaggina)</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Fatturato 227.210 KSEK (~20,1 M€) — bilancio 2024, +18,2% (fonte allabolag/bolagsfakta); org.nr 556257-9861. Nella società capofila risultano 0 dipendenti registrati (personale in società del gruppo). In pieno target di fatturato. Capogruppo: Aktiebolaget Joh. M. Johansson, Kött- &amp; Charkuteriaffär (gruppo familiare di 4 societa').</t>
-        </is>
-      </c>
-      <c r="D88" s="5" t="inlineStr"/>
-      <c r="E88" s="5" t="inlineStr"/>
+          <t>Fatturato 222.064 KSEK (~19,7 M€) e 81 dipendenti — bilancio 2024 (fonte bolagsfakta/allabolag); org.nr 559256-8256. In pieno target. Capogruppo Siljans Chark Holding AB (holding dei soci Par Nilsson e Mats Arjes); societa subentrata alla precedente Siljans Chark dopo il fallimento; controlla Norrlandsgarden AB e Siljanfood AB'.</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>Jonas Björ</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>VD (verkställande direktör)</t>
+        </is>
+      </c>
       <c r="F88" s="5" t="inlineStr"/>
       <c r="G88" s="5" t="inlineStr">
         <is>
@@ -23090,39 +23102,39 @@
       </c>
       <c r="H88" s="6" t="inlineStr">
         <is>
-          <t>https://www.ginsten.se/</t>
+          <t>https://siljanschark.se/</t>
         </is>
       </c>
       <c r="I88" s="5" t="inlineStr">
         <is>
-          <t>Harplinge (Halmstad), Hallands län</t>
+          <t>Mora, Dalarnas län</t>
         </is>
       </c>
       <c r="J88" s="5" t="inlineStr">
         <is>
-          <t>https://www.allabolag.se/foretag/aktiebolaget-ginsten-slakteri/harplinge/livsmedel/2JZTE39I5YFWD</t>
+          <t>https://www.bolagsfakta.se/5592568256-Nya_Siljans_Chark_AB</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>Nya Siljans Chark AB</t>
+          <t>Närkes Slakteri i Gällersta Aktiebolag</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Bovini/Carne — macello e salumificio (bovini, suini, selvaggina)</t>
+          <t>Bovini/Carne — macello e sezionamento bovini, suini e ovini, intermediazione capi vivi</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>Fatturato 222.064 KSEK (~19,7 M€) e 81 dipendenti — bilancio 2024 (fonte bolagsfakta/allabolag); org.nr 559256-8256. In pieno target. Capogruppo Siljans Chark Holding AB (holding dei soci Par Nilsson e Mats Arjes); societa subentrata alla precedente Siljans Chark dopo il fallimento; controlla Norrlandsgarden AB e Siljanfood AB'.</t>
+          <t>Fatturato 209.054 KSEK (~18,5 M€) e 27 dipendenti — bilancio 2024 (fonte bolagsfakta/allabolag); org.nr 556514-4861. In pieno target. Controllata da Kott &amp; Charkgruppen i Narke AB (gruppo di 5 societa)'.</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>Jonas Björ</t>
+          <t>Lars Mats Larsson</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
@@ -23131,77 +23143,29 @@
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr"/>
-      <c r="G89" s="3" t="inlineStr">
-        <is>
-          <t>n.d.</t>
+      <c r="G89" s="4" t="inlineStr">
+        <is>
+          <t>info@narkesslakteri.se</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>https://siljanschark.se/</t>
+          <t>https://narkesslakteri.se/</t>
         </is>
       </c>
       <c r="I89" s="3" t="inlineStr">
         <is>
-          <t>Mora, Dalarnas län</t>
+          <t>Örebro (Attersta/Gällersta), Örebro län</t>
         </is>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>https://www.bolagsfakta.se/5592568256-Nya_Siljans_Chark_AB</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="5" t="inlineStr">
-        <is>
-          <t>Närkes Slakteri i Gällersta Aktiebolag</t>
-        </is>
-      </c>
-      <c r="B90" s="5" t="inlineStr">
-        <is>
-          <t>Bovini/Carne — macello e sezionamento bovini, suini e ovini, intermediazione capi vivi</t>
-        </is>
-      </c>
-      <c r="C90" s="5" t="inlineStr">
-        <is>
-          <t>Fatturato 209.054 KSEK (~18,5 M€) e 27 dipendenti — bilancio 2024 (fonte bolagsfakta/allabolag); org.nr 556514-4861. In pieno target. Controllata da Kott &amp; Charkgruppen i Narke AB (gruppo di 5 societa)'.</t>
-        </is>
-      </c>
-      <c r="D90" s="5" t="inlineStr">
-        <is>
-          <t>Lars Mats Larsson</t>
-        </is>
-      </c>
-      <c r="E90" s="5" t="inlineStr">
-        <is>
-          <t>VD (verkställande direktör)</t>
-        </is>
-      </c>
-      <c r="F90" s="5" t="inlineStr"/>
-      <c r="G90" s="6" t="inlineStr">
-        <is>
-          <t>info@narkesslakteri.se</t>
-        </is>
-      </c>
-      <c r="H90" s="6" t="inlineStr">
-        <is>
-          <t>https://narkesslakteri.se/</t>
-        </is>
-      </c>
-      <c r="I90" s="5" t="inlineStr">
-        <is>
-          <t>Örebro (Attersta/Gällersta), Örebro län</t>
-        </is>
-      </c>
-      <c r="J90" s="5" t="inlineStr">
-        <is>
           <t>https://www.bolagsfakta.se/5565144861-Narkes_Slakteri_i_Gallersta_Aktiebolag</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:J90"/>
+  <autoFilter ref="A2:J89"/>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
@@ -23387,21 +23351,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F69" r:id="rId179"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId180"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F70" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F72" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F71" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F72" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId187"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F73" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F74" r:id="rId191"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId192"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F75" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F76" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId196"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F77" r:id="rId197"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId198"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId199"/>
@@ -23411,27 +23375,24 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F79" r:id="rId203"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId204"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F80" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F82" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId209"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F83" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F86" r:id="rId217"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId218"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F87" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId223"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26634,7 +26595,7 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Fatturato della BV non pubblicato (accesso premium su company.info). Riferimenti di stampa: 11,5 M€ di fatturato nel 2011; fatturato al consumo della catena oltre 20 M€ nel 2016 (fonte: MT/Sprout, Fonk Magazine). 77 dipendenti (fonte: company.info / OpenKvK, 2025). KVK 34093465, A. Hofmanweg 3 Haarlem. Torrefazione + confezionamento tè + catena in franchising dal 1826. BORDERLINE: potrebbe superare i 40 M€ di giro d'affari di insegna — da verificare prima del contatto.</t>
+          <t>Fatturato della BV NON pubblicato (bilancio abbreviato; accesso premium su company.info). Serie storica di stampa: 8,5 M€ di fatturato con 43 FTE e 29 negozi — dato di un'intervista del 2007, NON recente; 11,5 M€ nel 2011; oltre 20 M€ di fatturato al consumo dell'insegna nel 2016 (+4,6%). Ultimo esercizio noto: fatturato +20% (RetailTrends), crescita in parte spiegata dal raddoppio dei prezzi dell'arabica nel 2024 riversato sui listini. Oggi oltre 40 negozi specializzati in NL e BE; 77 dipendenti (company.info/OpenKvK, 2025). KVK 34093465, A. Hofmanweg 3 Haarlem; torrefazione + confezionamento tè + catena in franchising dal 1826. Direttore generale unico dal gennaio 2026 Bert Jongsma (primo esterno alla famiglia).</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
@@ -26682,7 +26643,7 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Fatturato non pubblicato nei registri (bilancio abbreviato); stima di terze parti ~12,4 M$ (rocketreach — non ufficiale, da verificare). 94 dipendenti dichiarati dall'azienda (2025). KVK 31022124, costituita 28-03-1978 (marchi Smit e Dorlas dal 1822). Torrefazione artigianale per l'horeca. Se la stima regge, rientra nel target 10-20 M€.</t>
+          <t>Fatturato NON pubblicato nei registri (bilancio abbreviato); nessuna cifra reperibile su fonti pubbliche — la stima di terze parti ~12,4 M$ (rocketreach) non e' verificabile e va trattata come non ufficiale. Dipendenti: 90 secondo l'azienda (88 secondo altra fonte). KVK 33239607 (numero corretto), Nijverheidsweg 1, 3641 RP Mijdrecht; societa' costituita nel 1992, attivita' di torrefazione dal 1822, oltre 190 anni di servizio all'horeca.</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr"/>
@@ -32198,7 +32159,7 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>Fatturato 31.327.285 EUR (Trends Top/NBB, ultimo esercizio pubblicato); n. impresa BE 0430.105.126</t>
+          <t>Fatturato 31.327.285 EUR (Trends Top/NBB, ultimo esercizio pubblicato); n. impresa BE 0430.105.126 Legame di gruppo: controllata del gruppo quotato svedese HEXPOL AB (Nasdaq Stockholm) — la compliance EUDR si decide a livello di capogruppo.</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr"/>
@@ -32706,7 +32667,7 @@
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Fatturato ca. 11 milioni EUR (VILT, stampa settoriale agroalimentare belga); organico ca. 50 persone (40 operai + 10 impiegati); capacita' 75.000 bovini ed equini/anno, ca. 125.000 bovini macellati per conto terzi. Numero d'impresa BE non verificato su fonte pubblica. Fa parte del gruppo Cadus NV (macelli in Belgio) ed e' socio Febev. N. impresa BE 0832.292.464.</t>
+          <t>Fatturato ca. 11 milioni EUR (VILT, stampa settoriale agroalimentare belga); organico ca. 50 persone (40 operai + 10 impiegati); capacita' 75.000 bovini ed equini/anno, ca. 125.000 bovini macellati per conto terzi. Numero d'impresa BE non verificato su fonte pubblica. Fa parte del gruppo Cadus NV (macelli in Belgio) ed e' socio Febev. N. impresa BE 0832.292.464. Legame di gruppo: unità della holding Cadus (quattro macelli bovini in Belgio, ~25% delle macellazioni bovine nazionali) — stesso decisore di Slachthuis Velzeke.</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr"/>
@@ -32834,7 +32795,7 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>50-99 dipendenti (Companyweb, dati piu' recenti); capacita' 2.000 bovini/settimana, uno dei maggiori macelli bovini del Belgio; n. impresa BE 1018.071.121. Fatturato NON disponibile: entita' costituita il 30/12/2024 (cambio di proprieta' nel 2025), nessun bilancio con cifra d'affari ancora depositato. Altri amministratori indicati: Guy De Bruycker, Johan Castelein.</t>
+          <t>50-99 dipendenti (Companyweb, dati piu' recenti); capacita' 2.000 bovini/settimana, uno dei maggiori macelli bovini del Belgio; n. impresa BE 1018.071.121. Fatturato NON disponibile: entita' costituita il 30/12/2024 (cambio di proprieta' nel 2025), nessun bilancio con cifra d'affari ancora depositato. Altri amministratori indicati: Guy De Bruycker, Johan Castelein. Legame di gruppo: dal 01-01-2025 controllata dalla holding Cadus, che l'ha rilevata da Vion Food Group — stesso decisore di Euro Meat Group.</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">

--- a/MyEUDR_Lead_Mapping_v2.xlsx
+++ b/MyEUDR_Lead_Mapping_v2.xlsx
@@ -3599,7 +3599,7 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>~5,5 mln € (2024); ~28 dip.; bean-to-bar (importa cacao)</t>
+          <t>~5,5 mln € (2024); ~28 dip.; bean-to-bar (importa cacao) Legame di gruppo non dichiarato: dall'agosto 2017 il 99% del capitale è di Ferrarelle S.p.A. Società Benefit.</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
@@ -10542,7 +10542,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>≈8,4 M€ (2024, Asiakastieto)</t>
+          <t>≈8,4 M€ (2024, Asiakastieto) Legame di gruppo non dichiarato: JET-Puu Oy fa parte di JETTA-Korporaatio (gruppo Jetta-Talo, case prefabbricate).</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -11802,7 +11802,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>≈31,4 M€ / ~119 dip. (2024, Asiakastieto)</t>
+          <t>≈31,4 M€ / ~119 dip. (2024, Asiakastieto) Legame di gruppo non dichiarato: acquisita dal gruppo estone Thermory (Livonia Partners), che ne detiene il 63% — il sito aziendale ha una pagina «Thermory Group».</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -14495,7 +14495,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>41 dipendenti (unità produttiva); le fonti aziendali parlano di ~40 addetti sotto la guida di Lasse Sørensen, figlio del fondatore Bøje Sørensen. Fatturato non pubblicato separatamente nelle fonti consultate. Con ~40 addetti in produzione i ricavi si collocano verosimilmente nella fascia bassa del target (stima non verificata). CVR 12224494, attività dal 01.01.1988 (fondata nel 1972 da Bøje Sørensen), sede Højagervej 5-7, 6623 Vorbasse; showroom su appuntamento a Tranegårdsvej 27, 2900 Hellerup. Centralino +45 75 33 33 44. Specializzata in finestre e porte per edifici storici e vincolati. LEGAME DI GRUPPO IMPORTANTE: dal 2017 controllata da INWIDO DENMARK A/S, parte del gruppo quotato svedese Inwido — la due diligence EUDR potrebbe essere centralizzata a livello di gruppo, il che riduce la probabilità di acquisto autonomo del software. Lead da qualificare con cautela.</t>
+          <t>41 dipendenti (unità produttiva); le fonti aziendali parlano di ~40 addetti sotto la guida di Lasse Sørensen, figlio del fondatore Bøje Sørensen. Fatturato non pubblicato separatamente nelle fonti consultate. Con ~40 addetti in produzione i ricavi si collocano verosimilmente nella fascia bassa del target (stima non verificata). CVR 12224494, attività dal 01.01.1988 (fondata nel 1972 da Bøje Sørensen), sede Højagervej 5-7, 6623 Vorbasse; showroom su appuntamento a Tranegårdsvej 27, 2900 Hellerup. Centralino +45 75 33 33 44. Specializzata in finestre e porte per edifici storici e vincolati. LEGAME DI GRUPPO IMPORTANTE: dal 2017 controllata da INWIDO DENMARK A/S, parte del gruppo quotato svedese Inwido — la due diligence EUDR potrebbe essere centralizzata a livello di gruppo, il che riduce la probabilità di acquisto autonomo del software. Lead da qualificare con cautela. Legame di gruppo non dichiarato: dal 2017 la società è controllata da INWIDO DENMARK A/S, parte del gruppo quotato svedese Inwido AB — la compliance EUDR si decide a livello di capogruppo.</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Circa 155 dipendenti complessivi (66 nell'unità di Thyholm + 106 nell'unità di Thisted secondo i registri; il totale aziendale dichiarato è ~155). Fatturato non pubblicato nelle banche dati consultate (campo vuoto su proff). AZIENDA DI CONFINE: con questo organico i ricavi potrebbero superare la fascia target — da verificare a bilancio prima del contatto. CVR 17010344, costituita 01.01.1993, capitale sociale 5.000.000 DKK. Centralino +45 96 91 22 22. Sito ufficiale hvidbjergvinduet.dk CONFERMATO in questa sessione. LEGAME DI GRUPPO: controllata da Hvidbjerg i A/S. Produce finestre e porte in legno/alluminio a Nors (Thy): soggetta a EUDR per il legname immesso sul mercato UE.</t>
+          <t>Circa 155 dipendenti complessivi (66 nell'unità di Thyholm + 106 nell'unità di Thisted secondo i registri; il totale aziendale dichiarato è ~155). Fatturato non pubblicato nelle banche dati consultate (campo vuoto su proff). AZIENDA DI CONFINE: con questo organico i ricavi potrebbero superare la fascia target — da verificare a bilancio prima del contatto. CVR 17010344, costituita 01.01.1993, capitale sociale 5.000.000 DKK. Centralino +45 96 91 22 22. Sito ufficiale hvidbjergvinduet.dk CONFERMATO in questa sessione. LEGAME DI GRUPPO: controllata da Hvidbjerg i A/S. Produce finestre e porte in legno/alluminio a Nors (Thy): soggetta a EUDR per il legname immesso sul mercato UE. Capogruppo corretta: la società è controllata dal gruppo ACO Nordic, a sua volta parte del gruppo tedesco ACO (famiglia Ahlmann), dal rilevamento del gruppo Plastmo nel 1995 — NON da «Hvidbjerg i A/S» come indicato in precedenza.</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -16567,7 +16567,7 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>75 dipendenti; produzione ~70.000 t/anno di carta (dato 2021). Proprietà Buur Invest A/S + dirigenti operativi (indipendente danese dal 2005). Fatturato non reperito su fonte verificabile: con questi volumi è AZIENDA DI CONFINE, plausibilmente sopra i 40 M€ - verificare regnskab prima del contatto.</t>
+          <t>75 dipendenti; produzione ~70.000 t/anno di carta (dato 2021). Legame di gruppo: acquisita dal gruppo statunitense quotato SONOCO Products Company (NYSE: SON); in precedenza Buur Invest A/S e dirigenti operativi. L'indipendenza danese dichiarata in precedenza non è più attuale. Fatturato non reperito su fonte verificabile: con questi volumi è AZIENDA DI CONFINE, plausibilmente sopra i 40 M€ - verificare regnskab prima del contatto.</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -16667,7 +16667,7 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>100-200 dipendenti complessivi (62 a Langeskov, 10 a Vejle); bruttofortjeneste 146 mio DKK nel 2024 (~19,6 M€ di solo margine lordo). CVR 16427284, NACE 172100, Erik Stoks Allé 4. Capogruppo STOK Denmark ApS. AZIENDA DI CONFINE / SOPRA FASCIA: il fatturato è verosimilmente &gt;50 M€ - da verificare prima del contatto, potenzialmente da escludere.</t>
+          <t>100-200 dipendenti complessivi (62 a Langeskov, 10 a Vejle); bruttofortjeneste 146 mio DKK nel 2024 (~19,6 M€ di solo margine lordo). CVR 16427284, NACE 172100, Erik Stoks Allé 4. Capogruppo STOK Denmark ApS. AZIENDA DI CONFINE / SOPRA FASCIA: il fatturato è verosimilmente &gt;50 M€ - da verificare prima del contatto, potenzialmente da escludere. Il campo nominava solo la capogruppo formale: dal 30.04.2024 STOK Denmark ApS è partecipata in maggioranza dal fondo di private equity statunitense A&amp;M Capital Europe.</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -18829,7 +18829,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Fatturato 51.898 KSEK (~4,6 M€) e 43 dipendenti — bilancio 2024 (fonte bolagsfakta/allabolag); org.nr 556474-7797. Sotto la soglia minima ideale: in Svezia le concerie sono pochissime e questa è la principale conceria indipendente attiva.</t>
+          <t>Fatturato 51.898 KSEK (~4,6 M€) e 43 dipendenti — bilancio 2024 (fonte bolagsfakta/allabolag); org.nr 556474-7797. Sotto la soglia minima ideale: in Svezia le concerie sono pochissime e questa è una delle poche concerie attive. Legame di gruppo: moderbolag Axel Bodéns Handels Aktiebolag — l'indipendenza dichiarata in precedenza non è confermata.</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -19185,7 +19185,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>≈7,0 M€ / 17 dip. (allabolag 2025: 79 011 KSEK; 2024: 53 348 KSEK con 15 dip.) · org.nr 556103-8695 · sotto la fascia target 10-20 M€, tenuta per copertura · membro SÅGAB</t>
+          <t>≈7,0 M€ / 17 dip. (allabolag 2025: 79 011 KSEK; 2024: 53 348 KSEK con 15 dip.) · org.nr 556103-8695 · sotto la fascia target 10-20 M€, tenuta per copertura · membro SÅGAB Legame di gruppo non dichiarato: moderbolag Brännfors Holding AB.</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr"/>
@@ -21001,7 +21001,7 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Fatturato 208.856 KSEK (~18,5 M€) e 63 dipendenti nel 2024 (fonte allabolag.se). Org.nr 556361-9161. Pienamente in target.</t>
+          <t>Fatturato 208.856 KSEK (~18,5 M€) e 63 dipendenti nel 2024 (fonte allabolag.se). Org.nr 556361-9161. Pienamente in target. Legame di gruppo non dichiarato: moderbolag WINO Holding AB, koncernmoder Nordh Invest i Stockaryd AB. Nota di trend: l'esercizio 2024 segna -31% sul 2023 e chiude in perdita (-742 KSEK).</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -21441,7 +21441,7 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Fatturato 248.036 KSEK (~22,0 M€) e 99 dipendenti — fonte allabolag/bolagsfakta, es. 2024. Org.nr 559063-9349. AZIENDA DI CONFINE: appena sopra il target 10-20 M€, ben dentro la fascia tollerabile. Tipografia indipendente a controllo familiare (collegata a Billes Tryckeri Förvaltning AB, org.nr 556259-9034). E-mail diretta VD pubblicata nelle fonti: niklas.bille@billes.se.</t>
+          <t>Fatturato 248.036 KSEK (~22,0 M€) e 99 dipendenti — fonte allabolag/bolagsfakta, es. 2024. Org.nr 559063-9349. AZIENDA DI CONFINE: appena sopra il target 10-20 M€, ben dentro la fascia tollerabile. Legame di gruppo: moderbolag Billes Tryckeri Holding AB (gruppo di 4 società, 122 dipendenti, 264,0 MSEK aggregati); Billes Tryckeri Förvaltning AB (org.nr 556259-9034) è invece una società immobiliare, non la capogruppo. E-mail diretta VD pubblicata nelle fonti: niklas.bille@billes.se.</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
@@ -24251,7 +24251,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Fatturato NON pubblicato (BV con bilancio abbreviato). Numero dipendenti non pubblicato nelle fonti consultate; l'azienda si autodefinisce produttore di pallet di media dimensione (fonte sito aziendale, 2025). KVK 24247802. Azienda familiare dagli anni '50, oggi guidata da Leander Jonkers, nipote del fondatore L. Verhoeven. Produce pallet CP, block e stringer pallet e imballaggi su misura.</t>
+          <t>Fatturato NON pubblicato (BV con bilancio abbreviato). Numero dipendenti non pubblicato nelle fonti consultate; l'azienda si autodefinisce produttore di pallet di media dimensione (fonte sito aziendale, 2025). KVK 24247802. Azienda familiare dagli anni '50, oggi guidata da Leander Jonkers, nipote del fondatore L. Verhoeven. Produce pallet CP, block e stringer pallet e imballaggi su misura. Struttura di gruppo non dichiarata: opera in gruppo con la consociata Zagerij Verhoeven (Harskamp), Kist&amp;Co (Ridderkerk) e Harskamp Timber (Harskamp).</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -25611,7 +25611,7 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Fatturato NON pubblicato (BV con bilancio abbreviato). 43-45 dipendenti (fonte drimble.nl / stagemarkt.nl, 2024-2025). KVK 09001229. Cartiera indipendente attiva dal 1618, specialità: carta per belle arti, acquerello, carta filigranata e carta circolare da residui del cliente. Membro Koninklijke VNP. Stima fatturato in fascia bassa del target (specialty paper, alto valore unitario).</t>
+          <t>Fatturato NON pubblicato (BV con bilancio abbreviato). 43-45 dipendenti (fonte drimble.nl / stagemarkt.nl, 2024-2025). KVK 09001229. Cartiera attiva dal 1618, dal 1° luglio 1998 nel gruppo francese quotato Exacompta Clairefontaine S.A., specialità: carta per belle arti, acquerello, carta filigranata e carta circolare da residui del cliente. Membro Koninklijke VNP. Stima fatturato in fascia bassa del target (specialty paper, alto valore unitario).</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -26891,7 +26891,7 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Fatturato non pubblicato. 20-49 dipendenti (fonte: transfirm.nl / Dun &amp; Bradstreet, dati KVK 2025). KVK 34146292. Costituita nel 2000. Sede Galvanistraat 10, Rotterdam. Produzione di cioccolato e prodotti dolciari a base di cacao.</t>
+          <t>Fatturato non pubblicato. 20-49 dipendenti (fonte: transfirm.nl / Dun &amp; Bradstreet, dati KVK 2025). KVK 34146292. Costituita nel 2000. Sede Galvanistraat 10, Rotterdam. Produzione di cioccolato e prodotti dolciari a base di cacao. Legame di gruppo non dichiarato: acquisita nel maggio 2009 dal gruppo belga Baronie (Baronie-de Heer B.V., stessa sede di Galvanistraat, Rotterdam).</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
@@ -28679,7 +28679,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Fatturato 17.158.424 EUR (bilancio depositato BNB, via Trends Top/Pappers.be) - 3a azienda del settore cuoio/calzatura in Belgio; n. impresa BE 0401.249.606. Nel cuore della fascia target. Concia esclusivamente vegetale di groppe e collo bovini di provenienza europea; fa capo al Groupe Saturne (Tannerie Fortier Beaulieu + Masure).</t>
+          <t>Fatturato 17.158.424 EUR (bilancio depositato BNB, via Trends Top/Pappers.be) - 3a azienda del settore cuoio/calzatura in Belgio; n. impresa BE 0401.249.606. Nel cuore della fascia target. Concia esclusivamente vegetale di groppe e collo bovini di provenienza europea; fa capo al Groupe Saturne (Tannerie Fortier Beaulieu + Masure). Legame di gruppo non dichiarato: dal 2014 la società fa parte del Groupe Saturne (holding francese Financière Saturne) insieme alla Tannerie Fortier-Beaulieu di Roanne.</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -31531,7 +31531,7 @@
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Fatturato 8.796.906 € (ultimo bilancio depositato NBB, deposito 26-06-2025; 8.421.952 € e 54° posto di settore su trendstop.knack.be). N. impresa BE 0433.283.558. Sede Avenue Vésale 12, 1300 Wavre; maison storica (marchio dal 1932), rete di ~20 boutique in Belgio e 15 in Francia. Sotto la fascia ottimale ma dentro il range tollerabile 5-40 M€.</t>
+          <t>Fatturato 8.796.906 € (ultimo bilancio depositato NBB, deposito 26-06-2025; 8.421.952 € e 54° posto di settore su trendstop.knack.be). N. impresa BE 0433.283.558. Sede Avenue Vésale 12, 1300 Wavre; maison storica (marchio dal 1932), rete di ~20 boutique in Belgio e 15 in Francia. Sotto la fascia ottimale ma dentro il range tollerabile 5-40 M€. Legame di gruppo non dichiarato: controllata dal gruppo Neuhaus dal 2013, che figura direttamente fra gli amministratori (denominazione registrale abbreviata «CPR CHOCOLATIER»).</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr"/>
@@ -31823,7 +31823,7 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Fatturato 25.731.148 € e 175,1 FTE (fonte: trendstop.levif.be / companyweb.be, ultimo bilancio depositato NBB, deposito 08-07-2025); 30° posto nel settore cioccolato e dolciumi. N. impresa BE 0722.764.519. Firmataria di Beyond Chocolate (impegni su deforestazione e tracciabilità del cacao). Nella parte alta del range tollerabile 5-40 M€.</t>
+          <t>Fatturato 25.731.148 € e 175,1 FTE (fonte: trendstop.levif.be / companyweb.be, ultimo bilancio depositato NBB, deposito 08-07-2025); 30° posto nel settore cioccolato e dolciumi. N. impresa BE 0722.764.519. Firmataria di Beyond Chocolate (impegni su deforestazione e tracciabilità del cacao). Nella parte alta del range tollerabile 5-40 M€. Legame di gruppo non dichiarato: non è una PMI indipendente ma lo stabilimento bruxellese di Godiva, ceduto nel giugno 2019 al fondo MBK Partners insieme alle attività Godiva di Giappone, Corea del Sud e Oceania.</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
@@ -32063,7 +32063,7 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Fatturato 16.954.714 EUR (Trends Top/NBB, ultimo esercizio pubblicato); 83,3 FTE; n. impresa BE 0694.906.812</t>
+          <t>Fatturato 16.954.714 EUR (Trends Top/NBB, ultimo esercizio pubblicato); 83,3 FTE; n. impresa BE 0694.906.812 Legame di gruppo non dichiarato: è l'entità Benelux del Gruppo Hannecard, che fa capo a Hannecard NV (BE 0892.311.512, stessa sede di Ronse); dal febbraio 2022 nel capitale è entrata BNP Paribas Fortis Private Equity.</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr"/>
@@ -36565,7 +36565,7 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Fatturato ca. 18 Mio. € - ca. 180 dipendenti (fonte Wikipedia/dati aziendali, ultimo dato pubblico 2018; ordine di grandezza confermato da cash.at). Firmenbuch FN 397683d, LG Wiener Neustadt; UID ATU67943648. Titolare del marchio storico viennese Niemetz Schwedenbomben (dal 1926) rilevato nel 2013; produzione trasferita a Wiener Neudorf. IN TARGET 10-20 M€. Grande utilizzatore di cioccolato/cacao per il rivestimento dei prodotti = operatore/commerciante EUDR.</t>
+          <t>Fatturato ca. 18 Mio. € - ca. 180 dipendenti (fonte Wikipedia/dati aziendali, ultimo dato pubblico 2018; ordine di grandezza confermato da cash.at). Firmenbuch FN 397683d, LG Wiener Neustadt; UID ATU67943648. Titolare del marchio storico viennese Niemetz Schwedenbomben (dal 1926) rilevato nel 2013; produzione trasferita a Wiener Neudorf. IN TARGET 10-20 M€. Grande utilizzatore di cioccolato/cacao per il rivestimento dei prodotti = operatore/commerciante EUDR. Legame di gruppo non dichiarato: l'entità austriaca è la succursale (Niederlassung Österreich) di Heidi Chocolat SA, con sede a Zug (Svizzera) — la compliance EUDR si decide a livello di gruppo.</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">

--- a/MyEUDR_Lead_Mapping_v2.xlsx
+++ b/MyEUDR_Lead_Mapping_v2.xlsx
@@ -2907,7 +2907,7 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Fatturato fascia 3-6 mln € (bilancio 2024, Registro Imprese)</t>
+          <t>⚠ SOTTO SOGLIA: ricavi 4.041.633 € nel bilancio 2024, con una perdita di 254.359 € — sotto il minimo di 5 M€ della forbice target. Tenuta nel censimento per copertura di filiera, su decisione del cliente. Fatturato fascia 3-6 mln € (bilancio 2024, Registro Imprese)</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr"/>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>n.d. (PMI artigianale; lavora cacao)</t>
+          <t>⚠ SOTTO SOGLIA: fatturato ~2,7 mln € — sotto il minimo di 5 M€ della forbice target. Tenuta nel censimento per copertura di filiera, su decisione del cliente. n.d. (PMI artigianale; lavora cacao)</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>~4 mln € (2024), in forte crescita; bean-to-bar (tosta cacao)</t>
+          <t>⚠ SOTTO SOGLIA: fatturato ~4 mln € (2024) — sotto il minimo di 5 M€ della forbice target. Tenuta nel censimento per copertura di filiera, su decisione del cliente. ~4 mln € (2024), in forte crescita; bean-to-bar (tosta cacao)</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>~59,3 mln € (2024); 50-99 dip. — sopra soglia ma PMI indip. specializzata in soia</t>
+          <t>⚠ FUORI TAGLIA: 59.292.815 € nel 2024 (utile 2.866.674 €), 50-99 dipendenti — sopra il tetto di ~50 M€. PMI indipendente specializzata in soia. Tenuta nel censimento su decisione del cliente.</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>~56 mln € — sopra soglia, PMI indip.; oli/grassi incl. palma raffinato</t>
+          <t>⚠ FUORI TAGLIA: 61.262.679 € di ricavi nel bilancio 2024 (+9% sul 2023), ca. 60 dipendenti — sopra il tetto di ~50 M€; il dato precedente (~56 mln €) era obsoleto. PMI indipendente; oli e grassi, incluso palma raffinato. Tenuta nel censimento su decisione del cliente.</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr"/>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Umsatz/MA n.d. (dal 1992)</t>
+          <t>⚠ SOTTO SOGLIA: totale di bilancio ~900 mila € (2023, -20,1%) — sotto il minimo di 5 M€ della forbice target. Tenuta nel censimento per copertura di filiera, su decisione del cliente. Umsatz/MA n.d. (dal 1992)</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>&gt;100 MA (gruppo), Umsatz n.d.; importatore gomma naturale — lead EUDR chiave</t>
+          <t>⚠ FUORI TAGLIA: fatturato stimato ca. 75 Mio. €, oltre il tetto di ~50 M€; &gt;100 dipendenti (gruppo). Importatore di gomma naturale — lead EUDR chiave ma fuori dalla forbice di taglia. Tenuta nel censimento su decisione del cliente.</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>&gt;200 MA; familiare; tratta olio di palma, palmisto, oleina, stearina — fascia alta</t>
+          <t>⚠ FUORI TAGLIA: fatturato 138,4 Mio. € (2023), oltre tre volte il tetto di ~50 M€; &gt;200 dipendenti. Impresa familiare; tratta olio di palma, palmisto, oleina e stearina — lead EUDR rilevante ma fuori dalla forbice di taglia. Tenuta nel censimento su decisione del cliente.</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Liikevaihto 3,4 M€ (2024); 19 dip. (Asiakastieto) Controllata di Auroora Yhtiöt Oyj (Tampere) — riqualificare il lead sulla capogruppo o scartare.</t>
+          <t>⚠ SOTTO SOGLIA: 3,4 M€ (2024), in calo dai 4,6 M€ del 2022 — sotto il minimo di 5 M€ della forbice target. Tenuta nel censimento per copertura di filiera, su decisione del cliente. Liikevaihto 3,4 M€ (2024); 19 dip. (Asiakastieto) Controllata di Auroora Yhtiöt Oyj (Tampere) — riqualificare il lead sulla capogruppo o scartare.</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Liikevaihto 3,62 M€ — sotto sweet spot</t>
+          <t>⚠ SOTTO SOGLIA: 3,7 M€ e 23 dipendenti (2025) — sotto il minimo di 5 M€ della forbice target. Tenuta nel censimento per copertura di filiera, su decisione del cliente. Liikevaihto 3,62 M€ — sotto sweet spot</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -10294,7 +10294,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>≈44 M€ / ~49 dip. (2024, Finder/Proff) — fascia alta, vicino al limite</t>
+          <t>⚠ SOPRA LA FORBICE: 42,9-44 M€ (2025) — sopra il tetto di 40 M€ della forbice tollerabile, ma sotto i ~50 M€ di esclusione. Il campo lo definiva «vicino al limite»: il limite è già superato. ≈44 M€ / ~49 dip. (2024, Finder/Proff) — fascia alta, vicino al limite</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -10790,7 +10790,7 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Liikevaihto 3,09 M€ (2023) — sotto sweet spot</t>
+          <t>⚠ SOTTO SOGLIA: liikevaihto 3,1 M€ (2024), 25 dipendenti — sotto il minimo di 5 M€ della forbice target. Tenuta nel censimento per copertura di filiera, su decisione del cliente. Liikevaihto 3,09 M€ (2023) — sotto sweet spot</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Liikevaihto 2,92 M€ (2024); ~20 dip. (Vainu/Asiakastieto)</t>
+          <t>⚠ SOTTO SOGLIA: liikevaihto 2,92 M€ (esercizio chiuso 05/2024, -28,8%), 16 dipendenti — sotto il minimo di 5 M€ della forbice target. Tenuta nel censimento per copertura di filiera, su decisione del cliente. Liikevaihto 2,92 M€ (2024); ~20 dip. (Vainu/Asiakastieto)</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -11078,7 +11078,7 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>≈5 M€ / ~18 dip. (2024-25, Asiakastieto)</t>
+          <t>⚠ SOTTO SOGLIA: 4,9 M€ (2025, in calo), 18 dipendenti — sotto il minimo di 5 M€ della forbice target. Tenuta nel censimento per copertura di filiera, su decisione del cliente. ≈5 M€ / ~18 dip. (2024-25, Asiakastieto)</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -11126,7 +11126,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Liikevaihto 1,3 M€ (2024); 17 dip. (Vainu/Asiakastieto)</t>
+          <t>⚠ SOTTO SOGLIA: liikevaihto 1,3 M€ (2024), 17 dipendenti, perdita operativa 183 k€ — sotto il minimo di 5 M€ della forbice target. Tenuta nel censimento per copertura di filiera, su decisione del cliente. Liikevaihto 1,3 M€ (2024); 17 dip. (Vainu/Asiakastieto)</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -11706,7 +11706,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>n.d. (liikevaihto non pubblicato)</t>
+          <t>⚠ SOTTO SOGLIA: liikevaihto 1,7 M€ (2024), 14 dipendenti, perdita operativa 45 k€ — sotto il minimo di 5 M€ della forbice target. Tenuta nel censimento per copertura di filiera, su decisione del cliente. n.d. (liikevaihto non pubblicato)</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr"/>
@@ -11894,7 +11894,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Liikevaihto 3,8 M€ (2025); 19 dip. (Asiakastieto/Vainu)</t>
+          <t>⚠ SOTTO SOGLIA: 3,8 M€ (2025, +13,6%), 19 dipendenti — sotto il minimo di 5 M€ della forbice target. Tenuta nel censimento per copertura di filiera, su decisione del cliente. Liikevaihto 3,8 M€ (2025); 19 dip. (Asiakastieto/Vainu)</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -12250,7 +12250,7 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>~28 dip. (2024); liikevaihto n.d. (gruppo Orapac)</t>
+          <t>⚠ SOTTO SOGLIA: liikevaihto ~2,0 M€, 28 dipendenti — sotto il minimo di 5 M€ della forbice target. Tenuta nel censimento per copertura di filiera, su decisione del cliente. ~28 dip. (2024); liikevaihto n.d. (gruppo Orapac)</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -13270,7 +13270,7 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>n.d.; importatore di caffè verde (da India/Bali) + vendita all'ingrosso — EUDR-rilevante</t>
+          <t>⚠ SOTTO SOGLIA: liikevaihto 130.000 € — sotto il minimo di 5 M€ della forbice target. Tenuta nel censimento per copertura di filiera, su decisione del cliente. n.d.; importatore di caffè verde (da India/Bali) + vendita all'ingrosso — EUDR-rilevante</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr"/>
@@ -16667,7 +16667,7 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>100-200 dipendenti complessivi (62 a Langeskov, 10 a Vejle); bruttofortjeneste 146 mio DKK nel 2024 (~19,6 M€ di solo margine lordo). CVR 16427284, NACE 172100, Erik Stoks Allé 4. Capogruppo STOK Denmark ApS. AZIENDA DI CONFINE / SOPRA FASCIA: il fatturato è verosimilmente &gt;50 M€ - da verificare prima del contatto, potenzialmente da escludere. Il campo nominava solo la capogruppo formale: dal 30.04.2024 STOK Denmark ApS è partecipata in maggioranza dal fondo di private equity statunitense A&amp;M Capital Europe.</t>
+          <t>⚠ FUORI TAGLIA: fatturato reale ca. 92 M€, oltre il tetto di ~50 M€ (il campo dava una stima «&gt;50 M€»). Tenuta nel censimento su decisione del cliente. 100-200 dipendenti complessivi (62 a Langeskov, 10 a Vejle); bruttofortjeneste 146 mio DKK nel 2024 (~19,6 M€ di solo margine lordo). CVR 16427284, NACE 172100, Erik Stoks Allé 4. Capogruppo STOK Denmark ApS. AZIENDA DI CONFINE / SOPRA FASCIA: il fatturato è verosimilmente &gt;50 M€ - da verificare prima del contatto, potenzialmente da escludere. Il campo nominava solo la capogruppo formale: dal 30.04.2024 STOK Denmark ApS è partecipata in maggioranza dal fondo di private equity statunitense A&amp;M Capital Europe.</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -17111,7 +17111,7 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>n.d. - fatturato e dipendenti non pubblicati nelle fonti consultate. Registrata nella categoria 'Kaffe og te - agentur og engros'; risteri proprio a Nr. Bjertvej 67, 6000 Kolding, import diretto di caffè verde. Gazelle Børsen 2023 e 2024. Fonte: proff.dk / nordiccoffeehouse.dk. Taglia probabilmente sotto il target: da verificare. · CVR 39807122</t>
+          <t>⚠ SOTTO SOGLIA: bruttofortjeneste 3,3 mio. DKK (~0,44 M€), 5-10 dipendenti — sotto il minimo di 5 M€ della forbice target. Tenuta nel censimento per copertura di filiera, su decisione del cliente. n.d. - fatturato e dipendenti non pubblicati nelle fonti consultate. Registrata nella categoria 'Kaffe og te - agentur og engros'; risteri proprio a Nr. Bjertvej 67, 6000 Kolding, import diretto di caffè verde. Gazelle Børsen 2023 e 2024. Fonte: proff.dk / nordiccoffeehouse.dk. Taglia probabilmente sotto il target: da verificare. · CVR 39807122</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
@@ -17679,7 +17679,7 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Fatturato non pubblicato (n.d.); bruttofortjeneste 3,2 mio DKK (~0,4 M EUR) nel 2025. ATTENZIONE: sotto la fascia target. Fonte: proff.dk (CVR 75144911), anno 2025 Capogruppo BEA HOLDING ApS; presidente CdA Pernille Andersen; distributore di imballaggi ed elastici, FUORI dalla forbice 5-40 M EUR.</t>
+          <t>⚠ SOTTO SOGLIA: bruttofortjeneste 3,2 mio. DKK (~0,43 M€) — sotto il minimo di 5 M€ della forbice target. Tenuta nel censimento per copertura di filiera, su decisione del cliente. Fatturato non pubblicato (n.d.); bruttofortjeneste 3,2 mio DKK (~0,4 M EUR) nel 2025. ATTENZIONE: sotto la fascia target. Fonte: proff.dk (CVR 75144911), anno 2025 Capogruppo BEA HOLDING ApS; presidente CdA Pernille Andersen; distributore di imballaggi ed elastici, FUORI dalla forbice 5-40 M EUR.</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
@@ -17831,7 +17831,7 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>n.d. (fatturato e dipendenti non pubblicati nelle fonti accessibili); societa fondata nel 1984, commercio e produzione di pneumatici industriali. Fonte: proff.dk (CVR 87222810)</t>
+          <t>⚠ SOTTO SOGLIA: bruttofortjeneste 8,06 M DKK nel 2023 (~1,1 M€), 7 dipendenti — sotto il minimo di 5 M€ della forbice target. Tenuta nel censimento per copertura di filiera, su decisione del cliente. n.d. (fatturato e dipendenti non pubblicati nelle fonti accessibili); societa fondata nel 1984, commercio e produzione di pneumatici industriali. Fonte: proff.dk (CVR 87222810)</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
@@ -18271,7 +18271,7 @@
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>Fatturato non pubblicato (n.d.); bruttofortjeneste 10,27 mio DKK (~1,4 M EUR); 4-5 dipendenti (2-10 secondo LinkedIn); importatore/rivenditore di oli vegetali con l'olio di palma come componente principale; oltre 150 mio kg di ingredienti/anno. Fonti: proff.dk (CVR 28119666), LinkedIn aziendale e piano d'azione palma su etiskhandel.dk (2021)</t>
+          <t>⚠ SOTTO SOGLIA: bruttofortjeneste 10,27 M DKK (~1,4 M€), 4-5 addetti — sotto il minimo di 5 M€ della forbice target. Tenuta nel censimento per copertura di filiera, su decisione del cliente. Fatturato non pubblicato (n.d.); bruttofortjeneste 10,27 mio DKK (~1,4 M EUR); 4-5 dipendenti (2-10 secondo LinkedIn); importatore/rivenditore di oli vegetali con l'olio di palma come componente principale; oltre 150 mio kg di ingredienti/anno. Fonti: proff.dk (CVR 28119666), LinkedIn aziendale e piano d'azione palma su etiskhandel.dk (2021)</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
@@ -22901,7 +22901,7 @@
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>ATTENZIONE TAGLIA: fatturato 589.951 KSEK (~52,2 M€) con soli 31-35 dipendenti — bilancio 2022 (fonte allabolag/bolagsfakta); org.nr 556002-3417. Sopra la soglia dei 40 M€ ma è PMI indipendente (famiglia Johansson dal 1953) con fatturato gonfiato dal costo della materia prima (ca. 100.000 t di cereali/anno).</t>
+          <t>⚠ SOPRA LA FORBICE: 505.457 KSEK (~44,7 M€) nell'esercizio 2024 — sopra il tetto di 40 M€ della forbice tollerabile, ma sotto i ~50 M€ di esclusione. Il dato precedente (589.951 KSEK, es. 2022) era obsoleto e sovrastimato. fatturato 589.951 KSEK (~52,2 M€) con soli 31-35 dipendenti — bilancio 2022 (fonte allabolag/bolagsfakta); org.nr 556002-3417. Sopra la soglia dei 40 M€ ma è PMI indipendente (famiglia Johansson dal 1953) con fatturato gonfiato dal costo della materia prima (ca. 100.000 t di cereali/anno).</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
@@ -27875,7 +27875,7 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>Fatturato non pubblicato (BV con deposito abbreviato; dati finanziari solo a pagamento). KVK 75119048 (entita DO IT Organic Food Ingredients B.V., Barneveld; il gruppo DO-IT opera dal 1990 ca.). Trader olandese di ingredienti biologici con rete mondiale di fornitori: soia ca. 15% del giro d'affari e oli/grassi (inclusi palma e cocco) ca. 10% - importatore/operatore EUDR su entrambe le commodity. Numero dipendenti non pubblicato.</t>
+          <t>⚠ FUORI TAGLIA: il gruppo DO IT Organic comunica ca. 125 milioni di € di fatturato con 110 dipendenti, oltre tre volte il tetto di ~50 M€. Tenuta nel censimento su decisione del cliente. Fatturato non pubblicato (BV con deposito abbreviato; dati finanziari solo a pagamento). KVK 75119048 (entita DO IT Organic Food Ingredients B.V., Barneveld; il gruppo DO-IT opera dal 1990 ca.). Trader olandese di ingredienti biologici con rete mondiale di fornitori: soia ca. 15% del giro d'affari e oli/grassi (inclusi palma e cocco) ca. 10% - importatore/operatore EUDR su entrambe le commodity. Numero dipendenti non pubblicato.</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
@@ -30479,7 +30479,7 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>DATO DI FATTURATO NON PUBBLICATO sulle fonti accessibili (companyweb/fincheck/pappers riportano la scheda ma non la cifra d'affari; l'azienda deposita in schema abbreviato). N. impresa BE 0448.350.331, costituita nel 1992. Azienda familiare, fabbricazione di scatole in cartone e articoli d'imballaggio e protezione; officina nel parco industriale di Martinrou, Rue de Rabiseau 12, 6220 Fleurus. AZIENDA DI CONFINE: taglia stimata SOTTO i 5 M€ — inserita per copertura della filiera in Vallonia, da qualificare prima del contatto.</t>
+          <t>⚠ SOTTO SOGLIA: margine lordo 142.075 € — sotto il minimo di 5 M€ della forbice target. Tenuta nel censimento per copertura di filiera, su decisione del cliente. DATO DI FATTURATO NON PUBBLICATO sulle fonti accessibili (companyweb/fincheck/pappers riportano la scheda ma non la cifra d'affari; l'azienda deposita in schema abbreviato). N. impresa BE 0448.350.331, costituita nel 1992. Azienda familiare, fabbricazione di scatole in cartone e articoli d'imballaggio e protezione; officina nel parco industriale di Martinrou, Rue de Rabiseau 12, 6220 Fleurus. AZIENDA DI CONFINE: taglia stimata SOTTO i 5 M€ — inserita per copertura della filiera in Vallonia, da qualificare prima del contatto.</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr"/>
@@ -30947,7 +30947,7 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>Impresa BE 0406.919.552, fondata nel 1880. Sede: Asiadok 28A, 2030 Antwerpen (porto di Anversa). Margine lordo € 686.005 e 43ª posizione nel settore 'koffie en thee' (trendstop); NON pubblica il fatturato nell'ultimo bilancio depositato (schema abbreviato NBB → ricavi presumibilmente sotto la soglia delle piccole società, ~11 M€): TAGLIA DA VERIFICARE, possibile sotto i 5 M€. Torrefazione familiare, indicata come la più antica e la più grande di Anversa (fornisce ~60% del mercato locale) e private-label roaster per marchi terzi. Contatto alternativo pubblicato: stmichel@skynet.be. Tel. 03 234 34 70.</t>
+          <t>⚠ SOTTO SOGLIA: margine lordo 575.000 € con 3 dipendenti (dato 2017) — sotto il minimo di 5 M€ della forbice target. Tenuta nel censimento per copertura di filiera, su decisione del cliente. Impresa BE 0406.919.552, fondata nel 1880. Sede: Asiadok 28A, 2030 Antwerpen (porto di Anversa). Margine lordo € 686.005 e 43ª posizione nel settore 'koffie en thee' (trendstop); NON pubblica il fatturato nell'ultimo bilancio depositato (schema abbreviato NBB → ricavi presumibilmente sotto la soglia delle piccole società, ~11 M€): TAGLIA DA VERIFICARE, possibile sotto i 5 M€. Torrefazione familiare, indicata come la più antica e la più grande di Anversa (fornisce ~60% del mercato locale) e private-label roaster per marchi terzi. Contatto alternativo pubblicato: stmichel@skynet.be. Tel. 03 234 34 70.</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -35473,7 +35473,7 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Fatturato stimato ca. 18,4 Mio. USD (~17 Mio. €) - 96 dipendenti (fonte profilo RocketReach, dato stimato); azienda attiva dal 1935, uno dei principali produttori austriaci di imballaggi in cartone ondulato. Firmenbuch FN 136639s, LG Feldkirch. IN TARGET 10-20 M€. 4 stabilimenti a Lauterach (Funkenstraße 6/11, Scheibenstraße 20). Impresa familiare indipendente; Hans-Peter Flatz indicato come co-Geschäftsführer in fonti di stampa.</t>
+          <t>⚠ FUORI TAGLIA: ca. 72 Mio. € di fatturato e 320 addetti dichiarati dall'azienda — oltre il tetto di ~50 M€. Il dato precedente (~17 Mio. €, profilo RocketReach) era errato di un fattore quattro. Attiva dal 1935, fra i principali produttori austriaci di imballaggi in cartone ondulato. Firmenbuch FN 136639s, LG Feldkirch. Tenuta nel censimento su decisione del cliente.</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -36809,7 +36809,7 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>10-19 dipendenti, classe di fatturato 0-10 Mio. €, Bilanzsumme 1,74 Mio. € al 31.12.2024 (firmenabc.at / northdata). NOTA: sotto la soglia target — produttore austriaco di articoli in gomma dal 1947. Altri GF: Mag. Dr. Ulrich Zrunek, Dipl.-Ing. Helena Zrunek Marja</t>
+          <t>⚠ SOTTO SOGLIA: Bilanzsumme 1,74 Mio. € al 31.12.2024, 10-19 dipendenti — sotto il minimo di 5 M€ della forbice target. Tenuta nel censimento per copertura di filiera, su decisione del cliente. 10-19 dipendenti, classe di fatturato 0-10 Mio. €, Bilanzsumme 1,74 Mio. € al 31.12.2024 (firmenabc.at / northdata). NOTA: sotto la soglia target — produttore austriaco di articoli in gomma dal 1947. Altri GF: Mag. Dr. Ulrich Zrunek, Dipl.-Ing. Helena Zrunek Marja</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
